--- a/data/train/BTC Project - Human Gold Standard Dataset (GEPA Input).xlsx
+++ b/data/train/BTC Project - Human Gold Standard Dataset (GEPA Input).xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="140">
   <si>
     <t>month</t>
   </si>
@@ -65,10 +65,13 @@
     <t>notes</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>BeInCrypto</t>
   </si>
   <si>
-    <t>November Crypto Predictions: What's in Store This Month?</t>
+    <t>The Biggest Crypto Predictions for November 2023</t>
   </si>
   <si>
     <t>https://beincrypto.com/november-crypto-predictions-this-month/</t>
@@ -77,6 +80,40 @@
     <t>Compares the current cycle to similar previous bullish cycles and says the same will happen again. It also says BTC will move above $45k.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+The Biggest Crypto Predictions for November 2023
+Valdrin Tahiri
+3–4 minutes
+The biggest November crypto predictions deal with Bitcoin (BTC), the Bitcoin Dominance Rate (BTCD), and Ocean Protocol (OCEAN).
+October was an extremely bullish month for the cryptocurrency market. Bitcoin and several other altcoins reached new yearly highs. BeInCrypto looks at the crypto predictions for November.
+Bitcoin Will Move Above $45,000
+The BTC price increased significantly in October, reaching a new yearly high of $35,198. The increase was crucial since it caused a breakout from the $30,000 horizontal area. The area had acted as support twice during the previous bull run.
+In the two previous bullish cycles, the breakout from this horizontal area confirmed that the new bullish market cycle had begun.
+After breaking out, the price increased in the next monthly candlestick, reaching the first lower high (green trendline) of the market cycle.
+In the current movement, the lower high is at $48,000, 40% above the current price.
+Bitcoin (BTC) Price Weekly
+BTC/USD Weekly Chart. Source: TradingView
+Despite this bullish BTC price prediction, a close below $30,000 will invalidate the positive forecast. In that case, BTC can decrease by 40% to the closest support at $20,500.
+Altcoins Will Lead the Way
+The BTCD has increased since September 2022. In June 2023, it broke out from the 48% horizontal resistance area, which had been in place for 760 days. This led to a new yearly high of 54.35% in October.
+Due to this increase, the monthly Relative Strength Index (RSI) reached a new all-time high of 61 (yellow icon). Market traders use the RSI as a momentum indicator to identify overbought or oversold conditions and to decide whether to accumulate or sell an asset.
+The two previous times the indicator was close to 60 (red icons) led to downward movements of 20 and 45%, respectively.
+In the current BTCD chart, a drop to the 48% support area will be a decrease of 10%. When combined with the previous bullish BTC price prediction, this would mean that a large percentage of altcoins will experience massive gains.
+Bitcoin Dominance Rate (BTCD) Movement
+BTCD Monthly Chart. Source: TradingView
+Despite this bearish BTCD prediction, a monthly close above the 0.5 Fib retracement resistance level at 56.50% will cause a 12% increase to the 0.618 Fib at 60.55%.
+OCEAN Concludes November Crypto Predictions
+OCEAN broke out from the $0.27 horizontal resistance area in January. While it reached a new yearly high of $0.58 the next month (red icon), it did not break out from a long-term descending resistance trendline. The trendline has been in place since the all-time high.
+After several unsuccessful breakout attempts, OCEAN finally broke out last week. At the time of the breakout, the trendline had been in place for 930 days.
+If the increase continues, the next closest resistance will be at $1.05, 180% above the current price.
+OCEAN Price Prediction
+OCEAN/USDT Weekly Chart. Source: TradingView
+Despite this bullish OCEAN price prediction, failure to sustain the increase can cause a 25% drop to the $0.28 horizontal support area.
+This would invalidate the breakout from the long-term trendline.
+For BeInCrypto’s latest crypto market analysis, click here.</t>
+  </si>
+  <si>
     <t>CoinDCX</t>
   </si>
   <si>
@@ -89,6 +126,29 @@
     <t>Says it will go up in every way including other cyptos and pointing out that investors are withdrawling BTC from exhanges. Also mentions government forces like rate cuts.</t>
   </si>
   <si>
+    <t xml:space="preserve">coindcx.com
+December Rally in Bitcoin Price Hints at $45,000 Level by March 2024!
+~4 minutes
+Key Takeaways:
+    Milestone Price Surge: Bitcoin price breached $40,000 for the first time since early April 2022 and is currently at $41,700, signifying a notable milestone in its market resurgence.
+    Ethereum Price Rally: Ethereum price also surged, surpassing $2,200 for the first time in several months, aligning with the broader crypto market’s positive momentum.
+    Market Sentiment and Drivers: The bullish trend in Bitcoin price was influenced by optimistic comments from US central bankers and hopes surrounding a potential spot Bitcoin ETF approval.
+    Investor Behavior: Withdrawals of 37,000 BTC from exchanges suggest a growing preference among investors for holding Bitcoin directly, reflecting a strong bullish sentiment.
+    Future Expectations: Analysts foresee potential rate cuts and anticipate further positive developments in Bitcoin price, with traders actively engaging in options that bet on Bitcoin reaching $45,000 by March 2024.
+The recent surge in Bitcoin price beyond $40,000 represents a significant milestone, marking a resurgence in the crypto landscape after a prolonged period. Ethereum price rise above $2,200 echoes the broader crypto market’s steady but promising rally, indicating renewed investor interest and market confidence.
+Bitcoin price fluctuation around the $40,000 level recently culminated in its breakthrough, crossing $41,700 at press time. Ethereum price mirrored this surge, reaching $2,205 within 24 hours. While several top 10 cryptos by market cap witnessed moderate gains, BNB coin slightly dipped by approximately 0.1% during the same period.
+Read On: Bitcoin Price Prediction
+BTC/USD | Source: TradingView
+The withdrawal of 37,000 BTC by Bitcoin holders between November 17 and December 1 has also signified a notable shift toward direct custody of coins, indicative of a robust bullish sentiment. Analysts foresee a possible rate cut in the upcoming year, fostering positive investor sentiment surrounding Bitcoin ETF applications from major asset management entities.
+Federal Reserve chairman Jerome Powell’s implications of restrictive interest rates have sparked expectations for an imminent rate cut. This, in turn, has propelled both gold futures and cryptos higher, contributing to bullish market sentiment and anticipated upticks in Bitcoin price in the near future. Moreover, the crypto market’s positive response to lower bond yields has further buoyed Bitcoin price’s upward trajectory.
+In line with this bullish sentiment, traders have increasingly engaged in topside option plays, placing their bets on Bitcoin price, potentially reaching $45,000 by March 2024. This trading activity surge signals confidence in Bitcoin’s future performance and market trajectory.
+The resurgence of Bitcoin above $41,700 is a testament to renewed investor optimism and resilience within the crypto landscape. The concurrent rise in Ethereum price underlines the market’s broader positive sentiment, reinforcing the renewed faith in digital assets and the anticipated growth within the crypto space.
+As the crypto market continues to evolve, the recent milestone achieved by Bitcoin and Ethereum symbolizes a potential turning point, reigniting interest among investors and enthusiasts alike and setting the stage for a potentially bullish period ahead.
+Learn More: Ethereum Price Prediction
+Source: CoinDesk
+</t>
+  </si>
+  <si>
     <t>WazirX</t>
   </si>
   <si>
@@ -101,6 +161,25 @@
     <t>Cites many fears based on uncertainty in the goepolitical state of the world and the stock market. Says the market sentiment is veering towards greed.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+wazirx.com
+Bitcoin's price remains steady, market sentiment veers towards 'Greed' - WazirX Blog
+Harshita Shrivastava
+~3 minutes
+The market is anticipating pivotal events: the Fed’s interest rate decision and US January unemployment rate data. Bitcoin’s substantial gains, driven by Tether issuing $1BN in USDT, faces uncertainty with the Fed’s announcement in line. A potential rate cut may favor bulls, while unchanged rates could signal bearish sentiment. Bitcoin’s Bollinger Bands hint at reduced volatility. 
+Bitcoin’s correlation with the S&amp;P 500 has declined in the last one month. This indicates a negative correlation between the two. This shouldn’t affect crypto if the US stock market faces a downfall after liquidation of Evergrande. However, should the correlation coefficient increase in the coming days, the ripple effects could be felt in the crypto industry. 
+The Exponential Moving Average for a 10-day EMA indicates “Buy” at 42113, and a 200-day EMA indicates “Buy” at 38583. The Simple Moving Average for a 10-day SMA indicates “Buy” at 41377, and a 200-day SMA indicates “Buy” at 33924.
+The Ichimoku Base Line, valued at 43777, continues to be neutral. The Hull Moving Average indicates “Sell” at 42563. The Volume Weighted Average indicates “Sell” at 42122. 
+The Relative Strength Index (14) sits at 57, indicating “Neutral”. The Stochastic %K (14, 3, 3) at 88 and the Average Directional Index (14) at 18 indicate a Neutral outlook. 
+The MACD Level (12, 26), at -196, indicates “Buy”. The Stochastic RSI Fast (3, 3, 14, 14) at 99  indicates ‘Neutral’, and William’s Percentage at -0 indicates ‘Neutral’ as well.
+As of 10:00 AM, 30th January 2024, on WazirX, Bitcoin’s price is ₹37,73,020, with a 0.12% decrease in the last 24 hours. There was a 3.04% increase in its price over the last 7 days.
+Ethereum (ETH) is trading at ₹2,20,986. There was a decrease of 0.27% in the last 24 hours. There was a 2.19% increase in its price over the last 7 days.
+The top gainers on Pendle(PENDLE), Storj(STORJ) and DFI.Money(YFII) with a price increase of 16.99%, 16.98%, and 12.98%, respectively.
+However, the tokens that underperformed comprised Contentos(COS), Auction(AUCTION), Uma(UMA) with price decreases of 13.42%, 7.36%, and 6.74%, respectively.
+Shiba Inu (SHIB) saw a price decrease of 0.12% and is now priced at ₹0.000815. Dogecoin (DOGE) saw a increase of 1.57% and is now priced at ₹7.21.
+  Disclaimer: Click Here to read the Disclaimer.</t>
+  </si>
+  <si>
     <t>CryptoNews</t>
   </si>
   <si>
@@ -113,6 +192,37 @@
     <t>Says rate cuts and an upcoming halving event will both move BTC up higher. Also says the SEC giving the go ahead on ETFs is going to bring traditional finance into the BTC market.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+cryptonews.com
+Matrixport: Bitcoin's Target of $63,000 by March 2024 is Achievable
+Author
+5–7 minutes
+Ruholamin Haqshanas
+Author
+Ruholamin HaqshanasVerified
+Part of the Team Since
+Oct 2021
+About Author
+Ruholamin Haqshanas is a contributing crypto writer for CryptoNews. He is a crypto and finance journalist with over four years of experience. Ruholamin has been featured in several high-profile crypto...
+Last updated: 
+February 23, 2024
+Bitcoin price
+Source: Midjourney
+A new report from Matrixport predicts that Bitcoin (BTC) could reach a target of $63,000 by March 2024. In its report, Matrixport identified four key catalysts that could propel Bitcoin to new heights, including the recent approval of spot Bitcoin ETFs, the upcoming halving event, and interest rate cuts. Since the SEC greenlighted spot Bitcoin ETFs on January 10, there has been a growing demand for these products. Earlier this week, daily spot Bitcoin ETF trading volume amounted to nearly $2 billion, the highest level since the first day of trading on January 11.As reported earlier, spot Bitcoin ETFs witnessed a substantial influx of approximately $2.3 billion last week, nearly doubling the previous week’s inflow of $1.2 billion.These inflows accounted for almost half of the total net inflow since the inception of BTC ETFs, which currently stand at approximately $5 billion.
+Bitcoin Halving to Further Drive Bitcoin Price Higher
+The Matrixport report noted that the Bitcoin Halving event, slated for 2024, will further drive the price of BTC higher by reducing supply. The Bitcoin halving is a pre-scheduled event that reduces the reward for mining new blocks by half, effectively slowing the rate at which new bitcoins are created. Historically, halving events have been precursors to substantial price rallies, attributed to the reduced supply of new Bitcoins entering the market.
+    Matrixport released a new report stating that BTC’s goal of reaching $63,000 in March 2024 is achievable. Catalysts include: the approval of a Bitcoin spot ETF, the Bitcoin halving, expectations of an interest rate cut after the Fed’s FOMC meeting, and the U.S. presidential…
+    — Wu Blockchain (@WuBlockchain) February 23, 2024
+The report also mentioned that expectations of interest rate cuts following the Federal Reserve’s Federal Open Market Committee (FOMC) meetings could tilt the scales in favor of riskier assets like Bitcoin. 
+Lower interest rates typically reduce the appeal of yield-generating investments, making growth-oriented assets more attractive.
+Furthermore, the upcoming US presidential elections and policy uncertainty could also affect Bitcoin prices. 
+Such periods have often seen investors flocking to alternative assets like Bitcoin as a hedge against potential economic policy shifts.
+However, the impact of such political events on cryptocurrency markets is quite complex, making it challenging to make a clear prediction.
+Bitwise CIO Sees Bitcoin Surpassing $80,000
+Bitwise Chief Investment Officer Matt Hougan also expects Bitcoin to soar beyond $80,000 this year thanks to the recent success of spot ETFs.In a recent interview, Hougan highlighted the sustained demand for ETFs, which has exceeded his expectations.He said that this wave of interest from traditional finance, akin to Bitcoin’s IPO in the US market, will lead to further institutional investment and drive up prices.“Think of the ETF launch as Bitcoin’s IPO in the U.S. market. It has just unleashed a huge wave of interest from traditional finance, and it has exceeded my expectations.” Likewise, analysts at investment firm Bernstein expect Bitcoin to resume its upward trajectory, surpassing its previous all-time high of $69,000 and potentially reaching $70,000 this year.The analysts have expressed confidence in the cryptocurrency’s risk-reward profile, stating that no significant challenges are anticipated to impede its ascent.Meanwhile, Anthony Scaramucci, the founder and managing partner of hedge fund SkyBridge, has suggested that the price of Bitcoin could potentially reach $170,000 in the coming year.
+Follow us on Google News</t>
+  </si>
+  <si>
     <t>247WallSt</t>
   </si>
   <si>
@@ -125,6 +235,46 @@
     <t>Equally long sections for both a bullish and bearish outlook. However, the title and rest of the article mentions milestons of $100k, which is higher than its price point at the time.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+247wallst.com
+Prediction: Bitcoin Will Top $100,000 in 2024
+Sam Daodu
+8–9 minutes
+This post may contain links from our sponsors and affiliates, and Flywheel Publishing may receive compensation for actions taken through them.
+Bitcoin (BTC), the world’s first and most popular cryptocurrency, has captivated investors with its meteoric rise and dramatic falls.  In 2023, it experienced a significant price increase, leaving many wondering if it can maintain this momentum and reach the highly anticipated milestone of $100,000 in 2024. 
+This article explores the key factors influencing Bitcoin’s possible $100,000 price trajectory and analyzes the scenarios supporting and opposing this ambitious prediction.
+Bitcoin (BTC) Price History
+Bull market trend. Cryptocurrency. Bitcoin Stock Growth. Chart shows a strong increase in the price of bitcoin. Investing in virtual assets. Investment platform with charts and bitcoin coin.
+Accurately forecasting any crypto token’s future price is complex.  Although past performance isn’t a perfect predictor, examining Bitcoin’s historical price movements offers valuable context for evaluating price predictions.  
+Bitcoin’s price journey has been nothing short of remarkable.  Upon its launch in 2009, Bitcoin held no value.  However, its price rose as user adoption grew through buying, selling, trading, and general use.  Bitcoin surpassed the $0.09 mark in 2010 and broke the $1 barrier in early 2011, even reaching double digits later that year.  The price fluctuated significantly, but Bitcoin climbed above $1,000 in 2013 before experiencing a decline in 2014, followed by a recovery in 2015.  
+A significant surge occurred in 2017, with Bitcoin surpassing $1,000 and reaching a peak of over $17,000 during the late 2017 crypto bullish run.  The following year, Bitcoin witnessed a correction, with the price dipping below $10,000 as the market entered a bear cycle.  However, 2021 marked a period of significant growth for Bitcoin and the cryptocurrency market.  
+Bitcoin experienced multiple price spikes, reaching a high above $60,000 in April before a summer slump.  The price recovered, culminating in a new all-time high of $68,789.63 on November 10, 2021.  The year closed with Bitcoin priced at $45,819.95.
+The cryptocurrency market experienced a significant downturn in late 2022.  A series of crashes resulted in Bitcoin (BTC) trading below $20,000 by November.  By year-end, Bitcoin closed at $16,517.52, representing a near 65% annual decline that mirrored the overall market trend.
+In contrast, 2023 proved to be a more positive year for Bitcoin.  The price temporarily surpassed $30,000 in April before experiencing a correction, reaching a low of $24,797 on June 15th. By November 1st, the price exceeded $35,000, and a key milestone was achieved on December 3rd when Bitcoin climbed above $40,000 for the first time since April 2023.  Bitcoin closed the year at $44,167.33, reflecting a remarkable 165% annual increase and exceeding general market performance.
+READ: The analyst who called NVIDIA in 2010 just named his top 10 AI stocks
+The positive momentum continued into early 2024. The launch of crypto ETFs on January 11th pushed the price even higher, reaching $48,969.  A slight correction occurred later in the month, with Bitcoin dipping below $40,000.  However, February recovered, with Bitcoin’s price reaching $47,125 by February 9th, 2024.
+As of today, Bitcoin (BTC) is trading at $73,139.81.  The 24-hour trading volume is significant, exceeding $51 billion.  Bitcoin’s price has increased by 2.78% in the past 24 hours.  It maintains its position as the leading cryptocurrency by market capitalization, valued at over $1.4 trillion.  There are approximately 19.65 million BTC coins in circulation, with a maximum supply capped at 21 million.
+The Bullish Case for $100,000 Bitcoin
+bullish divergent concept, gold bull
+Several factors contribute to the bullish sentiment surrounding Bitcoin’s price prediction to reach $100,000 in 2024:
+    The Halving Effect:  Scheduled for May 2024, the next Bitcoin halving event will significantly reduce the number of new Bitcoins entering circulation. Historically, price surges have followed halving events as demand outstrips supply. Proponents argue that the reduced supply and increasing demand could propel Bitcoin towards six figures.
+    Institutional Adoption:  The growing acceptance of Bitcoin by institutional investors, including hedge funds, investment banks, and corporations, is a significant driver of its price. As these institutions allocate more of their portfolios to Bitcoin, demand is expected to rise, potentially pushing the price toward $100,000.
+    Macroeconomic Uncertainty:  Global economic factors, such as rising inflation and potential recessions, could lead investors to seek alternative assets like Bitcoin.  Bitcoin’s perceived scarcity and potential hedge against inflation could attract investors seeking to preserve their wealth, potentially driving the price upwards.
+    Technological Advancements:  The continuous development of the Lightning Network, a second-layer solution designed to address Bitcoin’s scalability issues, could bolster its adoption and utility. Faster transaction speeds and lower fees attract a broader user base and contribute to increased demand, potentially pushing the price toward $100,000.
+The Bearish Case Against $100,000 Bitcoin
+Global recession. Financial crisis. Image of golden bitcoin rising among piles of other crypto coins on digital background of chart with sole thick red line representing crash of crypto trading market
+While the arguments predicting Bitcoin’s price at $100,000 by 2024 are compelling, several factors could hinder its progress:
+    Regulatory Scrutiny:  Regulatory uncertainty and potential crackdowns by governments worldwide could dampen investor enthusiasm and restrict Bitcoin’s growth. Stringent regulations could make it more difficult for institutions and individuals to invest in Bitcoin, potentially hindering price growth.
+    Altcoin Competition:  The emergence of alternative cryptocurrencies (altcoins) offering faster transaction speeds and unique features could challenge Bitcoin’s dominance. Investors may allocate funds towards altcoins with perceived advantages, impacting Bitcoin’s demand and price growth.
+    Security Risks:  The inherent volatility and security risks associated with cryptocurrency markets could deter investors seeking more stable investment options. High-profile hacks and security breaches could erode trust in Bitcoin and hinder its mainstream adoption.
+    Energy Consumption Concerns:  The energy-intensive proof-of-work mining process employed by Bitcoin raises environmental concerns. Growing public pressure and potential regulations to reduce Bitcoin’s carbon footprint could dampen investor sentiment and price growth.
+The Road to $100,000: A Speculative Outlook
+Predicting the future price of Bitcoin is a complex endeavor as it hinges on several factors.  The combined effects of the halving event, institutional adoption, and increasing public awareness could create a scenario conducive to positive price growth. However, regulatory issues, altcoin competition, and ongoing security concerns pose significant challenges.
+Regardless of the circumstances, the positive market sentiments and the impending bull run are set to propel Bitcoin to new heights. And with the approval of spot ETFs, Bitcoin is now available on the retail market, further increasing its viability. These market conditions are expected to impact Bitcoin, and we predict the cryptocurrency will finally cross the $100,000 milestone in 2024. 
+The analyst who called NVIDIA in 2010 just named his top 10 AI stocks
+Wall Street is pouring billions into AI, but most investors are buying the wrong stocks. The analyst who first identified NVIDIA as a buy back in 2010 — before its 28,000% run — has just pinpointed 10 new AI companies he believes could deliver outsized returns from here. One dominates a $100 billion equipment market. Another is solving the single biggest bottleneck holding back AI data centers. A third is a pure-play on an optical networking market set to quadruple. Most investors haven't heard of half these names. Get the free list of all 10 stocks here.</t>
+  </si>
+  <si>
     <t>Experts' Bitcoin Price Prediction After Halving 2024</t>
   </si>
   <si>
@@ -134,6 +284,36 @@
     <t>Quotes many experts, essentially all saying BTC will rise. Compares BTC to gold, with some experts calling it "digital gold."</t>
   </si>
   <si>
+    <t xml:space="preserve">
+wazirx.com
+Experts' Bitcoin Price Prediction After Halving 2024 | WazirX
+Harshita Shrivastava
+5–6 minutes
+    Cathie Wood’s Bitcoin Prediction on Bitcoin Halving
+    Michael Saylor’s Bitcoin Prediction on Bitcoin Halving
+    Binance’s CEO, Richard Teng’s Bitcoin Prediction on Bitcoin Halving
+    Winklevoss Twins’ Bitcoin Prediction on Bitcoin Halving
+    Tim Draper’s Bitcoin Prediction on Bitcoin Halving
+    JP Morgan’s Bitcoin Prediction on Bitcoin Halving
+As the crypto world eagerly anticipates the Bitcoin halving event in 2024, investors and enthusiasts are eager to learn insights into what the future holds for Bitcoin, the most prominent crypto.
+With each halving event historically heralding significant shifts in Bitcoin’s price trajectory, industry experts have been offering their predictions on where Bitcoin’s price may head after the upcoming halving.
+In this blog, let’s delve into the forecasts and insights shared by the experts.
+Cathie Wood’s Bitcoin Prediction on Bitcoin Halving
+Cathie Wood predicts a bullish trajectory for Bitcoin’s price post-halving, envisioning it reaching $3.8 million due to institutional adoption and new ETF products. Wood’s analysis suggests that if institutional investors allocate over 5% of their portfolios to Bitcoin, it could add $2.3 million to her initial projection. With Ark Invest’s bullish outlook and the SEC’s approval of spot Bitcoin ETFs, demand for the cryptocurrency has surged. Wood expects the halving event, anticipated in April, to catalyze further demand. Drawing parallels to past halvings, she foresees Bitcoin’s price continuing to soar, emphasizing the nascent stage of the financial ecosystem native to the internet.
+Get WazirX News First
+Michael Saylor’s Bitcoin Prediction on Bitcoin Halving
+Michael Saylor predicts Bitcoin will surpass gold’s value, emphasizing its superiority and potential to divert funds from traditional assets. With MicroStrategy’s recent purchase of 12,000 bitcoins, Saylor asserts that Bitcoin’s scarcity, emphasized by the upcoming halving, will drive its price upward to meet increasing investor demand. Bitcoin’s market cap has already surpassed silver’s, reaching over $1.4 trillion, yet it has considerable growth potential compared to gold’s $14.7 trillion valuation. Saylor’s bullish stance underscores Bitcoin’s status as a digital gold and its potential to reshape the financial landscape, exemplified by BlackRock’s interest in Bitcoin ETFs.
+Binance’s CEO, Richard Teng’s Bitcoin Prediction on Bitcoin Halving
+Binance’s CEO, Richard Teng, foresees Bitcoin surpassing $80,000 by year-end, attributing it to decreasing supply and increasing demand. Institutional adoption, highlighted by the approval of a spot Bitcoin ETF in the U.S., has fueled market rallies, with Bitcoin recently exceeding $73,000. Teng’s optimism aligns with Standard Chartered’s raised year-end target of $150,000 for Bitcoin. Teng succeeded Binance’s founder, Changpeng Zhao, in November 2023. Anticipating increased investment from family offices and endowment funds in Bitcoin ETFs, Teng acknowledges market volatility but views it positively for overall market health. His predictions signal a bullish outlook for Bitcoin’s price trajectory post-halving.
+Winklevoss Twins’ Bitcoin Prediction on Bitcoin Halving
+Cameron Winklevoss, the co-founder of the Gemini crypto exchange, anticipates a surge in Bitcoin demand after the 2024 halving, slated for April. He points to newly approved spot Bitcoin ETFs, accumulating BTC at a rate ten times higher than daily minting. Winklevoss highlights this trend as a potential catalyst for increased Bitcoin demand post-halving, with ETFs expected to remove twenty times more Bitcoin daily than what’s newly minted.
+Tim Draper’s Bitcoin Prediction on Bitcoin Halving
+Venture capitalist Tim Draper predicts Bitcoin’s value to triple by 2024, attributing this surge to the influx of investments into spot ETFs and the halving event. He envisions Bitcoin reaching $250,000 by year-end, facilitated by the introduction of spot Bitcoin ETFs in the U.S. Draper highlights ETFs as key for investors seeking exposure to Bitcoin without the complexities of direct ownership. He emphasizes Bitcoin’s capped supply and growing acceptance as a hedge against fiat currency depreciation. Draper advocates Bitcoin as a strategic hedge amid concerns over bank instability and currency depreciation, underscoring its relevance in diversifying investment portfolios.
+JP Morgan’s Bitcoin Prediction on Bitcoin Halving
+Despite historic gains, JP Morgan analysts predict a potential price decline for Bitcoin post-halving in April 2024. Halving and reducing daily token issuance is expected to create a supply shortage, historically leading to price increases. However, increased mining difficulty may lower production costs, driving Bitcoin’s price back to around $42,000. This estimate accounts for potential drops in hashrate due to less efficient miners exiting the market. Nevertheless, sustained high Bitcoin prices could mitigate this decline, especially with expanding access through new spot Bitcoin ETFs attracting investors and keeping smaller miners profitable.
+  Disclaimer: Click Here to read the Disclaimer.</t>
+  </si>
+  <si>
     <t>What Is PlanB's Amazing Bitcoin Price Prediction For 2024?</t>
   </si>
   <si>
@@ -143,6 +323,82 @@
     <t>Says the market remains cautiously optimistic and mentions many technical details as to why it thinks so.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+wazirx.com
+What Is PlanB’s Amazing Bitcoin Price Prediction For 2024? - WazirX Blog
+Shashank
+8–11 minutes
+    Stock-to-Flow Model
+    Market Cycle Analysis
+    Relative Strength Index (RSI)
+    200-Week Moving Average (200WMA)
+    Realized Price and Realized Return
+    Bitcoin in Profit
+    Conclusion
+Note: This blog is written by an external blogger. The views and opinions expressed within this post belong solely to the author.
+As we are towards the end of May 2024, the landscape of Bitcoin (BTC) pricing is on the minds of many investors and analysts. With the recent halving and various market indicators showing mixed signals, understanding the potential price movements of Bitcoin requires a deep dive into multiple analytical models and market cycles.
+In this blog, we have delved into PlanB‘s comprehensive prediction for Bitcoin’s price in May 2024 and beyond. He has leveraged various key charts and models. Let’s have a quick look at them.
+Get WazirX News First
+Stock-to-Flow Model
+The Stock-to-Flow (S2F) model is one of the most popular methods for predicting Bitcoin’s price. This model, which relates an asset’s stock (current supply) to its flow (new production), has been particularly insightful for Bitcoin, an asset with a fixed supply and predictable issuance schedule.
+As April 2024 ended, Bitcoin closed slightly above $60,000, an almost $10,000 drop from the previous month, primarily attributed to the cooling down of the ETF-driven price surge. Despite this dip, Bitcoin remains up 36% year-to-date. This period marks the end of the blue dot phase in the S2F model, indicating the conclusion of the pre-halving phase. Historically, Bitcoin’s price tends to catch up to the model’s predicted value post-halving, suggesting a bullish outlook.
+Key Points from the Stock-to-Flow Model:
+    Current Price (as of 21st May): Approximately $71,089.
+    2024-2028 Target: Around $500,000 on average.
+    Short-term Prediction: Recovery in miner revenue suggests a doubling of price, implying Bitcoin could reach $120,000 by the end of 2024.
+    Long-term Prediction: Possible peak around $200,000 by 2025 due to historical post-halving market behaviors.
+Market Cycle Analysis
+The Bitcoin market cycle analysis refers to studying the repetitive phases the crypto tends to go through over time. These cycles typically consist of four main phases:
+    accumulation: where prices are relatively low and smart investors start buying;
+    uptrend: characterized by rapid price increases and growing public interest;
+    distribution: where early investors begin to sell off their holdings at higher prices and
+    downtrend: marked by falling prices and widespread selling.
+Market cycle analysis aims to understand long-term trends by analyzing historical price data, trading volumes, and investor behavior. We can identify patterns that help predict future price movements by examining the cyclic nature of Bitcoin markets.
+Current Market Cycle Insights:
+    Current Phase: Still in a bull market, despite recent dips.
+    Historical Dips: 25% corrections are common and do not signal the end of a bull market.
+    Expected Movement: Continued upward trajectory with occasional corrections.
+Relative Strength Index (RSI)
+The Relative Strength Index (RSI) is one of the popular momentum oscillators used to evaluate the speed and change of price movements. Developed by J. Welles Wilder, RSI measures the magnitude of current price changes to determine overbought or oversold conditions in the market. It is typically displayed as a line graph on a scale of 0 to 100.
+An RSI above 70 suggests that crypto might be overbought and is due for a price correction, while an RSI below 30 indicates that it could be oversold and potentially undervalued. Traders mostly use RSI to identify potential buy and sell signals, gauge the strength of a trend, and predict possible reversals.
+RSI Observations:
+    Current RSI: Around 65, indicating a normalization.
+    Historical Context: Current RSI levels are consistent with those seen during previous halvings.
+    Future Expectation: Higher RSI in the coming months, signaling strong price increases.
+200-Week Moving Average (200WMA)
+The 200-Week Moving Average (200WMA) is a long-term technical indicator used to analyze a crypto market’s overall health and trend direction over an extended period. It calculates the average closing price of crypto over the past 200 weeks, smoothing out daily volatility to provide a clearer view of long-term trends. The 200WMA is particularly significant in the crypto market, where price swings can be extreme.
+Crypto trading above its 200WMA is generally considered to be in a long-term bullish phase, suggesting sustained upward momentum. Conversely, trading below this average often signals a bearish phase, indicating potential long-term weakness.
+Investors and traders use the 200WMA as a key support or resistance level, a critical price floor during market downturns. For instance, Bitcoin has historically rebounded from its 200WMA during significant corrections, making it a valuable tool for identifying strategic entry and exit points.
+200WMA Insights:
+    Current Level: Slight increase, indicating a conservative floor around $34,000.
+    Bull Market Behavior: Prices typically stay well above the 200WMA during bull markets.
+Realized Price and Realized Return
+Realized Price and Realized Return are important metrics in the crypto market, providing insights into a crypto’s cost basis and profitability.
+Realized Price is the average price at which all existing units of crypto were last moved on the blockchain. It is calculated by summing the value of all coins at the price they were last transacted and then dividing by the total supply. This metric helps investors understand the aggregate cost basis of the market, offering a benchmark for evaluating current price levels. When the market price is above the realized price, it indicates that the average investor is in profit.
+Realized Return measures the profitability of recently transacted coins. It reflects the percentage gain or loss experienced by the average coin that has moved on the blockchain within a specific timeframe. Positive realized returns indicate profitable sales, suggesting bullish market sentiment, while negative returns suggest selling at a loss, often associated with bearish conditions.
+Together, these metrics provide valuable context for market behavior and investor sentiment.
+Realized Price Analysis:
+    Current Realized Price: $29,000.
+    Short-term Holder Realized Price: $45,000, acting as a support level during dips.
+    Expected Behavior: Dips to $45,000 likely to bounce back, supporting bullish momentum.
+Realized Return Analysis:
+    Current Return: 7%, indicating sellers are taking profit, which is typical in a bull market.
+    Implication: Profit-taking does not signal weakness but rather a healthy market behavior.
+Bitcoin in Profit
+Bitcoin in Profit indicates the percentage of Bitcoin (BTC) currently held in wallets acquired at a price lower than the current market price. This metric reflects the proportion of holders in a profitable position based on their purchase price versus the present value.
+A high percentage suggests bullish sentiment, with most holders in profit, potentially supporting higher prices. Conversely, a lower percentage indicates increased selling pressure from holders at a loss, which may contribute to market downturns.
+Analyzing this metric provides insights into market sentiment and potential price movements, aiding investors in understanding Bitcoin’s financial health and holder behavior.
+Bitcoin in Profit Analysis:
+    Current Status: 12% of Bitcoins are in loss, mainly those bought at the recent peak of $70,000.
+    Comparison to Previous Cycles: Similar to early bull market phases in 2012 and 2020.
+    Future Outlook: Likely to see a second bullish wave as seen in past cycles.
+To check out the complete analysis in detail, click here.
+Conclusion
+Based on the various analytical models and market indicators, the outlook for Bitcoin in May 2024 and beyond remains cautiously optimistic. The Stock-to-Flow model suggests a significant upward trajectory post-halving, with potential short-term targets of around $120,000 by the end of 2024. The market cycle analysis, RSI, and realized price metrics all point towards continuing the bull market despite occasional dips and profit-taking.
+While no prediction can be guaranteed, the convergence of these indicators strongly suggests a bullish trend in Bitcoin’s price over the coming months. Investors should remain vigilant and consider these insights when making their investment decisions.
+  Disclaimer: Click Here to read the Disclaimer.</t>
+  </si>
+  <si>
     <t>This is What Plan B's Latest Bitcoin Outlook for June 2024</t>
   </si>
   <si>
@@ -152,6 +408,84 @@
     <t>Says the maket leans towards a bullish trend and lists many models and historical data to support it. Says BTC will potentially reach new heights.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+wazirx.com
+This is What Plan B’s Latest Bitcoin Outlook for June 2024 - WazirX Blog
+Shashank
+7–9 minutes
+    Bitcoin’s Historical Performance
+    Market Analysis for June 2024
+        Current Price and Market Sentiment
+        Stock-to-Flow Model Projections
+        Bitcoin Market Cycle
+        Relative Strength Index (RSI)
+        200-Week Moving Average (200W MA)
+        Realized Price
+        Realized Return
+    Predictions and Factors Influencing Bitcoin’s Price in June 2024
+    Risks and Considerations
+    Conclusion
+Note: This blog is written by an external blogger. The views and opinions expressed within this post belong solely to the author.
+As we enter June 2024, the crypto market remains a focal point for investors, analysts, and enthusiasts. Bitcoin, which has been trying to cross the $70k mark, has shown significant volatility and resilience in the past few months.
+In this blog, we have delved into PlanB‘s comprehensive prediction for Bitcoin’s price in June 2024 using various models, historical data, and market indicators.
+Get WazirX News First
+Bitcoin’s Historical Performance
+Since its launch in 2009, Bitcoin has experienced multiple market cycles. These cycles are often characterized by a period of rapid price increase (bull market) followed by a sharp decline (bear market).
+Key events that influence these cycles include:
+    halving events,
+    regulatory changes,
+    technological advancements, and
+    macroeconomic factors.
+Halving Events
+Bitcoin undergoes a halving approximately every four years, where the reward for mining new blocks is halved. This event decreases the rate at which new Bitcoins are created and is historically associated with significant price increases.
+The recent halving happened in April 2024, and the next is expected in 2028. Each halving has historically led to a bull market, which typically starts within a few months after the event. Currently, the crypto community is also expecting a bull run.
+Stock-to-Flow Model
+The Stock-to-Flow (S2F) model, popularized by analyst PlanB, predicts Bitcoin’s price based on its scarcity. The model considers the existing stock of Bitcoin (total supply) and the flow (new supply per year). Historically, Bitcoin’s price has closely followed the projections of the S2F model, particularly after halvings. Interesting, right!?
+Market Analysis for June 2024
+Current Price and Market Sentiment
+As of 06 June 2024, Bitcoin’s price hovers around $70,974, according to CoinMarketCap. This marks a significant rise from previous months, indicating a potential new cycle following the recent halving. Market sentiment appears bullish, with investors anticipating further price increases.
+Stock-to-Flow Model Projections
+The updated S2F model, refitted with five years of new data, maintains power of three in its parameters, suggesting continued validity. According to the model, Bitcoin’s price should see a substantial increase post-halving, potentially reaching new all-time highs. PlanB’s model suggests that Bitcoin could reach $100,000 or higher within this cycle, driven by increased scarcity and market adoption.
+Future Predictions
+    Last Cycle Prediction: $500,000 per Bitcoin
+    Next Cycle Prediction: $4,000,000 per Bitcoin
+The model suggests a substantial price increase, especially after halving events, with Bitcoin prices lagging slightly but eventually catching up.
+Bitcoin Market Cycle
+The recent halving event in 2024 has set the stage for a new bull market. Historical data shows that post-halving periods often lead to significant price increases. The market cycle analysis indicates that Bitcoin is likely entering a new bullish phase, with substantial price appreciation expected in the coming months.
+Patience is key, as historical data indicates that the real price pump usually starts after some delay post-halving.
+Relative Strength Index (RSI)
+The RSI, a momentum oscillator, measures the speed and change of price movements. As of June 2024, Bitcoin’s RSI stands at 70, indicating strong buying momentum. Bitcoin’s RSI has historically remained above 70 for extended periods during bull markets, sometimes exceeding 80. This suggests that the current uptrend may continue.
+Future Expectations
+PlanB expects a similar pattern to unfold, with the RSI staying elevated over the next year. The only exception was during the last cycle, which was impacted by the China mining ban, abruptly halting the bull market.
+200-Week Moving Average (200W MA)
+The 200W MA is a long-term trend indicator that smooths out price data to identify the overall direction. Currently, the 200W MA for Bitcoin is rising, reflecting sustained upward momentum. This trend is consistent with previous post-halving bull markets, where Bitcoin’s price has consistently stayed above this average, signaling strong support levels.
+Price Predictions
+Based on historical trends, the 200WMA suggests that Bitcoin should reach at least $100,000 soon, potentially within this year.
+Realized Price
+Current Analysis
+    Realized Price: $30,000
+    2-Year Realized Price: $47,000
+Both metrics are rising, resembling patterns seen before previous bull markets in 2016 and 2012. The realized price often serves as a support level during market dips.
+Historical Support
+The light blue line, representing the realized price, has acted as a support level in previous bull markets, such as the dip in April 2020. PlanB expects similar support to hold in the current market, predicting that Bitcoin will not fall below this level.
+Realized Return
+Market Sentiment
+May saw sellers returning to profit, a pattern similar to what occurred in 2016, signaling the start of a bull market. This pattern of red-green-orange in realized returns indicates a healthy market sentiment moving forward.
+Predictions and Factors Influencing Bitcoin’s Price in June 2024
+Short-Term Predictions
+Based on the above indicators and historical trends, Bitcoin’s price is expected to continue its upward trajectory throughout June 2024. The combination of positive market sentiment, a rising 200W MA, and a robust RSI supports this outlook. Short-term targets could see Bitcoin testing the $75,000 to $80,000 range, with potential for higher spikes driven by market euphoria.
+Long-Term Outlook
+Looking beyond June 2024, the long-term outlook for Bitcoin remains bullish. The S2F model suggests that Bitcoin could reach $100,000 or even higher by the end of the current cycle. Factors such as increasing institutional adoption, technological advancements like the Lightning Network, and growing acceptance as a store of value contribute to this optimistic view.
+Risks and Considerations
+Despite the bullish outlook, several risks could impact Bitcoin’s price trajectory:
+    Regulatory Changes: Stricter regulations or adverse legal developments could negatively affect market sentiment and price.
+    Technological Risks: Security vulnerabilities or significant technological setbacks could undermine confidence in the network.
+    Market Dynamics: Market manipulation, sudden large-scale sell-offs, or macroeconomic factors could lead to increased volatility and potential price drops.
+Conclusion
+As we navigate through June 2024, Bitcoin’s price prediction leans towards a continuation of the current bullish trend, potentially reaching new highs in the coming months. The convergence of positive market indicators, historical data, and the Stock-to-Flow model supports this outlook. However, investors should remain vigilant and always consider the risks associated with the volatile crypto market.
+  Disclaimer: Click Here to read the Disclaimer.</t>
+  </si>
+  <si>
     <t>The Biggest Crypto Predictions for July 2024</t>
   </si>
   <si>
@@ -161,6 +495,43 @@
     <t>Says there is a bearish macro pattern forming and that other cryptos are falling. Also notes that NFT demand is "dying."</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+The Biggest Crypto Predictions for July 2024
+Aaryamann Shrivastava
+4–5 minutes
+The month of July is primarily focused on the potential launch of spot Ethereum ETFs. However, Bitcoin and a few other crucial assets have something equally huge ahead of them.
+BeInCrypto has compiled what major developments you can expect in the next month that could impact the crypto market.
+Bitcoin’s Price Could See a Multi-Month Low
+Bitcoin’s price, at $61,150 at the time of writing, is holding itself above the $60,000 mark. While many feared that the market’s uncertainty could have pulled it below this level, they missed the bigger picture.
+BTC on the weekly chart can be seen forming a double-top pattern. This macro bearish pattern signals that the asset may be set for a downward trend. Bitcoin’s price can be seen breaking below the neckline at $61,483.
+This breakdown might find some support at $58,874, but the pattern suggests a much larger decline. The target price is set 17% below the neckline at $50,982, which would result in a four-month low for BTC.
+The possibility of this happening is rather strong, considering the “sell in May and go away” notion continues to impact spot BTC ETF inflows. Combining this with the volatility of the crypto market, a drawdown is very possible.
+Read More: Bitcoin Halving History: Everything You Need To Know
+Bitcoin Price Analysis.
+Bitcoin Price Analysis. Source: TradingView
+However, Bitcoin’s price could also bounce back from $60,000 or $58,847 to invalidate the bearish thesis. This would be confirmed once $62,000 is reclaimed as support.
+Arbitrum Could See a New All-Time Low
+Arbitrum’s price decline is expected, but the threat of a new all-time low is alarming. ARB, the second-largest Layer-2 token behind Polygon (MATIC), has seen its demand dwindle significantly in recent weeks, leading to a massive price drop. Since early March, it has fallen by over 60% to $0.799, forming a head and shoulders pattern.
+A head-and-shoulders pattern is a bearish reversal chart pattern with three peaks — a higher middle peak (the head) flanked by two lower peaks (the shoulders). Once the neckline is broken, it indicates a potential trend reversal from bullish to bearish.
+Based on this pattern, Arbitrum’s target price is projected at $0. However, this is absurd because ARB is a fundamentally strong asset. The most likely outcome is a new all-time low for ARB, as it is currently sits above the current minimum of $0.739.
+Shifting market sentiment could accelerate this decline, and before the end of July, ARB could see a new ATL.
+Read More: Arbitrum (ARB) Price Prediction 2024/2025/2035
+Arbitrum Price Analysis.
+Arbitrum Price Analysis. Source: TradingView
+On the other hand, if Arbitrum’s price manages to bounce back from $0.739, it could take a shot at breaching $0.929. A succesful attempt could send ARB above $1.00, invalidating the bearish thesis.
+NFTs Are Dying
+Non-fungible tokens (NFTs) gained prominence in 2022, but their performance since then has been disappointing. Some resurgence in activity and demand occurred in Q1 this year.
+However, this revival appears short-lived. Over the past three months, overall trading volume has plummeted from $38.8 million to $7.9 million, marking an 81% decline.
+Read More: 7 Best NFT Marketplaces You Should Know in 2024
+NFT Trading Volume.
+NFT Trading Volume. Source: Dune
+The cause behind this drop is twofold. First, the lack of innovation offered in this space has left its demand minimal. Second, there has been a rise in alternative investment options and assets such as real-world assets (RWA).
+The rise in Artificial Intelligence (AI) tokens has also drawn investors’ attention. Given AI’s potential for growth, crypto investors are leaning more toward choosing them.
+As a result, the NFT trading volume could decline further as bearish market conditions and the aforementioned factors gain strength.
+</t>
+  </si>
+  <si>
     <t>InvestingHaven</t>
   </si>
   <si>
@@ -173,6 +544,59 @@
     <t>Doesn't provide any sentiment. Says there are reasons to believe BTC could move in either direction, and lists $69k as an important breakout price, but doesn't offer an opinion.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+investinghaven.com
+Bitcoin Price Analysis: 5 Must-Read Insights For August 2024
+Taki T.
+4–6 minutes
+Once BTC clears $69k, on a 3 to 5 day closing basis, it will mark an epic breakout. This highest probability outcome is that this will happen in a few months from now.
+Insights from this article are based on our most recent Bitcoin price prediction, available in the public domain.
+TIP – We recommend readers to read out Bitcoin prediction page, mentioned above, as it contains lots of insights about Bitcoin’s expected trend as well as support and buy the dip levels.
+Bitcoin price insight #1. The longest term trendline
+While we are interested in short term Bitcoin price insights, for August 2024 primarily, we always have to start with the higher timeframes.
+    When analyzing Bitcoin’s price, it is imperative to take a top down approach.
+That’s because of this chart dynamic: the longer a trendline, the more dominant.
+What we see on Bitcoin’s longest timeframe is that BTC fell below its longest trendline in the summer of 2022 for the first time in 9 years! In May of 2024, BTC touched this longest trendline as resistance. This is meaningful, as it might indicate that the pace of advancement (in the bigger scheme of things) is slowing down.
+While this longest term trendline creates a very important dynamic on Bitcoin’s chart, it does not help us understand the short timeframe.
+Bitcoin price analysis longest trendline
+Bitcoin price analysis – longest trendline
+Bitcoin price insight #2. Another long term trendline
+While the longest trendline since 2015 was breached some 2 years ago, the one that originates in 2017 is being respected.
+This is meaningful, as it means Bitcoin remains in a strong uptrend, an insight that crypto enthusiast will like and which contrast with the somehow concerning conclusion from the chart shown above.
+Short term, it means that this trendline might be tested again, in case markets get under pressure which could happen in August of 2024.
+Bitcoin price analysis long term trendline
+Bitcoin price analysis – long term trendline
+Bitcoin price insight #3. Why $69k is a critical level
+If we zoom in a bit, we see that a strong uptrend started in October of 2023, leaving a rising trendline unbroken until June 2024.
+What is important to realize is the price point that marks a breakdown, in this particular case $68k roughly, can be re-tested, once or twice.
+    We use $69k as THE most important price point for BTC, certainly in the short term.
+Remember, any price point as resistance can be exceeded for 3, 5, 8 days but price can come down, creating a failed breakout. So, if BTC moves above $69k, and stays there for at least 8 consecutive days, it will be a breakout.
+It’s unlikely this will happen in August 2024. Never say ‘never’ though in financial markets.
+Bitcoin price analysis $69k
+Bitcoin price analysis – $69k breakout point
+Bitcoin price insight #4. Which ‘event’ can create another dump?
+Since April, Bitcoin has experienced several dumps:
+    April – war in the Middle East (fading soon after).
+    May – war in Ukraine (fading soon after).
+    July – Bitcoin dumped in the market by Germany and MtGox.
+What might create another dump in the price of Bitcoin, in August, is broad market weakness. This is likely because there is a high probability volatility window on the timeline. We will know by mid-August whether the timeline will create volatility in markets.
+Bitcoin price analysis August 2024 dump
+Bitcoin price analysis – August 2024 dump catalyst
+Bitcoin price insight #5. Three month cycles
+In closing, the last relevant insight for August 2024 comes from Bitcoin’s 3-month cycle chart.
+What stands out on this chart is this:
+    A falling trendline since March, tested 3 times, potentially to be tested once more in August or September, around $52k.
+    Resistance at $69k.
+    One critical week in August 2024.
+Note – there is one more critical week in, in October.
+So, we cannot get too bullish in the short term until and unless $69k is broken to the upside for at least 8 consecutive days. That’s what this 3-month cycle chart learns us.
+Bitcoin price analysis three month cycles
+Bitcoin price analysis – three month cycles
+The yellow vertical lines on the last chart are critical timeline insights.
+In particular, our research revealed two specific weeks in the coming 3 months that will give us decisive information about the state and future of crypto markets.
+Want to find out the exact dates and weeks? Our research insights are available in this article (sign up required) in the restricted area of our website: Where and When Could Bitcoin Bottom: Price &amp; Timing Targets</t>
+  </si>
+  <si>
     <t>Bitcoin Price Prediction: Why $45,000 Could Be Next</t>
   </si>
   <si>
@@ -182,6 +606,35 @@
     <t>Says the number of active addresses has fallen and that the US economy is weak. Also states that support at the $50k level is crucial if the price is to stay above the $45k it's predicting a drop to.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+Bitcoin (BTC) Price Drop to $45,000 Might Be Inevitable, Report Says
+Victor Olanrewaju
+~4 minutes
+Amid growing volatility and downward pressure in the cryptocurrency market, a new Bitcoin (BTC) price prediction has surfaced. Digital asset investment firm 10x Research suggests that Bitcoin’s value could drop to $45,000.
+In the firm’s report, Markus Thielen, Head of Research, outlines several factors supporting this forecast. BeInCrypto further explores this possibility by analyzing key on-chain metrics in its assessment of Bitcoin’s current outlook.
+Key Reasons for the Adjustment in Bitcoin Forecast
+Bitcoin price currently trades below $55,000 despite hitting a new all-time high of $73,750 in March. According to 10x Research, this significant correction was expected due to changes in Bitcoin’s active addresses and broader market decisions. 
+    “Bitcoin addresses peaked in November 2023 and sharply declined after the first quarter of 2024. When the amount of Bitcoin held by short-term holders began to decrease in April, while long-term holders took advantage of high prices to exit, it suggested that a cycle top had been reached,” the research company explained.
+BeInCrypto reviewed Bitcoin’s active addresses data and found the analysis to be accurate. In November 2023, active addresses totaled around 1.20 million, and by March, the figure still exceeded 1 million.
+Read more: 7 Best Crypto Exchanges in the USA for Bitcoin (BTC) Trading
+Bitcoin Active Addresses.
+Bitcoin Active Addresses. Source: Santiment
+However, the number of active addresses has since fallen to 612,000, signaling that hundreds of thousands of participants have stopped engaging with the cryptocurrency. This sharp decline highlights reduced activity on the Bitcoin network, suggesting a weakening interest or participation in recent months.
+Apart from that, the report mentioned the $1 billion Bitcoin ETF outflows this week as a bearish sign. It also pinpointed the weak US economy and massive futures liquidation as other reasons that could drive BTC down to $45,000.
+Data from Glassnode shows that the Mayer Multiple seems to agree with the price decrease. Often used to identify speculative bubbles in Bitcoin, a Mayer Multiple reading above 1 typically signals a bullish market trend.
+Bitcoin Mayer Multiple.
+Bitcoin Mayer Multiple. Source: Glassnode
+When the metric falls below this threshold, the cryptocurrency becomes more vulnerable to a notable decline. At press time, the Mayer Multiple stands at 0.8, and Bitcoin’s price remains below the 200-day EMA, indicating that BTC could face another drop below $50,000.
+BTC Price Prediction: $50,000 Is Crucial
+According to the weekly BTC/USD chart, traders began this month around the same price levels seen in November 2021, just before the Bitcoin bear market of 2022. After Bitcoin’s value declined toward the end of 2021, it dropped to $36,500 in January 2022 when it lost support at $50,000.
+Currently, a similar support level exists around $50,000, and Bitcoin appears likely to test this level again. If this happens, BTC’s price could fall to $48,338, with a possibility of closing in on $45,000.
+Read more: Bitcoin (BTC) Price Prediction 2024/2025/2030
+Bitcoin Weekly Price Analysis.
+Bitcoin Weekly Analysis. Source: TradingView
+Failure to bounce from this level might lead Bitcoin down toward $40,000. However, this outcome might change if the Mayer Multiple rises above 1, signaling a potential restart of a bull market, which could push Bitcoin beyond its previous all-time high.</t>
+  </si>
+  <si>
     <t>Binance Square</t>
   </si>
   <si>
@@ -194,6 +647,30 @@
     <t>Is not very commanding in its language surrounding predictions. Says it could continue to drop in the next couple weeks, but then doesn't provide much of a prediction afetr that.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bitcoin's historical price data from 2011 to the present shows strong volatility, with alternating periods of growth and correction. The data table provides an overview of Bitcoin's performance by month over each year, from which certain trends can be drawn.
+Analysis:
+January &amp; February: Bitcoin tends to be bullish in the first two months of the year.
+On average, January increased by 9.78% and February increased by 16.6%.
+However, there are still years that record a decrease during this period (e.g. 2022).
+March: March was volatile, with both significant increases and decreases.
+On average, March increased by 11.8%, but there were also years of sharp declines such as 2020 (-24.9%).
+April - June: Bitcoin usually performs well in Q2.
+April and May had high average growth rates (34.7% and 20%).
+June was a mixed month, with both strong gains and losses.
+July - September: Q3 is usually a volatile period for Bitcoin.
+July and August had positive average growth rates, but September saw a downward trend.
+October - December: Q4 is usually a positive period for Bitcoin.
+October and November had positive average growth rates, especially November (15.5% and 40.7%).
+December was a mixed month, with both strong gains and losses.
+Bitcoin Price Prediction from September 2024 - December 2024:
+Based on historical analysis, some preliminary predictions can be made for Bitcoin price from September 2024 - December 2024:
+September 2024: Bitcoin is likely to continue its downtrend from August, but the drop may not be too large.
+October 2024: Bitcoin could start to recover and increase in price again, based on its history of positive average growth this month.
+November 2024: Bitcoin could continue its bullish momentum and post significant growth, based on its strong November growth history.
+December 2024: Bitcoin may continue to rise or correct downwards, depending on market sentiment and external factors.
+</t>
+  </si>
+  <si>
     <t>Bitcoin November 2024 Price Prediction: What Analysts Expect</t>
   </si>
   <si>
@@ -203,6 +680,38 @@
     <t>Says recent rallies hint at continued gains and that rising levels of BTC dominance and finance interest support that. Also says it has the opportunity to fall off a cliff if a support of $70k is reached.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+What to Expect from Bitcoin (BTC) in November 2024: Analysts Weigh In
+Victor Olanrewaju
+4–5 minutes
+Bitcoin (BTC) is set to end October, which initially started rough, on a strong note. Over the past 30 days, BTC has surged by 13%, prompting many analysts to predict that this upward momentum will persist into the Bitcoin November 2024 price outlook. 
+But what’s driving this optimistic outlook? This in-depth on-chain analysis sheds light on the underlying factors contributing to this bullish sentiment.
+Bitcoin Has Many Factors in Its Favor, Analysts Say
+For starters, digital asset research firm 10x Research opined that BTC might continue to move upwards. According to the firm’s prediction, Bitcoin’s rally to $73,000 this month is one reason the price can continue to rise.
+To support this point, 10x Research mentioned that whenever Bitcoin hits a six-month high, its price increases by at least 40% within the next three months. Based on this sentiment, Bitcoin’s price is likely to surpass $100,000 before the end of January 2025, which also means it could break its all-time high in November.
+Besides this, the firm, via its YouTube page, noted that catalysts, including the US elections surging Bitcoin ETF inflows, which run into billions of dollars over the last few weeks, could also play a role.
+Another factor that could affect Bitcoin’s November 2024 price performance is its dominance. As of this writing, Bitcoin’s dominance has increased to 60%.
+Read more: 5 Best Platforms To Buy Bitcoin Mining Stocks After 2024 Halving
+Bitcoin Dominance rises
+Bitcoin Dominance Chart. Source: TradingView
+High dominance in Bitcoin’s market presence suggests that it is leading the cryptocurrency space, particularly during periods of uncertainty. 
+This trend often indicates that investors are gravitating toward Bitcoin’s relative stability, opting for its perceived safety in contrast to the higher risks associated with altcoins.
+Interestingly, on-chain data from Glassnode also seem to agree with 10x Research’s prediction. According to Glassnode, the Pi Cycle Top, which shows the potential peak BTC might hit, shows that the cryptocurrency could rally to $115,903.
+Bitcoin potential price top
+Bitcoin Pi Cycle Top. Source: Glassnode
+If that is the case, Bitcoin’s November 2024 prediction for Bitcoin could see the price break above its all-time high. Michaël van de Poppe, founder of MN Trading, also seems to agree with the outlook. 
+    “I think $80,000 in November and $90,000-100,000 in December will help Altcoins to outperform strongly as yields are going to drop.” van de Poppe said in a post on X.
+BTC Price Prediction: $76,000 Minimum in November?
+On the daily chart, Bitcoin still has a bullish technical setup, suggesting that the price could rise well above $72,319. First off, the cryptocurrency has been able to surpass the major resistance at $71,473.
+Historically, when Bitcoin’s price gets rejected at this zone, it undergoes a notable correction. For instance, in April, when this happened, BTC dropped by 14% within some days. A similar thing happened in June, which caused Bitcoin’s price to drop by 22% in less than a month.
+Furthermore, the Relative Strength Index (RSI), which measures momentum, has continued to ascend. This movement is similar to how it moved during the run-up to the all-time high in March.
+Read more: Bitcoin (BTC) Price Prediction 2024/2025/2030
+Bitcoin price analysis november
+Bitcoin Daily Price Analysis. Source: TradingView
+Should this trend continue, BTC could rally above $76,000 in November. On the other hand, a decline below $70,000 in the short term could invalidate this prediction. In that scenario, BTC could decline to $66,448.</t>
+  </si>
+  <si>
     <t>KuCoin</t>
   </si>
   <si>
@@ -215,6 +724,78 @@
     <t>Says BTC crossed $100k and that was a big milestone. All experts it cites think it will go up to at least $124k by year's end.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+kucoin.com
+Bitcoin Price Prediction 2024 | KuCoin
+9–12 minutes
+Bitcoin continues its remarkable ascent in 2024, crossing the historic $100,000 milestone and sparking predictions that it could surpass $150,000 by year-end. Major institutions and industry experts are bullish, with forecasts ranging from six-figure prices to projections of $1 million or more in the coming years. Here's an in-depth look at the latest Bitcoin price predictions and the key factors driving this bullish sentiment.
+Quick Take
+    Bitcoin crossed $100,000 for the first time on Dec. 5, reaching an all-time high of $103,800.
+    ARK Invest, led by Cathie Wood, predicts a minimum price of $124,000 by the end of 2024, driven by institutional adoption and strategic reserve considerations.
+    Market sentiment indicates a 10% chance of Bitcoin hitting $150,000 by year-end.
+    Decentralized prediction markets like Polymarket and Kalshi and technical analysts see $130,000 to $140,000 as achievable price targets in the coming months.
+Major Predictions for Bitcoin in 2024-25: How High Can BTC Price Go? 
+BTC/USDT price chart | Source: KuCoin
+Analysts and prediction platforms see Bitcoin breaking past $150,000 as likely, with a potential surge to $250,000 in the coming weeks and months. Here are some major predictions for Bitcoin’s value before the end of the year and into 2025: 
+1. ARK Invest’s $124,000 Target
+ARK Invest, led by Cathie Wood, maintains a bullish outlook for Bitcoin. Their latest research indicates a minimum price of $124,000 by December 2024, based on historical performance and the current halving cycle. “Bitcoin’s increasing integration into institutional portfolios signals strong momentum into 2025,” ARK concluded.
+Key factors include:
+    Growing institutional adoption, highlighted by Bitcoin ETFs and corporate investments.
+    Potential consideration by the U.S. government to include Bitcoin in its strategic reserves.
+2. Traders Eye $130,000–$140,000 Range
+Popular crypto analysts are optimistic about Bitcoin's next move.
+    Jelle, a well-known cryptocurrency trader, anticipates a bullish pennant breakout that could propel Bitcoin's price to approximately $130,000. This projection is based on technical analysis of current market patterns, suggesting a continuation of the upward trend.
+    Aksel Kibar, a Chartered Market Technician, identifies $137,000 as the next significant resistance level for Bitcoin. He considers the $100,000 mark to be more of a psychological barrier than a technical one, implying that surpassing it could lead to further gains.
+These predictions align with technical indicators that signal Bitcoin’s continued upward trajectory.
+Fibonacci Extensions: $154,250
+Technical analysts point to historical Fibonacci levels to forecast Bitcoin's next move.
+    Bitcoin recently broke the 1.618 Fibonacci extension at $101,562, setting the 2.618 level at $154,250 as the next milestone.
+3. Analyst Predictions for BTC Price
+    Ki Young Ju, CEO of CryptoQuant, predicts Bitcoin could rise to $146,000 by leveraging fresh capital inflows and growth in Bitcoin’s realized cap. Ju noted that Bitcoin’s realized cap growth pushed the ceiling price from $129,000 to $146,000 in just 30 days.
+    Tom Lee, at Fundstrat, predicts Bitcoin will hit $150,000 in 2024 and $250,000 by 2025, citing the halving cycle’s “sweet spot.” Lee emphasizes the compounding impact of supply reductions and strong market momentum, which historically drive post-halving price surges.
+Bernstein: $200,000 by Late 2025
+Bernstein analysts forecast Bitcoin reaching $200,000 by 2025, attributing their bullish outlook to:
+    Institutional adoption, with companies like BlackRock and MicroStrategy leading the charge.
+    Pro-crypto regulatory shifts, including Paul Atkins’ appointment as SEC chair under President Trump.
+4. Prediction Markets Target $128,000–$150,000
+Kalshi’s prediction for Bitcoin price | Source: Kalshi 
+Data from Kalshi, a leading prediction platform, shows that consensus estimates place Bitcoin’s year-end price at $128,000.
+    A notable 10% of participants predict BTC could exceed $150,000 by the end of 2024.
+    Over the past month, sentiment has grown increasingly bullish, with projected prices rising by $50,000.
+5. Hal Finney’s Long-Term Vision of BTC at $10M
+Bitcoin pioneer Hal Finney’s legendary prediction of $10 million per BTC remains a distant dream but has regained attention. Current market momentum and institutional support echo Finney’s early vision of Bitcoin as a global store of value.
+6. PlanB’s $1 Million Bitcoin Price Prediction
+PlanB’s BTC price forecast based on Bitcoin Stock-to-Flow (S2F) | Source: BitBo
+PlanB, the creator of the Bitcoin Stock-to-Flow (S2F) model, forecasts Bitcoin hitting $100,000 by the end of 2024 and reaching $500,000 to $1 million by 2025. The S2F model compares Bitcoin’s scarcity to assets like gold, emphasizing its deflationary nature and limited supply.
+PlanB’s model anticipates that as adoption grows and supply shrinks, Bitcoin will reach valuation levels comparable to global reserve assets like gold.
+Read more: Bitcoin Price Prediction 2024-25: Plan B Forecasts BTC at $1 Million by 2025
+Key Factors Driving Bitcoin’s Bull Run in 2024-25
+1. Rising Institutional Adoption Powered By Bitcoin ETFs 
+Bitcoin ETFs, approved by the SEC in early 2024, have attracted over $30 billion in inflows. BlackRock and Fidelity lead the charge, collectively holding 6% of Bitcoin’s market supply.
+    BlackRock’s IBIT ETF alone saw $31.74 billion in inflows, boosting confidence among retail and institutional investors.
+2. Regulatory Support From Trump’s Pro-Crypto Outlook 
+The pro-crypto stance of President-elect Donald Trump is another catalyst. Key initiatives include:
+    Plans for a U.S. national Bitcoin reserve.
+    Shifting crypto regulation to the Commodity Futures Trading Commission (CFTC).
+This shift has created a favorable regulatory environment, encouraging further adoption.
+3. 2024 Bitcoin Halving
+The April 2024 Bitcoin halving reduced mining rewards from 6.25 BTC to 3.125 BTC, tightening supply. Historically, halvings have preceded significant price surges, and this cycle appears no different.
+Read more: The History of Bitcoin Bull Runs and Crypto Market Cycles
+Challenges Ahead
+Despite the bullish momentum, Bitcoin faces potential hurdles:
+    Market Volatility: Bitcoin is known for its significant price swings, which can lead to sharp corrections even during bullish cycles. In 2021, Bitcoin experienced a sharp drop from $64,000 to below $30,000 within weeks due to profit-taking and fears of overvaluation.With Bitcoin’s rapid rise past $100,000, any speculative excess could trigger short-term sell-offs as traders lock in profits.
+    Regulatory Risks: While regulatory clarity has driven much of Bitcoin’s 2024 rally, any reversal or delay in pro-crypto policies could dampen sentiment. A shift in focus away from crypto-friendly initiatives by President-elect Donald Trump’s administration could create uncertainty. Delays in approving additional Bitcoin ETFs or sudden enforcement actions against major crypto firms could negatively impact Bitcoin and the overall crypto market’s performance. 
+    Macroeconomic Factors: Bitcoin’s appeal as a hedge against inflation and fiat devaluation could be tested by macroeconomic uncertainties. The Federal Reserve’s recent rate cuts have been favorable for risk assets, but unexpected rate hikes to combat inflation could pressure Bitcoin. Ongoing conflicts or economic sanctions can lead to sudden shifts in investor behavior, favoring traditional safe havens like gold over Bitcoin. A global economic slowdown could reduce liquidity, forcing investors to pull out of speculative assets, including Bitcoin.
+    Potential Black Swan Events: Unforeseen catastrophic events have previously disrupted the crypto market, and similar occurrences could pose risks in the future. For instance, the Terra (LUNA) crash in 2022 wiped out over $40 billion in value, triggering widespread liquidations across the crypto ecosystem. The FTX collapse, one of the largest crypto exchanges, caused a liquidity crisis and led to significant market-wide losses. Concerns over the stability of major crypto platforms, including custodial wallets and exchanges, could resurface. Hacks, security breaches, or mismanagement of large institutional Bitcoin holdings could erode investor trust. Sudden regulatory bans or unfavorable rulings in major economies, such as the U.S. or the EU, could spark panic selling.
+What’s Next for Bitcoin?
+Bitcoin’s price trajectory in 2024 is shaped by strong institutional adoption, favorable regulatory changes, and its post-halving supply dynamics. Analysts agree that six-figure prices are here to stay, with predictions pointing to $124,000–$250,000 by 2025.
+Bitcoin’s path to $150,000 is paved with optimism, but challenges remain. Analysts believe the combination of institutional adoption, regulatory clarity, and macroeconomic conditions will shape its trajectory.
+Whether Bitcoin ends 2024 at $124,000, $150,000, or beyond, one thing is clear: the crypto market’s flagship asset is poised for continued growth, making it a focal point for investors worldwide.
+Stay tuned to KuCoin News for the latest updates on Bitcoin and the broader crypto market!
+Disclaimer: The information on this page may have been obtained from third parties and does not necessarily reflect the views or opinions of KuCoin. This content is provided for general informational purposes only, without any representation or warranty of any kind, nor shall it be construed as financial or investment advice. KuCoin shall not be liable for any errors or omissions, or for any outcomes resulting from the use of this information. Investments in digital assets can be risky. Please carefully evaluate the risks of a product and your risk tolerance based on your own financial circumstances. For more information, please refer to our Terms of Use and Risk Disclosure.
+</t>
+  </si>
+  <si>
     <t>Yahoo Finance</t>
   </si>
   <si>
@@ -227,6 +808,19 @@
     <t>Says BTC's regaining of the $100k price point coinciding with inflation and CPI data releases sparks further optimism. Also likes long term outlooks.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+finance.yahoo.com
+Bitcoin Could Reach $300,000 in 2025, HashKey Survey Predicts Amid Growing Institutional Interest
+Ayesha Aziz
+3–4 minutes
+Bitcoin's price has attracted significant attention, with many analysts predicting substantial growth in 2025. A survey by HashKey Group, based in Hong Kong, revealed that 50% of respondents expect Bitcoin to surpass $300,000 this year, driven by increasing institutional adoption. Bitcoin recently reclaimed the $100,000 mark, coinciding with the release of inflation and CPI data, sparking further optimism.
+Geoff Kendrick, the Global Head of Digital Assets Research at Standard Chartered, forecasts Bitcoin could reach $200,000 by the end of 2025, thanks to factors like spot exchange-traded funds (ETFs) and more corporate treasury diversification. Similarly, ARK Invest's analysis highlights that 62% of Bitcoin’s circulating supply has remained stagnant for over a year, signaling long-term investor confidence. Historically, post-halving years for Bitcoin have yielded positive returns, suggesting 2025 could be a key year for the cryptocurrency.
+HashKey Group's research projects the total market capitalization of cryptocurrencies to rise from $3.64 trillion to $10 trillion by 2025, as technologies like security token offerings (STOs), ETFs, and central bank digital currencies (CBDCs) bring in new investments. Ethereum is also expected to see significant growth, with some analysts predicting its value could reach $8,000 by year-end. Ben El-Baz, Managing Director of HashKey Global, emphasizes Bitcoin’s decentralization and resistance to inflation, positioning it as a crucial tool for financial system diversification.
+Predictions from Bernstein’s analysts suggest Bitcoin could hit $200,000 in 2025, though they consider this estimate conservative. Arthur Hayes, CIO of Maelstrom Fund, anticipates a peak in Bitcoin’s market value between mid to late March 2025, linking it to a favorable liquidity environment. Institutional interest continues to grow, exemplified by MicroStrategy’s ongoing Bitcoin acquisitions and the increasing presence of crypto ETFs in mainstream financial markets.
+In the long term, Bitcoin's potential for growth remains high. VanEck predicts that Bitcoin could reach as much as $2.9 million by 2050 if the value of traditional reserve currencies declines and the cryptocurrency’s network scaling advances. Under more favorable conditions, Bitcoin could even exceed $52 million, according to their estimates.
+The crypto market is not without risks. Analysts caution that while long-term prospects appear strong, short-term volatility and overheated derivatives markets could affect the market shortly. Some countries are exploring the idea of using Bitcoin as a reserve asset, reflecting its growing role in global finance. Experts advise that potential investors conduct thorough research and carefully assess risks before entering the market.</t>
+  </si>
+  <si>
     <t>What to Expect from Bitcoin (BTC) Price in February 2025?</t>
   </si>
   <si>
@@ -236,6 +830,31 @@
     <t>Says the VDDM being at 1.22 is a good sign along with long-term holders being profitable. Says there's some risk if the price goes below a roughly $92k support.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+What to Expect from Bitcoin (BTC) Price in February 2025
+Aaryamann Shrivastava
+3–4 minutes
+Bitcoin’s price action has remained in a consolidation phase, which at first glance may seem bearish. However, this setup actually signals bullish potential. 
+The cryptocurrency has received strong backing from long-term holders (LTHs), a key cohort that typically influences major market moves. With this support, BTC appears primed for a rally.  
+Bitcoin Investor’s Resilience Is Key
+The Value Days Destroyed Multiple (VDDM) is a crucial indicator for tracking Bitcoin’s market trends. It compares short-term spending to yearly averages, with high values (above 1.4) indicating a heating market. Extreme values (over 2.9) have historically marked cycle peaks, signaling potential corrections.
+Currently, VDDM sits at 1.22, suggesting a different market structure than previous cycles.  
+Unlike past bull runs, Bitcoin’s spent coin volume remains relatively controlled despite reaching new all-time highs (ATHs). This signals a more sustainable rally, reducing the risk of sudden sell-offs. With no extreme spikes in VDDM, Bitcoin has room for further growth, supporting the argument for a continued uptrend in the near future.  
+Bitcoin VDD Multiple
+Bitcoin VDD Multiple. Source: Glassnode
+Bitcoin’s long-term holder profit and loss volumes provide another key insight into market momentum. The ratio between these two metrics remains significantly elevated, indicating that most LTHs are in profit. This pattern is characteristic of bull market phases, where minimal supply is held at a loss, reinforcing the ongoing accumulation trend.  
+As long-term holders continue to retain their BTC, selling pressure remains low. This behavior supports Bitcoin’s ability to maintain its bullish trajectory without major drawdowns. With limited LTH supply at a loss, the cryptocurrency is positioned for sustainable gains, increasing the likelihood of an extended upward move.  
+Bitcoin LTH Profit/Loss Ratio
+Bitcoin LTH Profit/Loss Ratio. Source: Glassnode
+BTC Price Prediction: New High Ahead
+Bitcoin’s price is currently setting up a Parabolic Curve pattern, a structure that historically precedes major rallies. Over the past year, BTC has established three bases, a key characteristic of this setup. The next phase of this formation suggests an impending breakout, which could drive the cryptocurrency significantly higher.  
+For confirmation, Bitcoin must close above $110,000, which would establish a new ATH. The Parabolic Curve pattern indicates a potential rally similar to previous base breaks, which theoretically could push BTC toward $185,661. However, a more practical and realistic target places BTC on track to reach $120,000 in the near term.  
+Bitcoin Price Analysis
+Bitcoin Price Analysis. Source: TradingView
+Currently, Bitcoin’s critical support level stands at $92,324, a price it has tested multiple times since mid-November 2024. Losing this support is unlikely unless selling pressure intensifies. However, if BTC breaks below this threshold, it could fall toward $85,000, invalidating the bullish outlook and delaying further gains.  </t>
+  </si>
+  <si>
     <t>What to Expect from Bitcoin (BTC) Price in March 2025</t>
   </si>
   <si>
@@ -245,6 +864,34 @@
     <t>Says big holders aren't trading as much and that RSI is signalling oversold conditions.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+What to Expect from Bitcoin (BTC) Price in March 2025
+Abiodun Oladokun
+3–4 minutes
+After spending most of February trading within a range, Bitcoin (BTC) has broken below the consolidation zone, slipping under $90,000 for the first time since November. The leading coin now trades at $88,956.
+This downturn signals growing bearish pressure, raising concerns that the decline could extend further into March.
+Range-Bound or Breakout? Experts Weigh In
+According to Brian, lead analyst at Santiment, Bitcoin whales continue to reduce their trading activity, increasing the likelihood of a further decline in the coin’s value.
+    “Bitcoin whales seem to have taken a bit of a breather and aren’t accumulating at the moment (mostly staying flat),” Brian told BeInCrypto.
+The decline in Bitcoin’s large holders’ netflow corroborates Brian’s position. According to IntoTheBlock, the metric has plummeted by over 600% in the past 30 days.
+Bitcoin Large Holders Netflow.
+Bitcoin Large Holders Netflow. Source: IntoTheBlock.
+Large holders refer to whale addresses that hold more than 0.1% of an asset’s circulating supply. Their netflow tracks the amount of coins they buy and sell over a specific period. 
+When it falls, these key investors are reducing their token holdings, signaling increased selling activity. This may exacerbate the downward pressure on BTC’s price as supply increases in the market. 
+For John Glover, Ledn’s Chief Investment Officer (CIO), BTC will likely remain range-bound between $89,000 and $108,000 in March. 
+    “From a technical perspective, BTC is following 1 of 2 paths. In the first place, there is a good potential for a dip to $89,000 or even $77,000 before the next rally. In the second, we have already seen the lows, and the next move will be higher, up to ~$130,000.  It’s impossible to predict which path we’re on, and short-term predictions are meaningless when intraweek/intra-month moves are dictated by news and, recently, by the actions of big players like Strategy. My personal view is that we remain stuck in a range of $89,000 to 108,000 in March,” Glover said. 
+Further, given President Donald Trump’s pro-crypto stance, some investors wonder how his policies might impact Bitcoin’s price in March. However, Glover believes that most of the “Trump effect” has already played out.
+    “The majority of the “Trump effect” has already been felt.  We know he is very supportive of digital assets and has set in motion his plans to streamline regulations associated with crypto.  I don’t think he is a major factor in the short run,” Glover stated.
+Bitcoin Nears Oversold Levels – Is a Rebound on the Horizon?
+Bitcoin may be oversold and ready for a rebound, as reflected by its Relative Strength Index (RSI) readings. At press time, this momentum indicator is downward at 31.16.
+The indicator measures an asset’s oversold and overbought market conditions. It ranges between 0 and 100, with values above 70 indicating that the asset is overbought and due for a decline. On the other hand, values below 30 suggest that the asset is oversold and may witness a rebound.
+BTC’s RSI reading suggests that it is nearing oversold territory. This hints at a possible rebound toward $92,325 if the selling pressure eases.
+Bitcoin Price Analysis.
+Bitcoin Price Analysis. Source: TradingView
+On the other hand, if this decline persists, the coin’s price could drop to $80,835.</t>
+  </si>
+  <si>
     <t>FXStreet</t>
   </si>
   <si>
@@ -257,6 +904,47 @@
     <t>Says there is an iminent price hike but also gives many reasons as to why there's fear in the market.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+fxstreet.com
+Bitcoin Price Prediction for April 2025: Coin Bureau CEO says BTC could repeat 360% breakout pattern from 2017
+Ibrahim Ajibade
+5–6 minutes
+Bitcoin price stabilized at the $83,400 mark on Monday, down 2% from the March opening price of $84,430. After posting 18% losses in February, BTC is on course to end March in red with another 2% haircut. Citing historical trends and critical on-chain data trends among US investors, CoinBureau CEO and ex-Goldman Sachs analyst Nic Puckrin makes bold predictions of a new BTC price all-time high in April 2025.
+    Question 1: Bitcoin has become increasingly correlated to US stocks, what does this mean for near-term price action?
+    Nic Puckrin: "A large proportion of Bitcoin investors weren’t around in 2017 – and for those that were, it feels like a different century because the crypto market moves so quickly.
+    For those who were watching the charts back then, though, Bitcoin’s current sideways consolidation pattern looks eerily similar to what we saw in fall 2017.
+    Back then, the leading crypto asset also spent several months consolidating around the $4,000 mark, before exploding some 360% from roughly $4,300 in October 2017 to its then all-time high of $19,800 in December.
+    And there’s a high chance we may see a similar trend playing out now, as long as Bitcoin manages to correct its recent divergence from the 2017 trading pattern.
+    This isn’t just speculation based on overlaying one chart over another.
+    The economic backdrop and sentiment look similar to 2017. Then, the sideways movement was driven by escalating fear, uncertainty and doubt (FUD) as China banned crypto initial coin offerings (ICOs) – the key driver of the 2017 bull run – and shut down all domestic crypto exchanges." 
+    Q2: Heading into April 2025, the Crypto Fear and Greed Index reads ‘Extreme Fear’. What are your insights on this?
+Nic Puckrin: Today, the global attitude to cryptocurrency is very different, yet the crypto Fear &amp; Greed index has only just rebounded from “Extreme Fear” amid concerns about the impact of US President Donald Trump’s tariffs on risk assets.
+The Libra meme coin fiasco, which cost investors $251 million in losses, hasn’t helped investor confidence, with several headlines calling the end of the bull market.
+Crypto Fear and Greed Index, March 31, 2025 | Source: CoinmarketCap
+Crypto Fear and Greed Index, March 31, 2025 | Source: CoinmarketCap
+And then there’s the monetary policy backdrop. Bitcoin tends to follow global liquidity cycles very closely (total money supply in the market). 
+During the 2017 cycle, we were seeing global liquidity ramping up; it peaked in January 2018, which also happened to mark the top of the previous cycle. In our current cycle, global liquidity is still increasing and all signs point to more of it flooding into the system (end of QT, China, Europe etc).
+These similarities in the macro backdrop give me confidence that BTC is highly likely to repeat the breakout pattern of 2017. 
+However, with Bitcoin now a much more stable asset, a 360% surge isn’t on the cards. I do, however, expect it to surpass its previous all-time high (ATH) of $109,354 (on January 20), likely hitting a new peak of around $150,000 during this cycle. 
+To do so, it must first break past a key resistance level at around $93,000, which is the 50% level from a high of around $109,000 on January 20 and a low of $76,000 on March 11. If Bitcoin does hit $93,000, this could create a Double Top pattern, which typically sees a rejection.
+    Q3: Considering the growing pushback against Trump’s Crypto Strategic Reserve proposal, what fundamental metrics could support this optimistic BTC price prediction?
+Nic Puckrin: The good news is that since the Federal Open Market Committee (FOMC) meeting on March 19, Bitcoin has been trading above its 200-day moving average – typically a bullish sign.
+It has also broken out of its three-month price downtrend and its RSI downtrend, which likely signals a shift in sentiment and might precede a stronger bounce in price. 
+Coinbase Premium Index, March 2025 | Source: CryptoQuant
+Coinbase Premium Index, March 2025 | Source: CryptoQuant
+Despite the pushback against Trump’s Crypto Strategic Reserve proposal, Bitcoin demand among  US Investors remains destiny. 
+CryptoQuant’s Coinbase Premium Index sloping upwards shows US investors are bullish enough to pay a premium for BTC on Coinbase over offshore exchanges. 
+Q4: What is your Bitcoin price forecast for April 2025?
+Nic Puckrin: The caveat here is that, in the very short term, we’re yet to see a pick-up in trading volume or 24-hour liquidations that would signal an imminent price surge.
+Daily exchange trading volume has, in fact, been dropping and currently sits at levels last seen in October 2024, 75% below the July peak of $132 billion, while liquidations remain low at around $250 million. This suggests BTC might struggle to break out of its holding pattern in the very near future.
+Bitcoin Price Forecast, April 2025 
+Bitcoin Price Forecast, April 2025 
+However, with Bitcoin market volatility recently hitting a six-month high, this could turn in a matter of hours if there’s a catalyst.
+It’s encouraging to see the price reacting far less to tariff news now than it did a few weeks earlier.
+If BTC can breach that $93,000 threshold, it could go flying to a new all-time high in a manner very much reminiscent of 2017.
+</t>
+  </si>
+  <si>
     <t>FinanceMagnates</t>
   </si>
   <si>
@@ -269,6 +957,315 @@
     <t>Provides many technical reasosn for why the author is bullish.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+financemagnates.com
+Bitcoin Price Prediction 2025, 2026, 2030. Experts BTC Forecast And Outlook (May 2025)
+Damian Chmiel
+40–51 minutes
+Bitcoin (BTC), the world’s largest cryptocurrency, has entered May 2025 with strong momentum and heightened investor attention. After a volatile start to the year, Bitcoin is trading near $95,000 – not far from its all-time high of about $109,000 set in January.
+The market has rebounded from a sharp spring drawdown, and analysts are now assessing where Bitcoin’s price could head next. In this May 2025 edition of our Bitcoin price prediction, we review the current price action, technical and on-chain trends, and a range of short-term and long-term forecasts.
+We also examine market sentiment – including the impact of newly launched Bitcoin exchange-traded funds (ETFs) – and consider the key factors that could drive prices higher or lower. The goal is a clear, objective outlook on Bitcoin’s trajectory in 2025, with insights grounded in data and expert analysis.
+Utip Advertisement
+This above is an advertisement by Utip
+Bitcoin’s Price in May 2025
+Bitcoin’s price in early May 2025 reflects a remarkable recovery and growth trend. The cryptocurrency started the year strong, but saw a “slump” in Q1 2025 before regaining its footing.
+In January, BTC briefly touched $109,000 – a new record high – before profit-taking and macroeconomic jitters triggered a pullback. By April 8, Bitcoin hit its lowest price of the year around $74,000, marking a nearly 30% drawdown from the peak. However, the decline proved short-lived. Within weeks, Bitcoin surged by 24% off that low, climbing back to the mid-$90,000s.
+As of the first week of May, BTC hovers near $95K, up roughly 15% from a month ago and well above key support levels established during the spring correction.
+Bitcoin price today. Source: CoinMarketCap.com
+This rebound has put Bitcoin firmly back in bull-market territory. Year-to-date, BTC is significantly higher – a testament to the post-halving cycle momentum and renewed institutional interest. Market observers note that Bitcoin has “shaken off” recent bearish signals and is showing resilience even in the face of mixed economic data. The $95,000 level has emerged as an important overhead resistance, with buyers and sellers battling for control around this zone.
+How High Can Bitcoin Go In May 2025? Seasonality
+From a seasonality perspective, May might not be Bitcoin’s strongest month historically, but it still delivers, on average, positive returns. Looking at the performance of the oldest cryptocurrency from 2013 to 2024, the average return for May was 7.4%, while the median return was just under 1%.
+Last year, May was especially favorable for Bitcoin, with the cryptocurrency climbing 11%. However, in the previous three years-from 2021 to 2023-a downward trend dominated this period. Of course, seasonality data should be treated more as an interesting tidbit than a reliable indicator of future results. We need to remember that, in markets, even the most robust statistics based on historical data never guarantee future performance.
+Bitcoin price seasonality patterns. Source: Coinglass.com
+Zooming out to the entire second quarter, Bitcoin’s average growth during this part of the year typically reaches 60%, with a median of 12%.
+Paul Howard, Wincent
+“There is no crystal ball in crypto but if we look at data in the options market it seems fair to me we have price upside to come and some short liquidations in the coming month,” said Paul Howard, Senior Director at Wincent. “I would like to christen the phrase, buy in May and go away. However I anticipate the biggest growth this month will be in the new TVL within the stablecoin segment. This could have net upside for DeFi in the coming months relative to Bitcoin alone."
+You may also like: Why Is Bitcoin Price Surging? BTC Taps 6-Week High, While Expert Predicts $200K Target in 2025
+Bitcoin Technical Analysis: May 2025 Outlook
+Based on my technical analysis of the Bitcoin to USD chart, the cryptocurrency is entering a new month of narrow consolidation below the resistance level around $95,000, which was established by March highs. Most importantly, the bounce from April lows located at the psychological support of $74,000 has ensured a return to the consolidation zone that has been forming since mid-November-between the support zone of $90,000-$92,000 and the resistance zone marked by historical maximums from December and January around $108,000-$109,000.
+It's within this range that Bitcoin once again has a chance to return to the all-time highs we observed at the beginning of this year. Other significant technical levels I currently identify on the daily chart include, on the resistance side, the $104,000 level established by local peaks from early December 2024, and the psychological six-figure level of $100,000 last tested at the end of February.
+Bitcoin technical analysis price chart. Source: Tradingview.com
+When looking at support levels, besides the mentioned zone around $90,000, the level of just under $89,000 will also be important-representing the lows from January 2025 and local peaks from the turn of March and April. Moving lower, the next levels are $82,000 (the minimums from late February/early March), $78,000 (the local March lows), and finally, the level I'm paying particular attention to, which in my opinion currently separates a bullish trend from a bearish one: the area around $74,000, which marks the early April minimums when Bitcoin was losing heavily alongside the American stock market, reacting to news regarding Donald Trump's tariffs.
+Overall, my outlook for Bitcoin in May remains rather bullish, similar to my stance for the entire year of 2025.
+Bitcoin Support and Resistance Levels (May 2025)
+Type
+Level
+Significance
+Resistance
+$109,000
+Historical maximum (December/January)
+Resistance
+$108,000
+Historical maximum (December/January)
+Resistance
+$104,000
+Local peaks (early December 2024)
+Resistance
+$100,000
+Psychological level (last tested late February)
+Resistance
+$95,000
+Current resistance (March highs)
+Support
+$90,000-$92,000
+Current consolidation support zone
+Support
+$89,000
+January 2025 lows &amp; March/April local peaks
+Support
+$82,000
+Late February/early March minimums
+Support
+$78,000
+Local March lows
+Support
+$74,000
+Early April minimums (bull/bear trend separator)
+Bitcoin On-Chain Analysis and Trends
+Bitcoin’s chart and blockchain data are both offering bullish signals as of May 2025. On the technical front, BTC/USD has reclaimed an uptrend after the spring correction. The price is trading comfortably above its major moving averages (including the 200-day moving average), indicating positive momentum. Short-term, traders highlight $95,000–$95,500 as a critical resistance zone, since Bitcoin has struggled to close above it in recent sessions. If bulls push the price beyond $95.5K with strong volume, it “opens the door” to a potential surge toward $100,000 and beyond. Notably, technical analysts see that Bitcoin’s recent consolidation under $100K has lacked excessive leverage – futures funding rates have been neutral or even slightly negative.
+Cautious positioning by traders (as indicated by negative funding rates) suggests the rally may have room to run, since there isn’t an overcrowded long trade despite the price strength. Key indicators like the Relative Strength Index (RSI) on the daily chart are in a healthy range (neither overbought nor oversold), reflecting stable momentum.
+All these technical factors point to a market that is primed for a breakout if buyers can decisively clear the $100K hurdle, while also being well-supported on dips.
+On-chain analytics reinforce the optimistic technical picture. Blockchain data shows that long-term holders and large investors – often dubbed “whales” – have been accumulating coins aggressively during the recent dip and recovery. According to Glassnode, wallets holding over 10,000 BTC (the biggest whales) showed an accumulation trend score near 1.0 in late April, indicating significant net buying.
+Likewise, entities holding 1,000–10,000 BTC were also steadily adding to their positions. This whale accumulation has been a key feature of the current rally, signaling conviction among Bitcoin’s most capitalized investors. “So far, large players have been buying into this rally,” Glassnode noted.
+At the same time, exchange flow data reveals a bullish supply trend: Bitcoin outflows from centralized exchanges hit a two-year high this season. In practice, heavy outflows mean investors are moving BTC into long-term storage (off exchanges), which often correlates with holding behavior rather than selling.
+Others also read: Will Bitcoin Reach $100K Again? Latest BTC Price Prediction for 2025 Says Yes
+Bitcoin Price Prediction 2025
+Wall Street institutions, crypto industry figures, and analysts have released a wide range of Bitcoin price forecasts for the remainder of 2025 and the second half of the decade. Notably, many established financial firms have turned increasingly bullish on Bitcoin’s long-term value, even as they acknowledge the potential for volatility.
+Standard Chartered, a major global bank, has one of the more optimistic mainstream forecasts. In an April analyst note, Standard Chartered’s head of digital assets research predicted Bitcoin could reach $200K by the end of 2025, with interim milestones of ~$100K in the coming months. The bank even outlined a glide path toward $500K in 2028 as adoption grows. This forecast rests on the view that as macroeconomic uncertainties drive strategic reallocations, Bitcoin will attract more capital as a non-US, non-fiat asset – effectively digital gold 2.0.
+Similarly bullish, VanEck – a large asset manager – has projected a “cycle apex” price of roughly $180,000 for Bitcoin in 2025. VanEck’s research team expects a dual-peak cycle, where BTC might hit ~$180K in a first-half rally, undergo a mid-year correction, then potentially set new highs in late 2025. They also foresee Ethereum at over $6,000 and other crypto assets surging alongside. These institutional forecasts suggest that six-figure Bitcoin prices are increasingly viewed as plausible in the near future.
+Bitcoin Price Prediction Table 2025, 2026, 2027, 2028, 2029, 2030
+Below is a summary of some high-profile predictions:
+Forecast Source
+End of 2025 Target
+Long-Term Target
+Standard Chartered (Geoff Kendrick)
+$120,000 by Q2 2025; $200,000 by end of 2025
+$500,000 by 2028 (multi-year path)
+VanEck (Matthew Sigel)
+Peak around $180,000 in 2025 (dual-cycle peak scenario)
+No official 2030 target (expects new highs beyond 2025; e.g. next cycle &gt;$400K)
+ARK Invest (Cathie Wood, et al.)
+– (Short-term not specified; bullish trajectory)
+$1.2 million base case by 2030; $2.4 million bull case; bear case ~$500K
+Finder.com Panel (avg of 50+ experts)
+$161,000 (average projection for end of 2025)
+$405,000 by 2030 (average forecast)
+Market Sentiment and ETF Impact
+Market sentiment around Bitcoin in May 2025 is notably upbeat, fueled in large part by the successful rollout of spot Bitcoin ETFs and growing mainstream acceptance. The launch of U.S. spot Bitcoin exchange-traded funds in late 2024 has proven to be a game-changer. Inflows into these Bitcoin investment products have been massive, providing a new conduit for institutional and retail money to enter the crypto market. For example, just this past week, U.S. spot Bitcoin ETFs saw roughly $591 million in net inflows in a single day, part of over $3.3 billion of inflows last week.
+BlackRock’s iShares Bitcoin Trust (IBIT) – one of the largest new ETFs – led the pack, raking in nearly $1 billion in daily purchases at the end of April. According to ETF analysts, this sudden rush of capital demonstrates how quickly investor demand can scale now that a regulated Bitcoin ETF exists.
+Beyond the ETF boom, overall market sentiment is in a phase of optimism, albeit with a cautious undertone. Crypto fear-and-greed indices in late April reached “Greed” levels as prices climbed, reflecting improving trader confidence. Social media chatter and Google Trends for Bitcoin have picked up again as the public takes notice of the approach toward $100K.
+What Could Drive Bitcoin Higher or Lower?
+Like any asset, Bitcoin’s price is ultimately driven by a mix of fundamental and speculative factors. As we look ahead, there are several key catalysts that could propel Bitcoin higher, as well as risks that might send it lower or increase volatility. Here are the main factors on each side:
+Upside Catalysts
+    Institutional Adoption:
+    Growing institutional exposure to BTC remains a strong bullish force. Firms like MicroStrategy paved the way, and with ETFs simplifying access, more hedge funds and pension plans may follow. ARK Invest’s $2.4M 2030 target assumes just a 6.5% portfolio allocation. Even now, asset manager or tech firm announcements often spark rallies.
+    Macro Tailwinds:
+    A softer economic outlook and potential Fed rate cuts could support liquidity-driven assets like Bitcoin. A weaker dollar and lower real yields make BTC more attractive as a store of value. Inflation fears or geopolitical stress may further push demand, especially from emerging markets—highlighted by ARK as a key long-term factor.
+    Halving &amp; Supply Dynamics:
+    The 2024 halving cut BTC issuance in half, historically leading to price appreciation. On-chain data shows rising cold storage and declining exchange supply, suggesting tightening float. Even modest demand increases could lift prices under these conditions.
+    Technological Progress:
+    Upgrades like Lightning Network expansion, smart contract integrations, and Layer-2 scaling improve Bitcoin’s utility. Growth in DeFi use cases, mining decentralization, and infrastructure gains also enhance the network's strength and appeal.
+    Market Psychology &amp; FOMO:
+    A decisive break above $100K could trigger retail FOMO, similar to past cycles. Positive feedback loops from price gains, media buzz, and increased participation could push BTC higher. Analysts are watching for signs of excess, such as funding spikes or parabolic moves.
+Key Risks to Bitcoin’s Outlook
+    Regulatory Setbacks:
+    Surprise crackdowns, tax policy shifts, or SEC actions could dent sentiment. Restrictions on banks or payment systems engaging with Bitcoin could limit adoption. Legal uncertainties remain a threat.
+    Macroeconomic Headwinds:
+    A surge in inflation or aggressive monetary tightening could weigh on risk assets. In a recession or crisis, investors may seek safety in cash or bonds. A strong dollar and higher rates reduce Bitcoin’s appeal.
+    Leverage and Market Structure:
+    Rapid gains can invite excessive leverage and lead to sharp corrections. Profit-taking by whales or liquidations of overleveraged positions can create volatile price swings.
+    Competition and Tech Risks:
+    Ethereum and newer chains may draw capital away. Technical flaws, security breaches, or scaling failures could damage trust in the network.
+    Geopolitical or Unforeseen Events:
+    Exchange hacks, mining crackdowns, or negative headlines could trigger fear-driven sell-offs. Whale sell pressure remains a risk, although accumulation has dominated in 2025 so far.
+“There are a growing number of ways to manage downside risk in digital assets, including a growing options market,” added Howard. “I have seen maybe as many as 10 new derivative exchange launches seeking funding in the past quarter, so these provide market-neutral institutions such as Wincent opportunities to manage volatility. In many cases, with the right structuring of these products in a portfolio, volatility quickly becomes an asset to fund performance.”
+Where Will Bitcoin Go in 2025?
+As of May 2025, Bitcoin stands at a pivotal juncture: the asset has achieved record highs and demonstrated resilience through a volatile economic climate, yet the year is far from over, and uncertainty still looms. The analysis above suggests a cautiously optimistic baseline – Bitcoin is on track to potentially cross the $100,000 mark and set new highs in 2025, barring any major adverse events.
+Short-term forecasts from market strategists point to a strong summer, with some expecting a climb to the $120K–$130K range in the next quarter. By the end of 2025, various models and experts envision Bitcoin at valuations well above current levels, often in the $150K–$200K area, and in some cases higher.
+These projections are underpinned by factors like rising institutional adoption, a favorable post-halving supply dynamic, and robust on-chain fundamentals that indicate long-term holders are in control. If those tailwinds persist, Bitcoin could very well finish 2025 near the upper end of forecasts – perhaps testing the mid-six-figure territory that seemed aspirational just a couple of years ago.
+In conclusion, “Where will Bitcoin go in 2025?” The data and expert opinions suggest an upward path, with Bitcoin likely pushing into new all-time highs. A realistic outlook sees Bitcoin potentially in the low-to-mid six figures by year-end, assuming no major disruptions – a development that would solidify its status as a leading asset class.
+Bitcoin Price News, FAQ
+How much will Bitcoin be worth by 2025?
+Forecasts for 2025 vary. Some analysts predict the btc price could reach $120,000 to $200,000, depending on market sentiment and macroeconomic factors. Institutions like Standard Chartered and Cathie Wood’s ARK Invest believe that if ETF inflows remain strong and the supply of bitcoin continues to tighten, the price of bitcoin may surge by year-end. However, short-term corrections are possible as the bitcoin market remains volatile.
+What will 1 Bitcoin be worth in 2040?
+There are no universally agreed-upon targets for 2040, but long-term projections often point to Bitcoin reaching $1 million per coin or more. These long-term bitcoin forecasts assume widespread adoption, limited issuance, and a shift in global store-of-value preferences. While speculative, some bulls argue that the bitcoin’s value will continue growing in line with expanding cryptocurrency market cap.
+What is the realistic Bitcoin price in 2030?
+According to multiple reports, the price prediction for bitcoin by 2030 ranges from $500,000 to over $1 million per coin. Cathie Wood’s team at ARK projects a base case of $1.2 million, assuming modest institutional allocation. Others suggest a more conservative price target around $400,000, depending on the average price of bitcoin over the next five years and Bitcoin’s role relative to altcoins and stablecoins.
+Will Bitcoin reach $10 million?
+Reaching $10 million would require exponential global adoption and a complete transformation of the financial system. While Bitcoin could rally under extreme scenarios, such a target goes well beyond even the most optimistic institutional models. For now, most analysts focus on whether bitcoin will go beyond $1M in the next five years to a decade.
+What are the latest BTC price predictions?
+Recent btc price predictions show a wide range. For 2025, targets range from $100K to $200K. For 2030 and beyond, long-term models, such as the exponential moving average or stock-to-flow, suggest that bitcoin to reach $1M is possible if demand grows. Monitoring bitcoin news, ETF inflows, and macroeconomic shifts can help investors stay updated on evolving projections.
+What’s the current bitcoin price and where can I track it?
+The current bitcoin price in May 2025 is around $95,000, but it fluctuates daily. You can track the btc price on major exchanges or through financial portals like CoinMarketCap or Bloomberg. Price changes often reflect the bitcoin’s price action, investor sentiment, and global events.
+How does the 50-day average affect Bitcoin's trend?
+The 50-day moving average is a key technical indicator for tracking bitcoin’s price movements. When BTC trades above it, it's often considered bullish. If the price of BTC breaks below this level, it may indicate short-term weakness or consolidation.
+Is Bitcoin a good investment in 2025?
+Bitcoin remains a high-risk, high-reward asset. If you plan to buy bitcoin, consider your risk tolerance and investment horizon. Many bitcoin bulls argue that BTC is undervalued in the long run. However, always seek investment advice and understand the volatility associated with bitcoins and the broader cryptocurrency market.
+What affects Bitcoin’s price history and future moves?
+Bitcoin’s price history shows cycles driven by halving events, market sentiment, and macroeconomic forces. Future price moves may depend on factors like interest rates, regulation, and altcoin competition. The bitcoin prediction landscape is constantly evolving, shaped by adoption trends, technology, and institutional participation.
+What role do altcoins like Solana and XRP play?
+Altcoins like Solana and XRP often influence investor behavior. When altcoin prices rise sharply, some capital may rotate out of Bitcoin. Conversely, BTC dominance can rise if xrp price or solana price weakens. Altcoin activity sometimes leads or lags behind BTC trends.
+How big is Bitcoin's market capitalization?
+As of May 2025, Bitcoin's market capitalization is over $1.8 trillion, making it the largest digital asset. The price of bitcoin directly impacts market cap, which is calculated by multiplying circulating supply with the btc price.
+Where could bitcoin go next?
+Bitcoin could hit new highs or face temporary corrections. Many analysts believe btc is expected to breach $100,000 soon, assuming current conditions hold. While the path is uncertain, several models suggest bitcoin would appreciate over the long term if adoption and scarcity trends persist.
+How often does Bitcoin hit new highs?
+Bitcoin often moves in 4-year cycles. Historically, BTC has reached a new high within 12–18 months post-halving. The current cycle, influenced by ETF inflows and tightening supply, could follow a similar trajectory—though external shocks could shift the timeline.
+Where can I view Bitcoin analytics?
+You can view bitcoin data on platforms like Glassnode, CryptoQuant, and CoinMetrics. These sites provide insight into on-chain activity, such as exchange flows, miner behavior, and long-term holder trends—all of which influence the bitcoin market outlook.
+Bitcoin (BTC), the world’s largest cryptocurrency, has entered May 2025 with strong momentum and heightened investor attention. After a volatile start to the year, Bitcoin is trading near $95,000 – not far from its all-time high of about $109,000 set in January.
+The market has rebounded from a sharp spring drawdown, and analysts are now assessing where Bitcoin’s price could head next. In this May 2025 edition of our Bitcoin price prediction, we review the current price action, technical and on-chain trends, and a range of short-term and long-term forecasts.
+We also examine market sentiment – including the impact of newly launched Bitcoin exchange-traded funds (ETFs) – and consider the key factors that could drive prices higher or lower. The goal is a clear, objective outlook on Bitcoin’s trajectory in 2025, with insights grounded in data and expert analysis.
+Utip Advertisement
+This above is an advertisement by Utip
+Bitcoin’s Price in May 2025
+Bitcoin’s price in early May 2025 reflects a remarkable recovery and growth trend. The cryptocurrency started the year strong, but saw a “slump” in Q1 2025 before regaining its footing.
+In January, BTC briefly touched $109,000 – a new record high – before profit-taking and macroeconomic jitters triggered a pullback. By April 8, Bitcoin hit its lowest price of the year around $74,000, marking a nearly 30% drawdown from the peak. However, the decline proved short-lived. Within weeks, Bitcoin surged by 24% off that low, climbing back to the mid-$90,000s.
+As of the first week of May, BTC hovers near $95K, up roughly 15% from a month ago and well above key support levels established during the spring correction.
+Bitcoin price today. Source: CoinMarketCap.com
+This rebound has put Bitcoin firmly back in bull-market territory. Year-to-date, BTC is significantly higher – a testament to the post-halving cycle momentum and renewed institutional interest. Market observers note that Bitcoin has “shaken off” recent bearish signals and is showing resilience even in the face of mixed economic data. The $95,000 level has emerged as an important overhead resistance, with buyers and sellers battling for control around this zone.
+How High Can Bitcoin Go In May 2025? Seasonality
+From a seasonality perspective, May might not be Bitcoin’s strongest month historically, but it still delivers, on average, positive returns. Looking at the performance of the oldest cryptocurrency from 2013 to 2024, the average return for May was 7.4%, while the median return was just under 1%.
+Last year, May was especially favorable for Bitcoin, with the cryptocurrency climbing 11%. However, in the previous three years-from 2021 to 2023-a downward trend dominated this period. Of course, seasonality data should be treated more as an interesting tidbit than a reliable indicator of future results. We need to remember that, in markets, even the most robust statistics based on historical data never guarantee future performance.
+Bitcoin price seasonality patterns. Source: Coinglass.com
+Zooming out to the entire second quarter, Bitcoin’s average growth during this part of the year typically reaches 60%, with a median of 12%.
+Paul Howard, Wincent
+“There is no crystal ball in crypto but if we look at data in the options market it seems fair to me we have price upside to come and some short liquidations in the coming month,” said Paul Howard, Senior Director at Wincent. “I would like to christen the phrase, buy in May and go away. However I anticipate the biggest growth this month will be in the new TVL within the stablecoin segment. This could have net upside for DeFi in the coming months relative to Bitcoin alone."
+You may also like: Why Is Bitcoin Price Surging? BTC Taps 6-Week High, While Expert Predicts $200K Target in 2025
+Bitcoin Technical Analysis: May 2025 Outlook
+Based on my technical analysis of the Bitcoin to USD chart, the cryptocurrency is entering a new month of narrow consolidation below the resistance level around $95,000, which was established by March highs. Most importantly, the bounce from April lows located at the psychological support of $74,000 has ensured a return to the consolidation zone that has been forming since mid-November-between the support zone of $90,000-$92,000 and the resistance zone marked by historical maximums from December and January around $108,000-$109,000.
+It's within this range that Bitcoin once again has a chance to return to the all-time highs we observed at the beginning of this year. Other significant technical levels I currently identify on the daily chart include, on the resistance side, the $104,000 level established by local peaks from early December 2024, and the psychological six-figure level of $100,000 last tested at the end of February.
+Bitcoin technical analysis price chart. Source: Tradingview.com
+When looking at support levels, besides the mentioned zone around $90,000, the level of just under $89,000 will also be important-representing the lows from January 2025 and local peaks from the turn of March and April. Moving lower, the next levels are $82,000 (the minimums from late February/early March), $78,000 (the local March lows), and finally, the level I'm paying particular attention to, which in my opinion currently separates a bullish trend from a bearish one: the area around $74,000, which marks the early April minimums when Bitcoin was losing heavily alongside the American stock market, reacting to news regarding Donald Trump's tariffs.
+Overall, my outlook for Bitcoin in May remains rather bullish, similar to my stance for the entire year of 2025.
+Bitcoin Support and Resistance Levels (May 2025)
+Type
+Level
+Significance
+Resistance
+$109,000
+Historical maximum (December/January)
+Resistance
+$108,000
+Historical maximum (December/January)
+Resistance
+$104,000
+Local peaks (early December 2024)
+Resistance
+$100,000
+Psychological level (last tested late February)
+Resistance
+$95,000
+Current resistance (March highs)
+Support
+$90,000-$92,000
+Current consolidation support zone
+Support
+$89,000
+January 2025 lows &amp; March/April local peaks
+Support
+$82,000
+Late February/early March minimums
+Support
+$78,000
+Local March lows
+Support
+$74,000
+Early April minimums (bull/bear trend separator)
+Bitcoin On-Chain Analysis and Trends
+Bitcoin’s chart and blockchain data are both offering bullish signals as of May 2025. On the technical front, BTC/USD has reclaimed an uptrend after the spring correction. The price is trading comfortably above its major moving averages (including the 200-day moving average), indicating positive momentum. Short-term, traders highlight $95,000–$95,500 as a critical resistance zone, since Bitcoin has struggled to close above it in recent sessions. If bulls push the price beyond $95.5K with strong volume, it “opens the door” to a potential surge toward $100,000 and beyond. Notably, technical analysts see that Bitcoin’s recent consolidation under $100K has lacked excessive leverage – futures funding rates have been neutral or even slightly negative.
+Cautious positioning by traders (as indicated by negative funding rates) suggests the rally may have room to run, since there isn’t an overcrowded long trade despite the price strength. Key indicators like the Relative Strength Index (RSI) on the daily chart are in a healthy range (neither overbought nor oversold), reflecting stable momentum.
+All these technical factors point to a market that is primed for a breakout if buyers can decisively clear the $100K hurdle, while also being well-supported on dips.
+On-chain analytics reinforce the optimistic technical picture. Blockchain data shows that long-term holders and large investors – often dubbed “whales” – have been accumulating coins aggressively during the recent dip and recovery. According to Glassnode, wallets holding over 10,000 BTC (the biggest whales) showed an accumulation trend score near 1.0 in late April, indicating significant net buying.
+Likewise, entities holding 1,000–10,000 BTC were also steadily adding to their positions. This whale accumulation has been a key feature of the current rally, signaling conviction among Bitcoin’s most capitalized investors. “So far, large players have been buying into this rally,” Glassnode noted.
+At the same time, exchange flow data reveals a bullish supply trend: Bitcoin outflows from centralized exchanges hit a two-year high this season. In practice, heavy outflows mean investors are moving BTC into long-term storage (off exchanges), which often correlates with holding behavior rather than selling.
+Others also read: Will Bitcoin Reach $100K Again? Latest BTC Price Prediction for 2025 Says Yes
+Bitcoin Price Prediction 2025
+Wall Street institutions, crypto industry figures, and analysts have released a wide range of Bitcoin price forecasts for the remainder of 2025 and the second half of the decade. Notably, many established financial firms have turned increasingly bullish on Bitcoin’s long-term value, even as they acknowledge the potential for volatility.
+Standard Chartered, a major global bank, has one of the more optimistic mainstream forecasts. In an April analyst note, Standard Chartered’s head of digital assets research predicted Bitcoin could reach $200K by the end of 2025, with interim milestones of ~$100K in the coming months. The bank even outlined a glide path toward $500K in 2028 as adoption grows. This forecast rests on the view that as macroeconomic uncertainties drive strategic reallocations, Bitcoin will attract more capital as a non-US, non-fiat asset – effectively digital gold 2.0.
+Similarly bullish, VanEck – a large asset manager – has projected a “cycle apex” price of roughly $180,000 for Bitcoin in 2025. VanEck’s research team expects a dual-peak cycle, where BTC might hit ~$180K in a first-half rally, undergo a mid-year correction, then potentially set new highs in late 2025. They also foresee Ethereum at over $6,000 and other crypto assets surging alongside. These institutional forecasts suggest that six-figure Bitcoin prices are increasingly viewed as plausible in the near future.
+Bitcoin Price Prediction Table 2025, 2026, 2027, 2028, 2029, 2030
+Below is a summary of some high-profile predictions:
+Forecast Source
+End of 2025 Target
+Long-Term Target
+Standard Chartered (Geoff Kendrick)
+$120,000 by Q2 2025; $200,000 by end of 2025
+$500,000 by 2028 (multi-year path)
+VanEck (Matthew Sigel)
+Peak around $180,000 in 2025 (dual-cycle peak scenario)
+No official 2030 target (expects new highs beyond 2025; e.g. next cycle &gt;$400K)
+ARK Invest (Cathie Wood, et al.)
+– (Short-term not specified; bullish trajectory)
+$1.2 million base case by 2030; $2.4 million bull case; bear case ~$500K
+Finder.com Panel (avg of 50+ experts)
+$161,000 (average projection for end of 2025)
+$405,000 by 2030 (average forecast)
+Market Sentiment and ETF Impact
+Market sentiment around Bitcoin in May 2025 is notably upbeat, fueled in large part by the successful rollout of spot Bitcoin ETFs and growing mainstream acceptance. The launch of U.S. spot Bitcoin exchange-traded funds in late 2024 has proven to be a game-changer. Inflows into these Bitcoin investment products have been massive, providing a new conduit for institutional and retail money to enter the crypto market. For example, just this past week, U.S. spot Bitcoin ETFs saw roughly $591 million in net inflows in a single day, part of over $3.3 billion of inflows last week.
+BlackRock’s iShares Bitcoin Trust (IBIT) – one of the largest new ETFs – led the pack, raking in nearly $1 billion in daily purchases at the end of April. According to ETF analysts, this sudden rush of capital demonstrates how quickly investor demand can scale now that a regulated Bitcoin ETF exists.
+Beyond the ETF boom, overall market sentiment is in a phase of optimism, albeit with a cautious undertone. Crypto fear-and-greed indices in late April reached “Greed” levels as prices climbed, reflecting improving trader confidence. Social media chatter and Google Trends for Bitcoin have picked up again as the public takes notice of the approach toward $100K.
+What Could Drive Bitcoin Higher or Lower?
+Like any asset, Bitcoin’s price is ultimately driven by a mix of fundamental and speculative factors. As we look ahead, there are several key catalysts that could propel Bitcoin higher, as well as risks that might send it lower or increase volatility. Here are the main factors on each side:
+Upside Catalysts
+    Institutional Adoption:
+    Growing institutional exposure to BTC remains a strong bullish force. Firms like MicroStrategy paved the way, and with ETFs simplifying access, more hedge funds and pension plans may follow. ARK Invest’s $2.4M 2030 target assumes just a 6.5% portfolio allocation. Even now, asset manager or tech firm announcements often spark rallies.
+    Macro Tailwinds:
+    A softer economic outlook and potential Fed rate cuts could support liquidity-driven assets like Bitcoin. A weaker dollar and lower real yields make BTC more attractive as a store of value. Inflation fears or geopolitical stress may further push demand, especially from emerging markets—highlighted by ARK as a key long-term factor.
+    Halving &amp; Supply Dynamics:
+    The 2024 halving cut BTC issuance in half, historically leading to price appreciation. On-chain data shows rising cold storage and declining exchange supply, suggesting tightening float. Even modest demand increases could lift prices under these conditions.
+    Technological Progress:
+    Upgrades like Lightning Network expansion, smart contract integrations, and Layer-2 scaling improve Bitcoin’s utility. Growth in DeFi use cases, mining decentralization, and infrastructure gains also enhance the network's strength and appeal.
+    Market Psychology &amp; FOMO:
+    A decisive break above $100K could trigger retail FOMO, similar to past cycles. Positive feedback loops from price gains, media buzz, and increased participation could push BTC higher. Analysts are watching for signs of excess, such as funding spikes or parabolic moves.
+Key Risks to Bitcoin’s Outlook
+    Regulatory Setbacks:
+    Surprise crackdowns, tax policy shifts, or SEC actions could dent sentiment. Restrictions on banks or payment systems engaging with Bitcoin could limit adoption. Legal uncertainties remain a threat.
+    Macroeconomic Headwinds:
+    A surge in inflation or aggressive monetary tightening could weigh on risk assets. In a recession or crisis, investors may seek safety in cash or bonds. A strong dollar and higher rates reduce Bitcoin’s appeal.
+    Leverage and Market Structure:
+    Rapid gains can invite excessive leverage and lead to sharp corrections. Profit-taking by whales or liquidations of overleveraged positions can create volatile price swings.
+    Competition and Tech Risks:
+    Ethereum and newer chains may draw capital away. Technical flaws, security breaches, or scaling failures could damage trust in the network.
+    Geopolitical or Unforeseen Events:
+    Exchange hacks, mining crackdowns, or negative headlines could trigger fear-driven sell-offs. Whale sell pressure remains a risk, although accumulation has dominated in 2025 so far.
+“There are a growing number of ways to manage downside risk in digital assets, including a growing options market,” added Howard. “I have seen maybe as many as 10 new derivative exchange launches seeking funding in the past quarter, so these provide market-neutral institutions such as Wincent opportunities to manage volatility. In many cases, with the right structuring of these products in a portfolio, volatility quickly becomes an asset to fund performance.”
+Where Will Bitcoin Go in 2025?
+As of May 2025, Bitcoin stands at a pivotal juncture: the asset has achieved record highs and demonstrated resilience through a volatile economic climate, yet the year is far from over, and uncertainty still looms. The analysis above suggests a cautiously optimistic baseline – Bitcoin is on track to potentially cross the $100,000 mark and set new highs in 2025, barring any major adverse events.
+Short-term forecasts from market strategists point to a strong summer, with some expecting a climb to the $120K–$130K range in the next quarter. By the end of 2025, various models and experts envision Bitcoin at valuations well above current levels, often in the $150K–$200K area, and in some cases higher.
+These projections are underpinned by factors like rising institutional adoption, a favorable post-halving supply dynamic, and robust on-chain fundamentals that indicate long-term holders are in control. If those tailwinds persist, Bitcoin could very well finish 2025 near the upper end of forecasts – perhaps testing the mid-six-figure territory that seemed aspirational just a couple of years ago.
+In conclusion, “Where will Bitcoin go in 2025?” The data and expert opinions suggest an upward path, with Bitcoin likely pushing into new all-time highs. A realistic outlook sees Bitcoin potentially in the low-to-mid six figures by year-end, assuming no major disruptions – a development that would solidify its status as a leading asset class.
+Bitcoin Price News, FAQ
+How much will Bitcoin be worth by 2025?
+Forecasts for 2025 vary. Some analysts predict the btc price could reach $120,000 to $200,000, depending on market sentiment and macroeconomic factors. Institutions like Standard Chartered and Cathie Wood’s ARK Invest believe that if ETF inflows remain strong and the supply of bitcoin continues to tighten, the price of bitcoin may surge by year-end. However, short-term corrections are possible as the bitcoin market remains volatile.
+What will 1 Bitcoin be worth in 2040?
+There are no universally agreed-upon targets for 2040, but long-term projections often point to Bitcoin reaching $1 million per coin or more. These long-term bitcoin forecasts assume widespread adoption, limited issuance, and a shift in global store-of-value preferences. While speculative, some bulls argue that the bitcoin’s value will continue growing in line with expanding cryptocurrency market cap.
+What is the realistic Bitcoin price in 2030?
+According to multiple reports, the price prediction for bitcoin by 2030 ranges from $500,000 to over $1 million per coin. Cathie Wood’s team at ARK projects a base case of $1.2 million, assuming modest institutional allocation. Others suggest a more conservative price target around $400,000, depending on the average price of bitcoin over the next five years and Bitcoin’s role relative to altcoins and stablecoins.
+Will Bitcoin reach $10 million?
+Reaching $10 million would require exponential global adoption and a complete transformation of the financial system. While Bitcoin could rally under extreme scenarios, such a target goes well beyond even the most optimistic institutional models. For now, most analysts focus on whether bitcoin will go beyond $1M in the next five years to a decade.
+What are the latest BTC price predictions?
+Recent btc price predictions show a wide range. For 2025, targets range from $100K to $200K. For 2030 and beyond, long-term models, such as the exponential moving average or stock-to-flow, suggest that bitcoin to reach $1M is possible if demand grows. Monitoring bitcoin news, ETF inflows, and macroeconomic shifts can help investors stay updated on evolving projections.
+What’s the current bitcoin price and where can I track it?
+The current bitcoin price in May 2025 is around $95,000, but it fluctuates daily. You can track the btc price on major exchanges or through financial portals like CoinMarketCap or Bloomberg. Price changes often reflect the bitcoin’s price action, investor sentiment, and global events.
+How does the 50-day average affect Bitcoin's trend?
+The 50-day moving average is a key technical indicator for tracking bitcoin’s price movements. When BTC trades above it, it's often considered bullish. If the price of BTC breaks below this level, it may indicate short-term weakness or consolidation.
+Is Bitcoin a good investment in 2025?
+Bitcoin remains a high-risk, high-reward asset. If you plan to buy bitcoin, consider your risk tolerance and investment horizon. Many bitcoin bulls argue that BTC is undervalued in the long run. However, always seek investment advice and understand the volatility associated with bitcoins and the broader cryptocurrency market.
+What affects Bitcoin’s price history and future moves?
+Bitcoin’s price history shows cycles driven by halving events, market sentiment, and macroeconomic forces. Future price moves may depend on factors like interest rates, regulation, and altcoin competition. The bitcoin prediction landscape is constantly evolving, shaped by adoption trends, technology, and institutional participation.
+What role do altcoins like Solana and XRP play?
+Altcoins like Solana and XRP often influence investor behavior. When altcoin prices rise sharply, some capital may rotate out of Bitcoin. Conversely, BTC dominance can rise if xrp price or solana price weakens. Altcoin activity sometimes leads or lags behind BTC trends.
+How big is Bitcoin's market capitalization?
+As of May 2025, Bitcoin's market capitalization is over $1.8 trillion, making it the largest digital asset. The price of bitcoin directly impacts market cap, which is calculated by multiplying circulating supply with the btc price.
+Where could bitcoin go next?
+Bitcoin could hit new highs or face temporary corrections. Many analysts believe btc is expected to breach $100,000 soon, assuming current conditions hold. While the path is uncertain, several models suggest bitcoin would appreciate over the long term if adoption and scarcity trends persist.
+How often does Bitcoin hit new highs?
+Bitcoin often moves in 4-year cycles. Historically, BTC has reached a new high within 12–18 months post-halving. The current cycle, influenced by ETF inflows and tightening supply, could follow a similar trajectory—though external shocks could shift the timeline.
+Where can I view Bitcoin analytics?
+You can view bitcoin data on platforms like Glassnode, CryptoQuant, and CoinMetrics. These sites provide insight into on-chain activity, such as exchange flows, miner behavior, and long-term holder trends—all of which influence the bitcoin market outlook.</t>
+  </si>
+  <si>
     <t>CCN</t>
   </si>
   <si>
@@ -281,6 +1278,83 @@
     <t>Doesn't provide any sentiment. If anything, it seems to be trying to argue with itself.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+ccn.com
+The Biggest Crypto Predictions for June 2025
+10–12 minutes
+Key Takeaways
+    Bitcoin could climb toward $120,000 if whale accumulation continues and the price holds above $108,000.
+    Ethereum may rally to $3,069, supported by strong on-chain buying pressure and a confirmed bull flag pattern.
+    XRP might drop to $1.94 amid bearish momentum, unless rising adoption triggers demand for the cryptocurrency..
+Out of the top five cryptocurrencies, only Bitcoin (BTC) managed to hit a new all-time high in May, living up to some of the boldest crypto predictions made ahead of the month.
+While BTC stole the spotlight, Ethereum (ETH) quietly delivered its strongest monthly close of the year. Over the past 30 days, ETH has surged more than 50%, even though it has yet to reclaim $3,000.
+XRP, on the other hand, hasn’t kept up. Despite outperforming many altcoins in late 2024 and early 2025, the token has remained stuck in a tight range. Throughout May, XRP failed to retest the $3 mark, raising the question: could June bring a breakout?
+In this analysis, CCN evaluates the biggest crypto predictions for the month ahead, focusing on the top three cryptos. Here is how market sentiment, technical setups, and fundamentals could impact their prices.
+Bitcoin (BTC)
+The biggest crypto predictions for 2025 would be incomplete without the flagship cryptocurrency, Bitcoin. On May 22, Bitcoin price hit a new all-time high of $111,814.
+While it has retraced to $107,780 at press time, it does not appear that BTC will experience a prolonged correction.
+To start with, CCN looked at the accumulation trend score. This metric checks whether large entities are accumulating more coins on-chain or distributing the majority.
+It ranges from zero to 1. Values close to 1 indicate notable accumulation, which could drive prices higher. On the other hand, when the accumulation trend score is close to zero, it means there is high selling pressure.
+For instance, in April, when BTC’s accumulation trend score was 0.19, the price fell to $76,270.
+According to Glassnode, the metric currently sits at $0.88, indicating that, despite some profit-taking, accumulation still outweighs distribution.
+accumulation surpasses distribution
+BTC Accumulation Trend Score | Credit: Glassnode
+If sustained, then Bitcoin price prediction for June could see it fail to slide below $100,000. This development also aligns with Santiment’s recent update.
+According to the on-chain analytics platform, Bitcoin whales holding between 100 and 1,000 BTC have snapped up 122,330 coins in the last six weeks alone.
+Historically, this cohort has emerged as one of the most influential forces among all investor groups.
+Their recent accumulation indicates rising buying pressure, which could push Bitcoin even higher in the near term.
+Despite the prevailing bullish sentiment, analysts at crypto derivatives exchange Bitunix are urging caution.
+In a conversation with CCN, they warned that a decisive breakdown below the critical $108,000 support level could spell trouble for Bitcoin
+    “BTC’s short-term pressure is around $110,800, where most of the past rebounds have stopped, and which is the core of the war between the bulls and the shorts. Support at $108,000 is the main long defense zone in the past two days. If it breaks down, it may trigger profit-taking pressure and turn into a short bias structure,” The Bitunix analytics highlighted.
+From a technical point of view, the daily chart shows that Bitcoin hit a new high after breaking above the upper trendline of a descending triangle. As of this writing, the coin is still above that point with a golden cross backing the upswing.
+For context, a golden cross occurs when a shorter Exponential Moving Average (EMA) crosses above a longer one. At press time, the 20 EMA (blue) had crossed above the 50 EMA (yellow), reinforcing the case for a potential uptrend.
+As long as this trend holds, BTC might retest $111,810 in June. If successful, this could set the stage for the next point of interest positioned between $116,000 and $120,000.
+Bitcoin price analysis prediction June 2025
+BTC/USD Daily Chart | Credit: TradingView
+However, traders might need to watch out. If distribution outpaces accumulation, this prediction might not come to pass. Macroeconomic factors could also impact the coin’s price action.
+Should this happen and selling pressure increases with a lot of BTC sent to exchanges, the price prediction for June could see it slide below $100,000.
+Ethereum (ETH)
+Ethereum’s impressive rally this month secures its spot in our biggest crypto predictions for June.
+Thanks to the recent price increase, on-chain data now shows that 67% of ETH holders are in profit, significantly higher than the percentage recorded back in April.
+At press time, Ethereum’s price is trading at its highest level in three months. From an on-chain perspective, it does not seem like the cryptocurrency is ready to give up those gains.
+One reason for this is the signals noticed via the In/Out of Money Around Price (IOMAP). Using the volume of coins in unrealized profits or losses, the IOMAP spots support and resistance.
+Typically, the higher the volume in the green region, the stronger the support. On the flip side, when the cluster “out of the money” is larger, it indicates resistance.
+Based on IntoTheBlock’s data, Ethereum’s strongest support zone lies between $2,316 and $2,402. At this range, roughly 2.59 million addresses accumulated over 64 million ETH positions now sitting comfortably in profit.
+Furthermore, this volume exceeds the combined amount acquired between $2,731 and $3,137, suggesting that ETH may not encounter heavy selling pressure as it climbs.
+ETH price support
+ETH In/Out of Money Around Price | Credit: IntoTheBlock
+Therefore, if buying pressure continues to build, Ethereum’s price could break past the $3,000 barrier in June 2025. Still, to validate this outlook, it is crucial to assess the price action from a technical perspective.
+On the daily chart. CCN observed that ETH has formed a bull flag, which is a bullish pattern. The pattern begins with a sharp upswing forming the flagpole.
+Later on, as the price moves sideways, it forms the flag. Once the price surges above the upper trendline of the flag, it validates the breakout.
+As seen below, Ethereum’s price is flirting with the flag’s upper trendline. In addition, the Money Flow Index (MFI) reading has continued to climb, indicating rising buying pressure.
+Ethereum price analysis June 2025
+ETH/USD Daily Chart | Credit: TradingView
+If the trend continues into next month, ETH’s price might hit $3,069 near the 0.618 golden ratio. Crypto analyst Michaël van de Poppe also seems to agree with this thesis, noting that the green candlestick on the ETH/USD monthly chart is not bearish.
+On the contrary, this prediction might be invalidated if selling pressure outpaces the buying volume.
+In that scenario, the cryptocurrency’s value could drop to $2,426. In a highly bearish case, it might slide to $2,028.
+XRP
+Unlike BTC and ETH, XRP’s technical setup lacks a clear signal for a breakout to new highs. On the daily chart, the altcoin is trading within a symmetrical triangle, a pattern formed by converging trendlines of equal slope.
+The upper trendline acts as resistance, while the lower trendline provides support. This formation indicates market indecision, as bulls and bears battle for control, typically resulting in a period of price consolidation.
+However, the Moving Average Convergence Divergence (MACD) reveals that XRP bears seem to have the upper hand.
+From the chart below, the MACD reading has turned negative, indicating bearish momentum.
+Also, the 12 EMA (blue) has crossed below the 26 EMA (orange), indicating a bearish crossover.
+Should this position remain the same as June approaches, then XRP’s price could drop below the $2.28 support.
+If the bearish scenario plays out, XRP’s market value could slip to $1.94. However, broader adoption might challenge this outlook.
+altcoin analysis June 2025
+XRP/USD Daily Chart | Credit: TradingView
+Take VivoPower International, for example. The energy solutions firm recently announced a $121 million private share placement, with plans to deploy the funds into a digital asset treasury strategy focused on XRP.
+    “As long-term holder of XRP myself, we all share a common vision and objectives with regards to how a publicly listed XRP-focused treasury company can be scaled for the benefit of the XRP community and VivoPower stakeholders alike,” Executive Chairman of VivoPower, Kevin Chin, said about the development.
+If this move drives buying pressure, XRP’s role in June’s biggest crypto predictions could change, potentially sending the price surging toward $3.40.
+The information provided in this article is for informational purposes only. It is not intended to be, nor should it be construed as, financial advice. We do not make any warranties regarding the completeness, reliability, or accuracy of this information. All investments involve risk, and past performance does not guarantee future results. We recommend consulting a financial advisor before making any investment decisions.
+Victor Olanrewaju
+Victor Olanrewaju is a crypto analyst and reporter at CCN with deep roots in on-chain research and technical analysis. His crypto journey began in 2017, but it was the 2020 Uniswap airdrop that sparked a full-time pivot into the space.
+With a foundation in copywriting, Victor honed his craft creating high-converting content for leading crypto brokers — most notably an XRP price prediction that ranked #1 on Google during the 2021 bull run.
+He later joined AMBCrypto in 2022, where he combined storytelling with technical and on-chain analysis to cover key market narratives.
+In 2024, he expanded his expertise at BeInCrypto, collaborating with analysts and using tools like Glassnode, Santiment, and IntoTheBlock to break down Bitcoin and altcoin trends.
+At CCN, Victor covers the top cryptocurrencies, memecoins, macro shifts, blending real-time insights with deep-dive metrics.
+He holds a Bachelor’s degree in Physics from the University of Ibadan, equipping him to simplify complex data for a wide audience. Follow his work or connect on LinkedIn or X.</t>
+  </si>
+  <si>
     <t>Bitcoin price prediction for 2025, 2030 and 2035: July 2025 report</t>
   </si>
   <si>
@@ -290,6 +1364,77 @@
     <t>Cites a bunch of experts all saying the price should continue to go up.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+yahoo.com
+Bitcoin price prediction for 2025, 2030 and 2035: July 2025 report
+Richard Laycock for Finder.com
+12–15 minutes
+Bitcoin (BTC) price prediction 2025, 2030 and 2035: July 2025 report 
+For its June bitcoin (BTC) survey, Finder.com analyzed expert predictions from a panel of 24 crypto industry specialists who shared their thoughts on how bitcoin will perform through 2035.
+All prices in this report are denominated in U.S. dollars.
+On average, the panelists think bitcoin (BTC) will be worth $145,167 by the end of 2025, up from the $135,048 predicted in our April 2025 report.
+Looking further ahead, they see the price of BTC rising to $458,647 by year-end 2030 and $1.02 million by the close of 2035.
+Key Insights: July 2025 predictions
+    2025 price forecast: The average year-end prediction for bitcoin is $145,167.
+    Peak and trough predictions: The end of 2025 could be rocky, with the average high prediction for BTC being $162,353, while the average low point is forecast at just $87,618.
+    Long-term projections: The panel sees BTC reaching new heights and being worth $458,647 by 2030 and $1.02 million by 2035.
+    Time to buy BTC: The majority of the panel (61%) say that bitcoin is currently a buy.
+    Panel consensus on bitcoin being a value: A slight majority of the panel (52%) say bitcoin is currently underpriced.
+Bitcoin price predictions for 2025, 2030 and 2035
+Bitcoin’s price is expected to rise to $145,167 by year-end 2025, according to the average prediction from Finder’s panelists.
+The most bullish panelists see BTC trading at $250,000 by the end of 2025, while the most bearish panelist sees it dropping well below where it is now, reaching $70,000 by the end of the year.
+The panelists also predict BTC will hit $458,647 by 2030 and $1.02 million by 2035. The panel is slightly more bullish than last quarter, when the long-term prediction came in at $452,714 for 2030 and $833,000 for 2035.
+Bitcoin (BTC) price predictions for year-end 2025, 2030 and 2035. - Finder.com
+Bitcoin (BTC) price predictions for year-end 2025, 2030 and 2035. - Finder.com
+Martin Froehler, the CEO of Morpher, is the most bullish panel member and expects BTC to close out 2025 at $250,000, buoyed by institutional demand. “Corporate and institutional demand is not slowing down while retail is still absent and nation state adoption is just getting started,” he said.
+Joseph Raczynski, a Futurist at JT Consulting &amp; Media, believes we’ll see BTC reach $240,000 as institutions and nations see the value of BTC. “Uncertainty has taken center stage, and bitcoin’s no longer playing the ‘risk-on’ role — it’s more of a brooding philosopher these days. So, perhaps the crowd could panic, where bitcoin could surge, is by the hands of savvy states and corporations quietly stacking bitcoin reserves,” he said.
+Josh Fraser, the cofounder of Origin Protocol, is similarly bullish with his prediction of $230,000 as people throw their money into hard assets. “We’re currently seeing a flight to hard assets, including bitcoin,” he said. “As countries continue to print fiat currency at unsustainable rates, people will find alternative ways to store value. Gold has been a primary store of value for hundreds of years, and bitcoin now competes as a better version of gold. When bitcoin reaches the same adoption as gold, BTC will be priced at roughly $1.15 million. Over the long term, I anticipate that bitcoin adoption will surpass that of gold.”
+John Hawkins, senior lecturer at the University of Canberra and resident crypto skeptic, gives one of the lowest predictions at $80,000 and says BTC is being propped up by the current administration. “BTC, and crypto in general, is being propped up by the Trump administration, ironically given its initial promotion as an alternative to government-backed currencies and support from libertarians,” he said. “But it still lacks any fundamental value, and after 16 years, it has still failed to meet its initial aspiration to be a common means of payment. It remains a speculative bubble.”
+How high and low will BTC go in 2025?
+The average peak price the panelists predict bitcoin will hit at some point in 2025 is $162,353, with some predicting it will climb as high as $250,000.
+Data chart showing how high and low will BTC go in 2025. - Finder.com
+Data chart showing how high and low will BTC go in 2025. - Finder.com
+The average lowest price the panelists predict bitcoin will hit at some point in 2025 is $87,618, with some predicting it will fall as low as $70,000.
+Data chart showing projections for lowest BTC price for the remainder of 2025. - Finder.com
+Data chart showing projections for lowest BTC price for the remainder of 2025. - Finder.com
+Ben Ritchie, the managing director of Alpha Node Global, is also quite bullish, as he thinks we’ll see BTC crest $180,000 as it is showing itself to be a store of value during periods of geopolitical and macroeconomic stress. “Our bitcoin price forecast remains at $160,000, despite ongoing uncertainties related to tariff tensions, the conflict in the Middle East, and the Federal Reserve’s tight monetary policy,” he says. “Much like gold, which continues to trade near all-time highs, bitcoin is increasingly demonstrating its role as a store of value during periods of geopolitical and macroeconomic stress. While we acknowledge that these headwinds are significant, we view them as temporary market noise. As such, we maintain a bull case scenario of up to $180,000 for bitcoin within the year.”
+Ruadhan O, founder of Seasonal Tokens, sees BTC possibly hitting $190,000 in 2025 and hitting a new all-time high after demonstrating its resilience throughout a chaotic start to 2025. “The support at $100K was strong enough to hold despite the outbreak of war between Israel and Iran and the subsequent U.S. involvement,” he says. “This suggests that it’s unlikely to break, which means that the price will probably break out to the upside and reach new all-time highs in the coming months.”
+Mitesh Shah, the founder and CEO of Omnia Markets, sees the potential of future Fed Rate cuts, coupled with other BTC technicals, inflating bitcoin’s value in 2025 as it heads toward his prediction of $170,000. “My $170,000 price forecast for bitcoin is based on strong institutional demand colliding with a historic supply squeeze and a supportive macroeconomic outlook,” he says. “Relentless inflows into spot ETFs (exchange-traded funds), with products like IBIT alone attracting over $13.7 billion this year, are absorbing a shrinking available supply, as on-chain data shows nearly 70% of bitcoin has not moved in over a year. Key valuation metrics like the MVRV Z-Score, currently at 2.4, also remain well below the historical cycle-top zone of 7+, suggesting significant room for growth. This is all supported by the Federal Reserve’s projections for two interest rate cuts later this year, which are expected to increase market liquidity and fuel further upside.”
+Is now the time to buy, sell or hold BTC?
+The majority of the panel says now is a good time to buy bitcoin.
+To be exact, 61% think bitcoin is a buy at its current price, while 26% believe it’s a good time to hold the asset. Just 13% think it’s time to sell.
+Data chart showing how survey respondents think of when is the best time to buy, sell or hold BTC. - Finder.com
+Data chart showing how survey respondents think of when is the best time to buy, sell or hold BTC. - Finder.com
+Kadan Stadelmann, the CTO at Komodo Platform, believes it’s time to buy BTC over the next six months before it returns to a bear market. “Considering bitcoin touched $110,000 already, and there’s still at least six months left in this bull run, it’s easy to see it going significantly higher before the end of 2025,” he says. “If we continue to follow history, I expect the peak around Q1 of 2026 and a bear market to follow.”
+Rouge International &amp; Rouge Ventures’ MD, Desmond Marshall, also says BTC is a buy, off the back of governmental support. “BTC is becoming more in tune to gold these days, especially after the bombing of Iranian nuclear sites by the U.S.,” he says. “Together with [President Donald] Trump’s embrace of digital crypto assets, his sons dealing with huge amounts of crypto projects and the strong U.S. dollar, the U.S. government is already buying large reserves of BTC. This is supported by many businesses venturing into this realm with enterprise crypto strategies. BTC is so much less manipulated than gold already.”
+Nicole DeCicco, CEO of CryptoConsultz, says that BTC is currently underpriced and its current price doesn’t reflect its value. “Bitcoin’s current price doesn’t fully reflect the underlying momentum in the market,” she says. “We’ve seen several structural shifts this year that signal long-term strength: the approval and adoption of spot ETFs, a clear pivot in U.S. policy direction, and increasing global recognition of bitcoin as a reserve-style asset. These aren’t short-term headlines — they’re foundational changes that are reshaping the market’s infrastructure and investor profile.”
+John Murillo, chief business officer at B2Broker, sees BTC is priced fairly but still sees a buying opportunity based on geopolitical tensions right now. “Geopolitical turmoils like we are seeing now usually act as a cash magnet,” he says. “Warfare requires investors to store money in cash and safe havens. Furthermore, governments tend to impose additional levies on taxable assets, which is bad news for stocks and alternative investments. Although BTC is sometimes dubbed as ‘digital gold,’ history shows that geopolitical turbulence diverts money from cryptocurrencies. Having said that, the long-term prospects for BTC remain very favorable given accelerated worldwide adoption.”
+Miles Paschini, the CEO of FV Bank, says it’s time to hold, but does highlight the fact that institutional demand is growing. “Increasing institutional demand, emergence of bitcoin treasury companies putting demand against limited supply and BTC dominance increasing in the overall market indicates a trend-favored digital asset,” he said.
+Is bitcoin (BTC) overpriced, priced fairly or underpriced?
+A little over half of panel members (52%) think bitcoin is currently underpriced.
+The remaining cohort is also split between 30% saying BTC is priced fairly and 17% saying it’s overpriced.
+Data chart showing how survey respondents think of the current price of BTC. - Finder.com
+Data chart showing how survey respondents think of the current price of BTC. - Finder.com
+Ruslan Lienkha, chief of markets for YouHodler, believes that BTC is underpriced at its current value as bitcoin continues to be embraced by traditional finance: “The integration of bitcoin into traditional finance and its adoption by institutional investors is accelerating,” he says. “As a result, the potential capital inflow from investment funds, banks, and both public and private corporate treasuries remains substantial. Furthermore, if bitcoin continues to gain recognition as a legitimate macroeconomic hedge, it could prompt investors to significantly increase, potentially double or triple, their portfolio allocations to BTC.”
+Johnny Gabriele, head analyst of Blockchain Economics and AI Integration at the Lifted Initiative, also says BTC is currently undervalued, saying that BTC has “increased geopolitical importance as a reserve asset.”
+Daniel Keller, the CEO of InFlux Technologies, doesn’t see much movement in the price in the near term and that BTC is currently fairly priced. “The money printer continues to operate with no signs of stopping,” he says. “As long as global conflicts persist and remain unresolved, BTC will likely rise in value as a hedge against inflationary fiat currencies, which have been destabilized by so much geopolitical turmoil.”
+Do you think quantum computers will become a threat to bitcoin’s cryptographic security?
+The vast majority of the panel (79%) see quantum computing as a threat to bitcoin’s cryptographic security. But, when those threats will appear has them split.
+A quarter of panel members (25%) say that quantum computers will be able to crack BTC within the next five years, while another 25% say these developments will come within the next five to ten years. The remainder (29%) say it’ll take longer than 10 years.
+Just 8% say that quantum computers pose no threat.
+Data chart showing survey results to the question - Finder.com
+Data chart showing survey results to the question - Finder.com
+How prepared is the bitcoin community to address potential quantum computing threats?
+Close to half of the panel (46%) say that the bitcoin community is not well equipped for the threats quantum computing poses to BTC, with 42% saying that the community is somewhat underprepared and 4% saying they’re not prepared at all.
+A third of the panel (33%) is confident that the community is somewhat prepared.
+Data chart showing survey results to the question - Finder.com
+Data chart showing survey results to the question - Finder.com
+Table listing names of participants from the panel. - Finder.com
+Table listing names of participants from the panel. - Finder.com
+Disclaimer: This page is not financial advice or an endorsement of digital assets, providers or services. Digital assets are volatile and risky, and past performance is no guarantee of future results. Potential regulations or policies can affect their availability and services provided. Talk with a financial professional before making a decision. Finder or the author may own cryptocurrency discussed on this page.
+This story was produced by Finder.com and reviewed and distributed by Stacker.</t>
+  </si>
+  <si>
     <t>August 2025 Crypto Outlook: Bitcoin's Next Target $140K?</t>
   </si>
   <si>
@@ -299,6 +1444,91 @@
     <t>Says the price has been constant and that a lot of experts believe there to be movement in the near future.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+cryptonews.com
+August 2025 Crypto Outlook: Bitcoin's Next Target $140K?
+Features writer
+14–17 minutes
+Olga Primakova
+Features writer
+Olga PrimakovaVerified
+Part of the Team Since
+Nov 2024
+About Author
+Olga started writing about cryptocurrency and finance in 2021.
+Fact Checked by
+Elena Bozhkova
+Features Lead
+Elena BozhkovaVerified
+Part of the Team Since
+May 2024
+About Author
+Elena is the Features Lead at Cryptonews.com. With a Master's degree in science journalism from City University, London, she is passionate about exploring complex topics in the world of technology.
+Last updated: 
+August 1, 2025
+BTC ETH SOL August
+Key Takeaways:
+    Bitcoin is stuck below $120,000, but institutional accumulation and low volatility suggest a major move is brewing.
+    Ethereum led large-caps in July, boosted by ETF inflows and strong Layer 2 activity — $4,000 is the next key test.
+    Solana is holding ground near $200, backed by rising DeFi volume, ETF buzz, and surging on-chain momentum.
+    August is packed with market-moving events, from inflation data to Jackson Hole — all eyes on macro and momentum.
+After a strong close to July, crypto markets are entering August with momentum and caution. Bitcoin (BTC) remains range-bound, Ethereum (ETH) is riding institutional flows, and Solana (SOL) continues to grow as an on-chain hub. Each is approaching critical levels, both technically and psychologically.
+At the same time, macro forces are back in focus. U.S. inflation data, fresh tariff tensions, and major policy signals from Jackson Hole could all shake sentiment this month. With altcoin activity heating up and ETF speculation spreading, August may set the tone for the rest of Q3.
+Table of Contents
+    In This Article
+    In This Article
+    Show Full Guide
+Bitcoin’s Price Holds Steady — ‘A Big Move Is Likely Ahead’
+Bitcoin spent most of July in a narrow holding pattern between $115,000 and $118,000 — a surprisingly quiet month for the leading cryptocurrency. Even a mid-July attempt to reclaim the $120,000 level quickly fizzled, leaving the market in a low-volatility, low-volume consolidation phase.
+According to Abbas Abdul Sater, Head of Sales at Capital.com, this kind of calm could be setting the stage for something bigger:
+    Historically, periods like this often come before sharp moves. If Bitcoin can break above $120,000 with strong buying volume, the next target could be $140,000 or higher. But if it fails to hold current levels around $115,000, a short-term pullback might follow.
+Part of the optimism stems from improving macro conditions. U.S. GDP growth and a recovering labor market have boosted global risk appetite. Stocks are trending higher, and interest in risk-on assets like crypto is slowly picking up again — a setup that could support Bitcoin in early August.
+Abdul Sater also points to more regulatory clarity and a steady Fed policy as key tailwinds:
+    The Federal Reserve kept interest rates at 4.25%, which caused a brief dip in BTC before prices rebounded. At the same time, U.S. regulators are making progress — pushing for CFTC oversight on spot Bitcoin and allowing in-kind ETF creations, bringing crypto ETFs closer to traditional commodity standards.
+But while August begins with renewed interest in risk assets, Bitcoin’s price has already come under pressure. The month opened with a pullback triggered by Donald Trump’s announcement of new import tariffs, which spooked global markets and briefly dragged crypto down with equities.
+Historically, both August and September tend to be weaker months for Bitcoin, often marked by corrections or sideways movement. It’s October that frequently flips the script — with strong rallies following prolonged periods of cooling.
+Abbas Abdul Sater adds that the current setup may be laying the groundwork for a larger move:
+    Bitcoin is in a key consolidation phase. Steady accumulation from institutions and ETFs is providing long-term support, but low volatility signals that a big move is likely ahead.
+‘A Move Toward $6,000–$7,200 Is Realistic’ for Ethereum
+Ethereum posted a strong rebound in July, adding nearly 50% over the month and closing above $3,500 — a level not seen since early spring. This performance added fresh fuel to what many are calling the start of altcoin season.
+Dean Chen, Analyst at Bitunix, notes that Ethereum held up well despite broader volatility:
+    August will be a crucial test for Ethereum. Despite intense market volatility following the July FOMC meeting, Ethereum has maintained its position above $3,200, demonstrating notable relative strength.
+That strength was also reflected in ETF flows. Ethereum investment products saw net inflows on nearly every trading day in July, with just a single day of outflows at the start of the month. Inflows peaked on July 16, reaching $726.6 million — a signal that institutional interest in Ethereum is growing again.
+Chen sees this as part of a broader trend:
+    Institutional capital is increasingly flowing into Ethereum-native sectors like Real World Assets and modular apps. Should macro liquidity conditions turn favorable again, Ethereum reclaiming $4,800 and potentially expanding into the $6,000–$7,200 range is a realistic scenario.
+Technically, Ethereum is also showing signs of building a more stable base. Chen believes a measured pullback could strengthen the setup for a breakout:
+    If Ethereum pulls back and stabilizes around $3,450 — a key zone of prior highs and supply confluence — it would set up a healthier attempt to break the major resistance at $4,000. This level is structurally significant, formed during 2021–2022. If broken, a move back to the all-time high at $4,800 becomes highly probable.
+Solana Price Eyes $240 As On-Chain Momentum Builds
+Following Ethereum’s lead, Solana also moved higher in July, briefly breaking above $200. While its monthly performance of roughly 13.2% was more modest compared to ETH, interest in the Solana ecosystem continues to grow — fueled by rising DeFi activity and a steady stream of meme coins launching on its network.
+Pauline Shangett, CSO at ChangeNOW, highlights a surge in on-chain activity as a key factor behind Solana’s momentum:
+    We’re seeing a sharp rise in Solana’s TVL, now between $10–14 billion, a six-month high. DeFi activity is booming too, with DEX volume in July surpassing $1.4 trillion. On the institutional side, things are heating up: major players like Grayscale and Invesco Galaxy have filed or revised spot ETF applications, with decisions expected closer to October.
+This growing interest may help support price action in the weeks ahead. Maria Carola, CEO of StealthEx, says market sentiment is leaning bullish:
+    Most predictions for August are fairly optimistic. Some put it in the $195–$200 range, while others see it pushing toward $250 or even higher if momentum picks up.
+The question now is whether that momentum can hold. Shangett believes August will be pivotal for Solana’s price structure:
+    August will be a key moment to see if that momentum holds. I’m watching the $185–200 range closely. If Solana can maintain that zone, it sets a solid base for the next leg higher. Continued strength in on-chain activity, new users, rising transaction volume, and capital inflows could push the price toward $220–240 in the near term.
+August Could Be Pivotal for BTC, ETH, and SOL
+With July behind, Bitcoin, Ethereum, and Solana are entering August with mixed setups — but all three show signs of underlying strength.
+Bitcoin remains in a consolidation phase, trading just below $120,000. A decisive move in either direction could set the tone for the broader market. Abbas Abdul Sater summarizes the key inflection point:
+    A decisive break above $120,000 could push Bitcoin toward $140,000, while failure to maintain momentum may lead to a short-term dip.
+Ethereum closed the month as one of the top-performing large-cap assets, supported by ETF inflows and sustained Layer 2 activity. Markus Levin, co-founder of XYO, sees room for further growth despite possible volatility:
+    Ethereum’s rally in July has been driven by a combination of macro tailwinds, growing anticipation around the broader adoption of ETH ETFs, and renewed developer momentum in the ecosystem. Layer 2 activity has remained strong, and institutional sentiment is cautiously improving. Prices might be a little volatile, but yes, in the medium term, we believe Ethereum should continue to trend positively into August and beyond.
+Solana, meanwhile, is gaining traction across DeFi and retail communities. Its price is now hovering around the psychologically important $200 mark. Shawn Young, Chief Analyst at MEXC Research, expects that level to be a key test:
+    As for price action, the $200 level will be a battleground, both psychologically and technically. We may see resistance there in the near term due to strong network usage metrics and inflows into Solana-based products. This only suggests that if broader market conditions remain favourable, this level could become a support floor by Q4.
+Key Crypto Events to Watch in August 2025
+    August 4 — Solana Seeker Ships. Launch of Solana Mobile’s second-generation phone, potentially boosting ecosystem activity.
+    August 7 — U.S. Reciprocal Tariffs Take Effect. New import tariffs announced by Donald Trump come into force, with potential impact on global markets.
+    August 7 — U.S. Initial Jobless Claims. Weekly update on unemployment claims, a key labor market signal.
+    August 12 — US Inflation Data Release:
+        Consumer Price Index (CPI) – Monthly Change
+        CPI – Annual Change
+        Core CPI – Monthly Change
+    August 14 — US Producer Price Index (PPI). Tracks wholesale inflation, offering early clues about consumer price trends.
+    August 21 — 23 – Jackson Hole Economic Policy Symposium (US). Global central bankers gather for key policy discussions and potential market-moving statements.
+    August 29 — Iran Nuclear Deal Deadline (JCPOA). This is the deadline for negotiations on the Joint Comprehensive Plan of Action, which could have a possible geopolitical and market impact.
+Disclaimer: Crypto is a high-risk asset class. This article is provided for informational purposes and does not constitute investment advice.
+Follow us on Google News</t>
+  </si>
+  <si>
     <t>How Low Can Bitcoin Go in September 2025? BTC Price Predictions &amp; Analysis</t>
   </si>
   <si>
@@ -308,6 +1538,150 @@
     <t>Says september is historically a bad month for crypto and that important support levels are dangerously close to being passed.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+financemagnates.com
+How Low Can Bitcoin Go in September 2025? BTC Price Predictions &amp; Analysis
+Damian Chmiel
+14–18 minutes
+The question "How low can Bitcoin go in September 2025?" has taken on urgent relevance as the cryptocurrency enters its historically weakest month trading today, Monday, 1 September 2025, at $108,253, down 0.49% from yesterday and marking a concerning 6.5% August decline.
+Why is Bitcoin going down as September begins reflects both seasonal patterns and technical breakdowns that suggest further weakness ahead. However, my technical analysis suggests that the declines will be limited, and expert Bitcoin price predictions for the short and medium term indicate a relatively quick rebound toward all-time highs (ATH).
+Bitcoin September 2025: Current Price Action
+Bitcoin (BTC) begins September at a critical juncture, having broken its four-month winning streak with August's 6.5% decline while US-listed spot ETFs hemorrhaged $751 million in outflows. The cryptocurrency now trades near $108,000, approximately 13% below its August all-time high of $124,533.
+Key Bitcoin metrics for September 1, 2025:
+    Current price: $108,253
+    Monthly start: Down 0.49% from August 31
+    August performance: -6.5% (first red month since April)
+    ETF outflows: $751 million in August
+    Whale addresses (100+ BTC): Record high 19,130
+The price action reflects growing concern about Bitcoin's ability to maintain support levels as the month progresses.
+Bitcoin price today. Source: CoinMarketCap.
+Red September: Historical Patterns Spell Trouble
+September's Brutal Track Record
+Bitcoin price predictions September 2025 must account for the month's devastating historical performance. Since 2013, Bitcoin has posted average returns of -3.77% in September, closing red in 8 of the past 12 years. This "Red September" phenomenon mirrors broader market patterns, with the S&amp;P 500 averaging -1.20% returns in September since 1928.
+Yuri Berg from FinchTrade explains the mechanics: "Many investment funds close their fiscal year in September, divesting losing positions for tax reasons, and rebalancing their portfolios". The structural selling pressure creates a self-reinforcing downward spiral as traders anticipate weakness.
+September is the one of the worst months for Bitcoin price action. Source: CoinGlass
+2025 Mirrors 2017 Pattern
+However, analyst Rekt Fencer argues "a September dump is not coming" this year, citing similarities to 2017 when Bitcoin found support after August weakness before "rocketing to $20,000". The chart overlay reveals Bitcoin hovering near the crucial $105,000-$110,000 base that previously acted as resistance before flipping to support.
+    SEPTEMBER DUMP IS NOT COMING$BTC already front-ran the sell-off.
+    It played out the same way in 2017
+    Bears will miss the pump again pic.twitter.com/XIhKmpUlT1
+    — Rekt Fencer (@rektfencer) August 30, 2025
+Technical Analysis: How Low Can Bitcoin Drop?
+Key Support Levels Under Siege
+Based on my comprehensive technical analysis, Friday's nearly 4% decline broke Bitcoin out of its two-month consolidation that had kept prices near historical maximums. The cryptocurrency has now broken through legal support around $107,500, which coincides with the lowest levels in nearly two months.
+The critical support zone begins at $104,000, precisely at the 200-day moving average (200 MA). This support extends down to the psychological $100,000 level, where significant buy orders have accumulated. This zone is further reinforced by the 50% Fibonacci retracement measured from the April uptrend to August's historical maximum near $125,000.
+If asked how low Bitcoin can fall in September 2025, from current levels it would be maximum 8% decline to exactly $100,000, in my opnions. The analysis doesn't anticipate a stronger correction, and all downward movements will be treated as reaccumulation opportunities and buying chances at more attractive prices.
+Despite the bearish setup, "hidden bullish divergence" appears on Bitcoin's RSI, suggesting "the market is not as weak as the price chart suggests". Analyst ZYN projects Bitcoin could reach "a fresh all-time high above $124,500 within the next 4–6 weeks" based on these technical patterns.
+How low can Bitcoin go? Technical analysis. Source: Tradingview.com
+Institutional Dynamics: Mixed Signals
+    Record Whale Accumulation Despite Weakness - A remarkable development shows whale addresses holding 100+ BTC reached a record high of 19,130, surpassing even the 2017 peak. This accumulation pattern suggests sophisticated investors are buying the dip despite retail capitulation.
+    ETF Outflows Signal Institutional Caution - Conversely, $751 million in ETF outflows during August indicates institutional uncertainty. The divergence between whale accumulation and ETF selling suggests different time horizons and risk appetites among large holders.
+    Fed Policy Creates Macro Tailwind - Currency traders are turning bearish on the dollar with expectations for Fed rate cuts creating potential upside catalysts. The 52-week correlation between Bitcoin and the Dollar Index has weakened to -0.25, its lowest level in two years, suggesting Bitcoin could benefit from dollar weakness.
+September 2025 Bitcoin Price Predictions: Expert Consensus
+Bearish Scenarios Dominate
+Changelly's Bitcoin price predictions September 2025 show potential volatility with a minimum target of $108,802 and maximum of $124,283. However, most technical analysts lean bearish given the seasonal headwinds and broken support levels.
+Binance's forecast projects September ending around $108,332, suggesting limited upside potential.
+Bull Case: Breaking the Pattern
+Despite historical weakness, some analysts believe Bitcoin could "break the Red September curse" in 2025. Tom Lee, co-founder of Fundstrat Global Advisors, has been one of the most bullish and accurate Bitcoin analysts in recent years. He believes that Bitcoin can go back to $120,000 this month and end the year around $200,00.
+The bull case relies on:
+    Federal Reserve rate cuts providing liquidity
+    Institutional adoption continuing despite ETF outflows
+    Technical rebound from oversold conditions
+    2017 pattern repetition suggesting final shakeout before rally
+Ash Crypto predicts "the Fed will start the money printers in Q4" with "two rate cuts mean trillions will flow into the crypto market".
+You may also like: New BTC Price Predictions Point to $200K in 2025 and $1M Long Term
+Why is Bitcoin Going Down: Fundamental Drivers
+Structural September Selling
+The September Effect stems from multiple converging factors:
+    Portfolio rebalancing by institutional investors
+    Tax loss harvesting before fiscal year-end
+    Reduced summer liquidity creating volatility
+    Psychological selling based on historical patterns
+Technical Momentum Breakdown
+Key momentum indicators have turned decisively bearish:
+    MACD histogram dropped below zero
+    RSI shows oversold conditions below 30
+    Moving average structure confirms downtrend
+FAQ: Bitcoin September 2025 Outlook
+How low can Bitcoin realistically go in September 2025?
+My technical analysis suggests $100K-$101K as primary support, though some projections see potential for deeper correction to mid-$90Ks.
+Will Bitcoin break the Red September pattern in 2025?
+Mixed signals, whale accumulation and Fed policy support bulls, while technical breakdowns and ETF outflows favor bears.
+What would trigger a September rally instead of decline?
+Federal Reserve dovishness, dollar weakness, and institutional re-entry above $113.5K resistance could flip sentiment.
+Is September selling just a self-fulfilling prophecy?
+Partly, but structural factors like portfolio rebalancing and reduced liquidity create genuine seasonal headwinds.
+The question "How low can Bitcoin go in September 2025?" has taken on urgent relevance as the cryptocurrency enters its historically weakest month trading today, Monday, 1 September 2025, at $108,253, down 0.49% from yesterday and marking a concerning 6.5% August decline.
+Why is Bitcoin going down as September begins reflects both seasonal patterns and technical breakdowns that suggest further weakness ahead. However, my technical analysis suggests that the declines will be limited, and expert Bitcoin price predictions for the short and medium term indicate a relatively quick rebound toward all-time highs (ATH).
+Bitcoin September 2025: Current Price Action
+Bitcoin (BTC) begins September at a critical juncture, having broken its four-month winning streak with August's 6.5% decline while US-listed spot ETFs hemorrhaged $751 million in outflows. The cryptocurrency now trades near $108,000, approximately 13% below its August all-time high of $124,533.
+Key Bitcoin metrics for September 1, 2025:
+    Current price: $108,253
+    Monthly start: Down 0.49% from August 31
+    August performance: -6.5% (first red month since April)
+    ETF outflows: $751 million in August
+    Whale addresses (100+ BTC): Record high 19,130
+The price action reflects growing concern about Bitcoin's ability to maintain support levels as the month progresses.
+Bitcoin price today. Source: CoinMarketCap.
+Red September: Historical Patterns Spell Trouble
+September's Brutal Track Record
+Bitcoin price predictions September 2025 must account for the month's devastating historical performance. Since 2013, Bitcoin has posted average returns of -3.77% in September, closing red in 8 of the past 12 years. This "Red September" phenomenon mirrors broader market patterns, with the S&amp;P 500 averaging -1.20% returns in September since 1928.
+Yuri Berg from FinchTrade explains the mechanics: "Many investment funds close their fiscal year in September, divesting losing positions for tax reasons, and rebalancing their portfolios". The structural selling pressure creates a self-reinforcing downward spiral as traders anticipate weakness.
+September is the one of the worst months for Bitcoin price action. Source: CoinGlass
+2025 Mirrors 2017 Pattern
+However, analyst Rekt Fencer argues "a September dump is not coming" this year, citing similarities to 2017 when Bitcoin found support after August weakness before "rocketing to $20,000". The chart overlay reveals Bitcoin hovering near the crucial $105,000-$110,000 base that previously acted as resistance before flipping to support.
+    SEPTEMBER DUMP IS NOT COMING$BTC already front-ran the sell-off.
+    It played out the same way in 2017
+    Bears will miss the pump again pic.twitter.com/XIhKmpUlT1
+    — Rekt Fencer (@rektfencer) August 30, 2025
+Technical Analysis: How Low Can Bitcoin Drop?
+Key Support Levels Under Siege
+Based on my comprehensive technical analysis, Friday's nearly 4% decline broke Bitcoin out of its two-month consolidation that had kept prices near historical maximums. The cryptocurrency has now broken through legal support around $107,500, which coincides with the lowest levels in nearly two months.
+The critical support zone begins at $104,000, precisely at the 200-day moving average (200 MA). This support extends down to the psychological $100,000 level, where significant buy orders have accumulated. This zone is further reinforced by the 50% Fibonacci retracement measured from the April uptrend to August's historical maximum near $125,000.
+If asked how low Bitcoin can fall in September 2025, from current levels it would be maximum 8% decline to exactly $100,000, in my opnions. The analysis doesn't anticipate a stronger correction, and all downward movements will be treated as reaccumulation opportunities and buying chances at more attractive prices.
+Despite the bearish setup, "hidden bullish divergence" appears on Bitcoin's RSI, suggesting "the market is not as weak as the price chart suggests". Analyst ZYN projects Bitcoin could reach "a fresh all-time high above $124,500 within the next 4–6 weeks" based on these technical patterns.
+How low can Bitcoin go? Technical analysis. Source: Tradingview.com
+Institutional Dynamics: Mixed Signals
+    Record Whale Accumulation Despite Weakness - A remarkable development shows whale addresses holding 100+ BTC reached a record high of 19,130, surpassing even the 2017 peak. This accumulation pattern suggests sophisticated investors are buying the dip despite retail capitulation.
+    ETF Outflows Signal Institutional Caution - Conversely, $751 million in ETF outflows during August indicates institutional uncertainty. The divergence between whale accumulation and ETF selling suggests different time horizons and risk appetites among large holders.
+    Fed Policy Creates Macro Tailwind - Currency traders are turning bearish on the dollar with expectations for Fed rate cuts creating potential upside catalysts. The 52-week correlation between Bitcoin and the Dollar Index has weakened to -0.25, its lowest level in two years, suggesting Bitcoin could benefit from dollar weakness.
+September 2025 Bitcoin Price Predictions: Expert Consensus
+Bearish Scenarios Dominate
+Changelly's Bitcoin price predictions September 2025 show potential volatility with a minimum target of $108,802 and maximum of $124,283. However, most technical analysts lean bearish given the seasonal headwinds and broken support levels.
+Binance's forecast projects September ending around $108,332, suggesting limited upside potential.
+Bull Case: Breaking the Pattern
+Despite historical weakness, some analysts believe Bitcoin could "break the Red September curse" in 2025. Tom Lee, co-founder of Fundstrat Global Advisors, has been one of the most bullish and accurate Bitcoin analysts in recent years. He believes that Bitcoin can go back to $120,000 this month and end the year around $200,00.
+The bull case relies on:
+    Federal Reserve rate cuts providing liquidity
+    Institutional adoption continuing despite ETF outflows
+    Technical rebound from oversold conditions
+    2017 pattern repetition suggesting final shakeout before rally
+Ash Crypto predicts "the Fed will start the money printers in Q4" with "two rate cuts mean trillions will flow into the crypto market".
+You may also like: New BTC Price Predictions Point to $200K in 2025 and $1M Long Term
+Why is Bitcoin Going Down: Fundamental Drivers
+Structural September Selling
+The September Effect stems from multiple converging factors:
+    Portfolio rebalancing by institutional investors
+    Tax loss harvesting before fiscal year-end
+    Reduced summer liquidity creating volatility
+    Psychological selling based on historical patterns
+Technical Momentum Breakdown
+Key momentum indicators have turned decisively bearish:
+    MACD histogram dropped below zero
+    RSI shows oversold conditions below 30
+    Moving average structure confirms downtrend
+FAQ: Bitcoin September 2025 Outlook
+How low can Bitcoin realistically go in September 2025?
+My technical analysis suggests $100K-$101K as primary support, though some projections see potential for deeper correction to mid-$90Ks.
+Will Bitcoin break the Red September pattern in 2025?
+Mixed signals, whale accumulation and Fed policy support bulls, while technical breakdowns and ETF outflows favor bears.
+What would trigger a September rally instead of decline?
+Federal Reserve dovishness, dollar weakness, and institutional re-entry above $113.5K resistance could flip sentiment.
+Is September selling just a self-fulfilling prophecy?
+Partly, but structural factors like portfolio rebalancing and reduced liquidity create genuine seasonal headwinds.
+</t>
+  </si>
+  <si>
     <t>Bitcoin (BTC) Price Prediction – October 2025</t>
   </si>
   <si>
@@ -317,6 +1691,48 @@
     <t>Says October is usually a good month for crypto, though it says that current government shutdown concerns and a history of issues during October shutdowns is a risk.</t>
   </si>
   <si>
+    <t>Bitcoin (BTC): Strong October track record, but risks from a possible U.S. government shutdown could trigger short-term corrections.
+Ethereum (ETH): Oversold and primed for a rebound, with historical Q4 gains suggesting potential for a major rally toward $7K–$8K.
+XRP: Biggest catalyst this month with eight ETF decisions due; approvals could unleash billions in institutional inflows and push prices into new highs.
+As September 2025 closes in the green, cryptocurrency markets enter October with cautious optimism. Historically, October has been one of the strongest months for Bitcoin (BTC) and Ethereum (ETH), while XRP faces potentially transformative ETF decisions. With macroeconomic uncertainty, institutional flows, and investor sentiment heating up, October may prove pivotal for the digital asset market.
+Bitcoin (BTC) Price Prediction – October 2025
+Bitcoin ended September with gains — historically a strong signal for continued upside. An analysis of the past 15 Octobers shows a 73% chance of a positive monthly close, with 11 out of 15 years finishing in the green.
+Historical October returns: Average +27%, Median +28.3%
+Six straight positive Octobers: Some rallies exceeded +30% to +40%
+Last negative October: 2018 (-3.3%) during a prior shutdown
+If history repeats, Bitcoin could continue higher. However, negative Octobers have historically delivered deeper drawdowns (~30%), which would put BTC near the $80K range in a downside scenario.
+Technical view:
+Early signals point to possible corrective targets near $105K–$102.5K.
+If Bitcoin follows its Q4 track record, a surge toward new all-time highs remains likely.
+Ethereum (ETH) Price Prediction – October 2025
+Ethereum enters October after dipping below $4,000 in September, but it rebounded and is holding above the $3,900 support zone.
+Immediate resistance: $4,260
+Next targets: $4,670 and $5,000 if breakout confirmed
+Support range: $4,000–$4,600 consolidation possible
+Oversold setup: Ethereum’s RSI is at its lowest since April 2025 — a condition that previously triggered a +134% rally within two months.
+Historical Q4 strength:
++104% (2020)
++142% (2017)
++36% (2023)
++28% (2024)
+Average Q4 gain: ~+24%
+If ETH holds above $4K weekly, analysts see a rally toward $7K–$8K, potentially fueling a larger bull run into 2026.
+XRP Price Prediction – October 2025
+XRP may be the biggest story of October. Final decisions are expected on eight XRP ETF applications later this month, raising expectations for significant institutional inflows.
+Analyst estimate: $3–5B inflows in the first year could double XRP’s market cap and push toward $5.
+Sustained adoption could open the door to double-digit XRP for the first time in history.
+Technical view:
+Current support: $3.00 (critical battleground)
+Resistance levels: $3.65 → $4.50
+Failure to hold momentum: Risk of pullback to $2.75 support
+Analysts note XRP’s current chart resembles its 2017 parabolic setup, hinting at potential for a powerful breakout.
+Conclusion
+Bitcoin: October has historically been bullish, though risks like the U.S. government shutdown could spark short-term corrections.
+Ethereum: Oversold conditions and strong Q4 track record suggest a rebound toward $7K–$8K is possible.
+XRP: ETF decisions this month could be transformative, with institutional inflows possibly unlocking a new era of growth.
+⚡ Overall, Q4 2025 may set the stage for a major crypto rally heading into 2026.</t>
+  </si>
+  <si>
     <t>Why Analysts See November as Cycle Bottom for Bitcoin</t>
   </si>
   <si>
@@ -326,6 +1742,44 @@
     <t>Says lunar phases and strong support at $100k are signalling a local bottom with a possibility for a rebound.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+Bitcoin Bottom in Sight? Technicals and Lunar Cycles Point to November Reversal
+Lockridge Okoth
+5–6 minutes
+Bitcoin (BTC) traders anticipate a local bottom forming in mid-November, as the 50-day simple moving average (SMA) is set to cross below the 200-day SMA near $100,000, a pattern that has often marked local bottoms.
+In addition, some analysts are overlaying lunar phases on price charts, noting that First Quarter moons often precede rallies extending into Full or Third Quarter moons. These contrasting strategies, classic technical analysis and the use of lunar phase timing, are capturing attention as Bitcoin tests critical supports.
+Death Cross and Key Support Levels Indicate November Bottom
+The expected intersection of Bitcoin’s 50-day and 200-day SMAs, often called a death cross, could occur in mid-November near $100,000. Historically, this event signals local bottoms and does not usually mark long-term downturns.
+According to Binance’s analysis, the average price change one month after a death cross is just -3.2%, challenging the idea that it reliably triggers lasting bear markets.
+Analyst Colin suggests the lowest reasonable level for Bitcoin in this bull market cycle is around $98,000, a region with multiple support alignments. This matches with the 50-week SMA, which has provided support since Q1 2023.
+Binance data from October 2025 indicates that the 50-week SMA is approximately $101,700, a key level during the ongoing bull market.
+Since Q1 2023, Bitcoin has not closed a weekly candle beneath the 50-week SMA, a point highlighted by analyst Ted Pillows in his October post. This level, now around $102,800, serves as the threshold Bitcoin must hold to maintain the bull run.
+A weekly close below this support level could indicate a potential downturn in market structure.
+Rising Wedge Formation Could Lead to 15-35% Dip
+Despite positive long-term signals, Bitcoin’s weekly chart now displays a rising wedge, a bearish pattern characterized by converging trendlines that indicate waning momentum.
+Bitcoin (BTC) Price Performance
+Bitcoin (BTC) Price Performance. Source: TradingView
+In previous cycles, this setup has resulted in declines ranging from 15% to 35%, as observed in both 2018 and 2021. The pattern suggests weaker buying pressure at increasingly higher prices within a narrowing range.
+Still, the overall bull market structure holds. Bitcoin continues to record higher lows and higher highs within an ascending channel since 2022.
+Historically, bounces from the channel’s lower range have rebounded 60% to 170%. Some analysts maintain a price target of $170,000 or higher, crediting this strong uptrend and the absence of overbought cycle signals traditionally seen at macro tops.
+The current sideways trading between $105,000 and $110,000 is viewed as a consolidation, rather than a market breakdown.
+Colin’s analysis suggests the market is testing holders’ patience, especially for altcoin investors, as the cycle stretches beyond a standard Q4 peak. He notes Bitcoin bucked precedent in the last bear market when its low of $15,000 fell below the former cycle’s top of $20,000, a first for the digital asset.
+Lunar Cycle Observations Add to Bullish Case
+Some traders also match Bitcoin’s price patterns with lunar phases. Analyst LP_NXT shared an analysis illustrating that when Bitcoin is mapped alongside moon cycles, a clear rhythm emerges for 2025.
+First Quarter moons, including the recent October 29 event, have often corresponded with the beginning of upward moves extending into the Full or Third Quarter moon periods.
+The First Quarter moon on October 29, 2025, could thus align with a bullish trend according to this theory. This timing aligns with the technical view that mid-November could mark the local bottom.
+Supporters attribute these cycles to recurring market psychology rather than superstitious reasoning. Although lunar phase analysis lacks the rigor of established technical tools, its recurrence among traders highlights the diverse range of strategies employed in crypto markets.
+The alignment of lunar timing, established support levels, and moving average crossovers makes November 2025 a focal point for traders.
+Bullish Structure Holds as Market Consolidates
+Current market conditions balance short-term bearish technicals with long-term bullish momentum. Colin’s analysis highlights the importance of patience, suggesting that market shakeouts may occur for those seeking a traditional Q4 peak.
+He recommends holding Bitcoin until a new all-time high is reached, then potentially rotating into altcoins using Bitcoin-denominated gains a few weeks later.
+The so-called death cross, while generally seen as negative, acts more as a lagging confirmation in Bitcoin’s history.
+Meanwhile, Ledger’s educational materials point out that it often signals capitulation (exhausted selling and reversal) rather than forecasting major moves in advance.
+As October 2025 concludes, Bitcoin’s ability to remain above the 50-week SMA will determine the bull market’s path.
+The mid-November window, suggested by both moving average analysis and lunar timing, provides traders with a timeframe for potential accumulation. Whether traditional or unconventional methods prove accurate, November 2025 is shaping up to be a decisive period for Bitcoin price action.</t>
+  </si>
+  <si>
     <t>Bitcoin Price Prediction For December: Breakdown or Rally?</t>
   </si>
   <si>
@@ -335,6 +1789,61 @@
     <t>Says a lot of weak sentiment in the market after a disappointing month is likely to continue. Some analysts think there isn't going to be much movement.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+beincrypto.com
+What To Expect From Bitcoin Price In December 2025
+Ananda Banerjee
+6–8 minutes
+The Bitcoin price in December is now a key focus, given that the market ended November on a weak note. Bitcoin dropped more than 17% this month, breaking its usual November trend and raising questions about whether the recent $80,000 bounce was the real bottom.
+December has a mixed history for Bitcoin, and early data for this year shows some caution in both spot flows and on-chain signals. This analysis examines three key areas: seasonal performance, ETF flows, and insights from on-chain and price charts regarding the upcoming month.
+Bitcoin’s December History and What ETF Flows Reveal
+December is not usually a very strong month for Bitcoin. The long-term average return is 8.42%, but the median return is only 1.69%. The last four years also show mixed results, with three negative Decembers.
+November added more caution. Instead of repeating its strong seasonal pattern, Bitcoin finished the month more than 17% lower.
+BTC Price History
+BTC Price History: CryptoRank
+Want more token insights like this? Sign up for Editor Harsh Notariya’s Daily Crypto Newsletter here.
+ETF flows echo that caution. November closed with –$3.48 billion in net outflows across US spot ETFs. The last clear multi-month inflow streak happened between April and July.
+Since then, flows have been inconsistent, and November confirmed that institutions remained defensive.
+ETF Flows Need To Make A Green Sreak
+ETF Flows Need To Make A Green Sreak: SoSo Value
+MEXC Chief Analyst Shawn Young told BeInCrypto that stronger and more consistent ETF demand is essential before a meaningful rebound can begin:
+    “The most evident indicators of Bitcoin’s next upside rally would be a resurgence in risk sentiment, improved liquidity conditions, and market depth… When Bitcoin spot ETFs begin to see multiple days of inflows of $200–$300 million, it may indicate that institutional allocators are rotating back into BTC and the next leg up is underway,” he mentioned.
+Hunter Rogers, Co-Founder of TeraHash, added that the setup for December still looks muted even after November’s flush-out:
+    “I don’t expect a highly-volatile December — neither a major jump nor a major drop. A quieter month with a slow upward movement looks more realistic. If ETF flows calm down and volatility stays low, Bitcoin could put in a small positive surprise. But this still feels like a repair phase,” he said.
+Together, the seasonal pattern and ETF flows show that December may stay cautious unless ETF demand turns sharply higher.
+On-Chain Metrics Still Show Weak Conviction
+Bitcoin’s on-chain data still does not match what a confirmed December bottom usually looks like. Two core signals tell the same story: whales are still sending coins to exchanges, and long-term holders remain in distribution mode.
+The Exchange Whale Ratio — which measures how much of total inflows come from the top 10 large wallets — climbed from 0.32 earlier this month to 0.68 on November 27.
+Even after easing to 0.53, it remains in a zone that historically reflects whales preparing to sell, not accumulate. Durable bottoms rarely form when this ratio stays elevated across several weeks.
+Whales Keep Moving BTC To Exchanges
+Whales Keep Moving BTC To Exchanges: CryptoQuant
+The Hodler Net Position Change, which tracks long-term investor behavior, also stays deep in the red. These wallets have been reducing their positions for more than six months. The last strong BTC rally began only after this metric turned green in late September — a milestone it has not achieved again yet.
+Long-Term Investors Still Selling
+Long-Term Investors Still Selling: Glassnode
+Until long-term holders stop sending coins back into circulation, sustained upside becomes harder to support.
+Shawn believes that a true shift begins only when long-term sellers step aside:
+    “The rally could begin when OG sellers stop transferring coins onto exchanges, whale accumulation turns positive again, and market depth starts to thicken across major venues,” he emphasized
+Hunter Rogers echoed this view, linking any trend reversal to cleaner supply behavior from miners and long-term wallets:
+    “When long-term holders quietly move back into accumulation, it means supply pressure is fading,” he mentioned
+So far, neither trend has flipped. Whales continue to send coins to exchanges, and long-term holders continue to distribute. Together, they signal that the Bitcoin price in December may attempt deeper retests before any strong recovery attempt.
+Bitcoin Price In December: Key Risks And Confirmations
+The Bitcoin price now sits at a point where even a small move can set the tone for December. The broader trend still leans bearish, and the chart structure confirms what the ETF and on-chain data already hint at.
+BTC recently slipped below the lower band of a bear flag that has been building for weeks. This breakdown suggests a possible extension to $66,800, although the market may not reach that level immediately if liquidity remains stable.
+For December, the first major line to watch is $80,400. That level acted as a rebound zone earlier this month, but it remains fragile.
+A clean close below $80,400 opens room for new lows, aligning with what Shawn Young believes is still “a plausible liquidity sweep” before any stronger recovery attempt.
+Here is what he said in an exclusive bit, giving the market some hope as well:
+    “Bitcoin’s market setup suggests a wick-style liquidity sweep rather than a prolonged breakdown,” he believes
+On the upside, the structure only flips if BTC reclaims $97,100 — the midpoint of the larger pole-and-flag setup. A daily close above that zone would erase the bear-flag breakdown and begin a move toward resistance near $101,600.
+Hunter also pointed out that reclaiming higher trend levels only matters if volume rises along with it. As he put it:
+    “If Bitcoin holds above the breakout zone and volume improves, then the market can start treating that area as a durable floor,” he mentioned.
+For December, that breakout zone sits between $93,900 and $97,100, which is where the chart, ETFs, and on-chain conditions need to switch from defensive to supportive.
+Bitcoin Price Analysis
+Bitcoin Price Analysis: TradingView
+Until those confirmations arrive, the downside remains more pronounced than the upside. A deeper Bitcoin price retest stays in play if ETF outflows accelerate or if whales continue to send coins to exchanges.
+For now, the Bitcoin price in December begins with the OG crypto sitting between two critical walls — $80,400 as the last defensive floor, and $97,137 as the ceiling that can reset momentum.
+</t>
+  </si>
+  <si>
     <t>Tom Lee Dusts Off Failed 2025 Bitcoin Prediction, Sees $250,000 This Year</t>
   </si>
   <si>
@@ -344,6 +1853,30 @@
     <t>Doesn't really offer any prediction. Honestly reads more like market noise, but does say prices are likely to go WAY up in the long run.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+finance.yahoo.com
+Tom Lee Dusts Off Failed 2025 Bitcoin Prediction, Sees BTC Hitting $250K In 2026
+David Okoya
+~3 minutes
+Benzinga and Yahoo Finance LLC may earn commission or revenue on some items through the links below.
+Fundstrat investment chief Tom Lee is bringing back his Bitcoin price prediction from last year.
+Bitcoin could reach between $200,000 and $250,000 this year, Lee told CNBC on Monday, dusting off his failed call for the asset last year. The asset reached a record price of about $126,000 last year before crashing to end the year near $88,000.
+Lee said he was optimistic about Bitcoin this year following the Oct. 10 crash. He said the crash wiped out excess leverage, which could allow for a healthy rally. He also cited tailwinds such as institutional adoption and government support.
+Don't Miss:
+    Missed Nvidia and Tesla? RAD Intel Could Be the Next AI Powerhouse — Invest Now at Just $0.85 a Share
+    Sam Altman Says AI Will Transform the Economy — This Platform Lets Investors Back Private Tech Early
+Additionally, he said Bitcoin is likely to benefit from gold and silver’s rally last year, noting that gold rallies have typically led Bitcoin rallies.
+At the same time, Lee said if Bitcoin hit the $250,000 target, it would confirm the end of the so-called four-year cycle.
+The four-year cycle refers to a historical pattern that has seen Bitcoin surge to new highs and crash once every four years. The cycle is associated with "the halvening," a programmed event that reduces the supply of new Bitcoin roughly every four years. With the last halvening in 2024, the pattern suggests that last year was Bitcoin’s up year and this year would see the beginning of an extended crash.
+Trending: 7 Million Gamers Already Trust Gameflip With Their Digital Assets — Now You Can Own a Stake in the Platform Before the Raise Ends 1/19
+However, like Lee, several analysts have suggested that the four-year cycle is likely over, citing changes in Bitcoin’s market structure. These changes include the launch of spot exchange-traded funds and the proliferation of treasury companies.
+Still, this year is not going to be without hurdles for Bitcoin and the broader market, according to Lee.
+"Compressed in one year will be joy, depression and rally," he told CNBC, referring to the broader market.
+See Also: Americans With a Financial Plan Can 4X Their Wealth — Get Your Personalized Plan from a CFP Pro
+According to Lee, a 15% to 20% correction in the S&amp;P 500 is likely in the second half of the year, though he sees the index surging to $7,700. He said the volatility would likely result from uncertainty surrounding new Federal Reserve leadership.
+</t>
+  </si>
+  <si>
     <t>Bitcoin Price Outlook: '$60K–$65K Looks Realistic'</t>
   </si>
   <si>
@@ -353,6 +1886,84 @@
     <t>Seems everyone it cites think it will go down due to macro preasures and political issues. Doesn't say the drop will be catastrophical, though.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+cryptonews.com
+Bitcoin Price Outlook: ‘$60K–$65K Looks Realistic’, Analysts Warn
+Features writer
+8–10 minutes
+Olga Primakova
+Features writer
+Olga PrimakovaVerified
+Part of the Team Since
+Nov 2024
+About Author
+Olga started writing about cryptocurrency and finance in 2021.
+Fact Checked by
+Elena Bozhkova
+Features Lead
+Elena BozhkovaVerified
+Part of the Team Since
+May 2024
+About Author
+Elena is the Features Lead at Cryptonews.com. With a Master's degree in science journalism from City University, London, she is passionate about exploring complex topics in the world of technology.
+Last updated: 
+February 4, 2026
+BITCOIN PRICE
+Key Takeaways:
+    Bitcoin is retesting the $74,000 area, a level that previously marked the start of a strong six-month rally in 2024.
+    Several analysts see the $60,000–$65,000 range as a realistic downside floor, representing a typical 50% correction for Bitcoin cycles.
+    Macro pressure and geopolitics, including Trump’s tariffs and ETF outflows, continue to weigh on Bitcoin, reinforcing its role as a risk asset in the short term.
+    Near-term conditions remain cautious. Analysts warn of false breakouts, fading rallies, and the need for patience until Bitcoin establishes a clearer trading range.
+    A deeper drop below $60,000 would likely require a clear surge in panic selling, which some experts see as less likely given the behavior of long-term holders.
+Bitcoin price has once again approached a key level around $74,000. This is where BTC began its recovery back in April last year. Since then, the market has not revisited this zone.
+From that level, Bitcoin went on a strong run. The uptrend, with only shallow pullbacks, lasted roughly six months. It culminated in a new all-time high on Oct. 6, when BTC briefly touched $126,080. That peak now sits almost 40% above current prices.
+But the context today looks very different.
+On the one hand, $74,000 has history on its side. Last year, it acted as a clear bottom. Buyers stepped in aggressively, and the market turned higher. That memory still matters.
+On the other hand, sentiment has changed since the October crypto sell-off. Buyers now look hesitant. Every attempt by Bitcoin to push out of its current range is quickly met with selling pressure. Rallies fade fast. In that light, it’s easy to understand investors who are using small rebounds to reduce losses or exit at breakeven.
+In this Cryptonews report, we spoke with analysts about what February could bring for Bitcoin and why a move below $70,000 is increasingly part of the discussion.
+Bitcoin Price Could See a 50% Correction, ‘Which Is Brutal but Normal’
+In a conversation with Cryptonews, Tanisha Katara, a blockchain governance consultant and researcher working with Avail, Filecoin, and Polygon, said the market may be closer to a real bottom than many fear:
+    $60,000–$65,000 is a realistic floor, and that’s where real buyers historically show up. It represents roughly a 50% drawdown, which is brutal but normal for Bitcoin corrections.
+At the same time, she dismissed scenarios calling for a much deeper drop. A move toward the $30,000–$35,000 range, Katara argued, “is a ridiculous and baseless prediction.”
+Katara added that Bitcoin is currently behaving like a classic risk asset, with macro pressure playing a major role:
+    Trump’s tariffs triggered a risk-off move across global markets. Leverage was wiped out, followed by $1.6 billion in monthly ETF outflows. This combination created selling pressure for BTC and other crypto assets.
+Bitcoin Price Awaits Its Next Move
+Gavin Thomas, CEO and co-founder of TEN Protocol, told Cryptonews that he sees a similar support zone but emphasized what would be required for Bitcoin to break lower:
+    $60,000 is where most models see deeper support if Bitcoin drops through the psychological $70,000 floor. For Bitcoin to retreat past $60,000, putting it bluntly, there will need to be a strong upshift in panic selling.
+Thomas argues that this may be harder than it sounds. Many long-term holders have already lived through multiple cycles. Instead of selling into fear, they are more likely to hold through volatility or accumulate at lower levels.
+Looking ahead to the near term, he expects February to remain challenging.
+Thomas said the next month is likely to be marked by caution across the crypto industry, with reduced spending and limited activity outside a small number of standout projects:
+    Over the next four weeks there will be continued cost-cutting across the crypto industry, very few to zero ICOs and only isolated pockets of innovation capturing people’s attention. One or two projects may take advantage of the vacuum of good news to execute prepared marketing campaigns, but generally this month will see a continued downtrend as geopolitical conditions continue to inject uncertainty.
+While some experts remain optimistic about Bitcoin’s broader outlook and long-term performance, short-term expectations are notably more cautious.
+Beyond macroeconomic data, geopolitics has become an increasingly important factor for Bitcoin price, often triggering sharp moves to the downside. In this environment, capital preservation matters.
+False moves are likely. At times, the market may look ready to rally, only to reverse shortly after. For now, patience is key. The market needs time to cool off and establish a clear range before a more reliable trend can emerge.
+February Crypto &amp; Macro Calendar
+February 4
+    EUR — CPI (YoY), Jan
+    USD — S&amp;P Global Services PMI, Jan
+    USD — JOLTS Job Openings, Dec
+February 5
+    USD — ISM Non-Manufacturing Prices, Jan
+    USD — ISM Non-Manufacturing PMI, Jan
+    USD — Initial Jobless Claims
+February 10
+    USD — Retail Sales (MoM), Dec
+    USD — Core Retail Sales (MoM), Dec
+February 11
+    USD — CPI (MoM), Jan
+    USD — CPI (YoY), Jan
+    USD — Core CPI (MoM), Jan
+February 12
+    USD — Initial Jobless Claims
+February 13
+    USD — Existing Home Sales, Jan
+February 20
+    USD — S&amp;P Global Services PMI, Feb
+    USD — S&amp;P Global Manufacturing PMI, Feb
+Disclaimer: Crypto is a high-risk asset class. This article is provided for informational purposes and does not constitute investment advice.
+Follow us on Google News</t>
+  </si>
+  <si>
     <t>Bitcoin High-Stakes March: $120K Forecasts Meet the $60K–$70K Accumulation Grind</t>
   </si>
   <si>
@@ -362,6 +1973,66 @@
     <t>Equally long sections for both a bullish and bearish outlook. It does say odds may favor the bulls through.</t>
   </si>
   <si>
+    <t xml:space="preserve">
+cryptonews.com
+Bitcoin High Stakes This March
+Web 3 Journalist
+7–9 minutes
+Bitcoin High-Stakes March: $120K Forecasts Meet the $60K–$70K Accumulation Grind
+Tim Hakki
+Web 3 Journalist
+Tim HakkiVerified
+Part of the Team Since
+Feb 2024
+About Author
+A journalist and copywriter with a decade's experience across music, video games, finance and tech.
+Fact Checked by
+CryptoNews Editorial Team
+Author
+CryptoNews Editorial TeamVerified
+Part of the Team Since
+Sep 2018
+About Author
+The CryptoNews editorial team is composed of seasoned writers specializing in cryptocurrency and blockchain technology. Their expertise ensures comprehensive, accurate, and insightful content for...
+Last updated: 
+March 2, 2026
+Bitcoin's High-Stakes March: $120K Forecasts Meet the $60K–$70K Accumulation Grind
+Bitcoin March outlook is separating the bulls from the bears. After grinding through a sustained high-stakes consolidation phase that bottomed at $62,900 last week, Bitcoin is back trading above $66,000 at the time of writing.
+While price action feels heavy following the 22% decline from this time last year, macro analysts are eyeing a violent repricing event that could send the asset vertical before the end of the month.
+Key Takeaways:
+    Macro economist Henrik Zeberg projects a primary scenario where Bitcoin rallies to $110,000–$120,000 in March, fueled by ETF inflows and risk-on sentiment.
+    A volatility flush to $62,920 triggered a massive short squeeze, resetting funding rates and clearing over-leveraged positions.
+    On-chain metrics place the current $60,000–$70K action in a historic accumulation band, despite fear persisting in the market.
+Bitcoin ETF Inflows Point to $110K–$120K: But Can It Last?
+Despite the recent chop, the institutional thesis remains aggressively bullish. Macro economist Henrik Zeberg has doubled down on a Bitcoin price prediction that sees the asset nearly doubling within weeks.
+    Portfolio Target Analysis – March 2026
+    Fundamental Perspectives to the Outlook and Targets of the Portfolio.
+    My Core Hypothesis
+    Bitcoin rallies to $110–120K in the primary scenario – fueled by Risk-On Fever, ETF inflows, and continued institutional adoption. There is a…
+    — Henrik Zeberg (@HenrikZeberg) March 1, 2026
+On March 1, Zeberg outlined a “primary scenario” targeting $110,000 to $120,000, representing an 80% upside from the recent lows around $66,000.
+    Bitcoin rallies to $110–120K in the primary scenario – fueled by Risk-On Fever, ETF inflows, and continued institutional adoption.
+    — Henrik Zeberg (@HenrikZeberg) March 1, 2026
+Zeberg attributes this potential surge to “Risk-On Fever” and relentless ETF demand. He even assigns a 25% probability to an overshoot scenario reaching $140,000 to $150,000.
+This aligns with data from Bernstein analysts led by Gautam Chhugani, who argue that the market is witnessing the “weakest bear case” in history due to banking adoption and pro-crypto policies under the Trump administration.
+Institutional infrastructure is rapidly catching up to these forecasts. For instance, Morgan Stanley applying for a national trust charter to hold clients’ crypto signals that major players are positioning for a long-term hold, reducing the floating supply available on exchanges.
+If these inflows sustain their current pace, the supply shock could validate Zeberg’s $120,000 target sooner than the derivatives market expects.
+Discover: The best new crypto on the market
+Bitcoin $62.9K Short Squeeze, and Why March is Critical
+The path to these highs, however, is being paved with volatility. Bitcoin dropped to $62,920 early last week on Feb 24. The dip punctured the rising support line, trapping late bears who piled in expecting a crash to $50,000.
+What followed was a textbook BTC short squeeze. As price reclaimed $65,000, short positions were forced to cover, driving the asset back up above $69,000 the following day.
+This flush mirrors the market dynamics seen recently, where Bitcoin rebounded after sudden geopolitical shocks erased $5K in 24 hours, proving the market’s resilience at these levels.
+The RSI on the daily chart has reset from overbought territory to a neutral 41, suggesting the market has room to run if buying pressure returns.
+Is Bitcoin’s March to $120k Possible?
+CoinMarketCap’s Fear &amp; Greed Index is currently set to “Extreme Fear” (15/100), a classic contrarian signal that often marks local bottoms.
+The divergence is clear: weak hands are selling the dip, while smart money treats the $60K floor as a gift. Key historic patterns suggest that post-halving corrections often end with this type of grinding consolidation before the markup phase resumes.
+The market is now coiled between two critical levels. The immediate resistance sits at $72,000. A clean break above this level confirms the end of the correction and opens the door to Zeberg’s $110,000 target.
+However, risks remain. If Bitcoin fails to hold the $60,000 support, the structure weakens significantly. Bearish voices like Jimmy Wales have famously argued against the asset’s long-term viability, and warnings that BTC could collapse below $10k should investors panic still circulate during downturns, though they look increasingly disconnected from the current institutional reality.
+Still, the odds may yet favor the bulls. The combination of political tailwinds from the expected passing of CLARITY, ETF inflows, and a completed leverage flush sets the stage for a march higher.
+Discover: The best pre-launch crypto sales
+Follow us on Google News</t>
+  </si>
+  <si>
     <t>Bitcoin Price Forecast: BTC steadies as bears shift focus toward $70,000</t>
   </si>
   <si>
@@ -369,6 +2040,49 @@
   </si>
   <si>
     <t>Says BTC is the lowest its been in years and that market sentiment is low. Also says people holding could be hurt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+fxstreet.com
+Will BTC slip toward the $70,000 level?
+Manish Chhetri
+8–10 minutes
+Bitcoin (BTC) price recovers slightly, trading above $76,000 at the time of writing on Wednesday, after reaching levels not seen since early November 2024 the previous day. The broader crypto market sentiment remains fragile, with derivatives traders staying defensive, signaling a hands-off approach amid a challenging environment of relative weakness. Traders should be cautious, despite a short-term recovery, as BTC’s long-term trend remains bearish, with bears targeting $70,000.
+US-Iran tensions escalate as an Iranian drone is shot down 
+Bitcoin price remains under pressure so far this week, with the Crypto King slipping below $73,000 on Tuesday for the first time since November 2024. The price dip in BTC was fueled as the news came in late Tuesday that the US military shot down an Iranian drone that “aggressively” approached the USS Abraham Lincoln aircraft carrier in the Arabian Sea. 
+“The incident occurred as tensions in the Middle East are high, with President Donald Trump weighing potential military strikes against the Islamic Republic,” reported CNBC.
+These developments have reduced investors’ risk appetite, despite President Trump’s special envoy, Steve Witkoff, is scheduled to meet with Iranian officials later this week.
+Following Tuesday’s incident, Iran has insisted that the talks take place in Oman rather than Turkey and that the scope be limited to two-way conversations on the nuclear issue only, complicating an already delicate diplomatic effort. 
+Market participants are closely monitoring developments in the US–Iran negotiations, as any signs of rising geopolitical tensions could trigger deeper corrections toward the riskier assets such as BTC.
+Derivatives traders remain defensive
+The K33 Research reported on Tuesday that Bitcoin traders on the Chicago Mercantile Exchange (CME) have remained defensive for months.
+The chart (left) below shows that the annualized BTC futures premium was holding steady at 6.3% on Tuesday, consistent with premiums observed over the past three months, signaling that traders remain largely hands-off amid the dicey environment of relative weakness. In addition, while futures premiums have been stable, the term structure continues to trend lower, with CME’s 7-day (right chart) average next-month premium currently at lows not seen since the US banking crisis of March 2023, pointing toward considerable reluctance to add calendar risk. 
+CME BTC and ETH Futures Annualized Rolling 1mth Basis (left chart). CME BTC Futures: Average Daily Next Month Premium (right chart). Source: K33 Research
+Vetle Lunde, Head of Research at K33 Research, noted that, “BTC is currently trading at a crucial area, near the March 2024 all-time high and the April 2025 support zone. If prices fall below this range, we are prepared to trim risk, as we would then anticipate downside momentum to accelerate.”
+Lunde further explained that Monday offered a few promising flashes in favor of a forming bottom. Trade volumes moved into the 90th percentile, and the perp regime flashed an even rarer extreme signal associated with past market lows, with leverage obliterated as yields turned deeply negative.
+“Still, both metrics offer limited reliability in isolation and may represent false flags. However, with both flashing while BTC remains above support, a bottom may have formed,” Lunde concluded. 
+Michael Burry warns BTC’s ongoing sell-off could hurt the corporations holding BTC
+Famous Wall Street trader Michael Burry, who bet on the 2008 housing market crash, warned that Bitcoin’s ongoing decline could destroy significant value, especially for companies holding large BTC reserves.
+Burry said, “Bitcoin has failed as a safe haven like Gold and could push aggressive corporate holders into bankruptcy, triggering broader market fallout,” reports Walter Bloomberg X post on Wednesday.
+As the largest corporate holder of Bitcoin, with 713,502 BTC in its reserves, Strategy (MSTR) stock price continued its correction, reaching a daily low of $126.74 on Tuesday, a decline of more than 70% from its 2025 high of $457.22. 
+With the upcoming earnings and revenue report on Thursday, investors remain on high alert, watching closely for any commentary on its Bitcoin strategy and balance-sheet exposure amid ongoing market volatility.
+MSTR weekly chart
+Meanwhile, the current NAV premium metric, which measures how much the market values the company relative to the net value of its Bitcoin holdings and other assets, excluding liabilities, reads -18.50% (0.81x), implying the market values MSTR at 81% of the value of its Bitcoin holdings per share (excluding other business value).
+This suggests that investors are currently unwilling to pay a premium for Strategy’s leveraged Bitcoin exposure, as concerns over dilution, rising debt costs, and Bitcoin’s recent price drop weigh on sentiment – making it harder for MSTR to raise low-cost capital for further BTC accumulation without pressuring shareholders.
+Bitcoin Price Forecast: BTC hits the lowest level since November 2024
+Bitcoin recovers slightly to trade near $76,000 at the time of writing on Wednesday after hitting a low of $72,945, a level not seen since early November 2024, the previous day. 
+The current market situation suggests a falling knife scenario. Traders should be cautious, as attempting to buy the dip remains risky, as the downside may not be complete yet.
+If BTC resumes its downward trend and closes below the daily support at $73,072 on a daily basis, it could extend the decline toward the key psychological level of $70,000.
+The Relative Strength Index (RSI) reads 26 on the daily chart, an oversold condition, indicating strong bearish momentum. The Moving Average Convergence Divergence (MACD) also showed a bearish crossover on January 20, which remains intact with rising red histogram bars below the neutral level, further supporting the negative outlook.
+BTC/USDT daily chart
+Meanwhile, market participants should keep a watch as the primary trend for BTC remains bearish, so any short-term recovery has a high probability of a dead-cat bounce — a brief price increase within a broader downtrend. 
+If BTC recovers, it could extend the advance toward the 61.8% Fibonacci retracement level (from the August 2024 low of $49,000 to the October 2025 all-time high of $126,199) at $78,490.
+Bitcoin, altcoins, stablecoins FAQs
+Bitcoin is the largest cryptocurrency by market capitalization, a virtual currency designed to serve as money. This form of payment cannot be controlled by any one person, group, or entity, which eliminates the need for third-party participation during financial transactions.
+Altcoins are any cryptocurrency apart from Bitcoin, but some also regard Ethereum as a non-altcoin because it is from these two cryptocurrencies that forking happens. If this is true, then Litecoin is the first altcoin, forked from the Bitcoin protocol and, therefore, an “improved” version of it.
+Stablecoins are cryptocurrencies designed to have a stable price, with their value backed by a reserve of the asset it represents. To achieve this, the value of any one stablecoin is pegged to a commodity or financial instrument, such as the US Dollar (USD), with its supply regulated by an algorithm or demand. The main goal of stablecoins is to provide an on/off-ramp for investors willing to trade and invest in cryptocurrencies. Stablecoins also allow investors to store value since cryptocurrencies, in general, are subject to volatility.
+Bitcoin dominance is the ratio of Bitcoin's market capitalization to the total market capitalization of all cryptocurrencies combined. It provides a clear picture of Bitcoin’s interest among investors. A high BTC dominance typically happens before and during a bull run, in which investors resort to investing in relatively stable and high market capitalization cryptocurrency like Bitcoin. A drop in BTC dominance usually means that investors are moving their capital and/or profits to altcoins in a quest for higher returns, which usually triggers an explosion of altcoin rallies.
+</t>
   </si>
 </sst>
 </file>
@@ -648,6 +2362,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="66.75"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -671,19 +2388,22 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3">
         <v>45231.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1">
         <v>1.0</v>
@@ -692,7 +2412,10 @@
         <v>4.0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -700,13 +2423,13 @@
         <v>45261.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>1.0</v>
@@ -715,7 +2438,10 @@
         <v>5.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -723,13 +2449,13 @@
         <v>45292.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1">
         <v>-1.0</v>
@@ -738,7 +2464,10 @@
         <v>2.0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -746,13 +2475,13 @@
         <v>45323.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>1.0</v>
@@ -761,7 +2490,10 @@
         <v>4.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -769,13 +2501,13 @@
         <v>45352.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1">
         <v>1.0</v>
@@ -784,7 +2516,10 @@
         <v>3.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -792,13 +2527,13 @@
         <v>45383.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1">
         <v>1.0</v>
@@ -807,7 +2542,10 @@
         <v>4.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -815,13 +2553,13 @@
         <v>45413.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E8" s="1">
         <v>1.0</v>
@@ -830,7 +2568,10 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -838,13 +2579,13 @@
         <v>45444.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1">
         <v>1.0</v>
@@ -853,7 +2594,10 @@
         <v>3.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -861,13 +2605,13 @@
         <v>45474.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1">
         <v>-1.0</v>
@@ -876,7 +2620,10 @@
         <v>4.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -884,13 +2631,13 @@
         <v>45505.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1">
         <v>0.0</v>
@@ -899,7 +2646,10 @@
         <v>2.0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -907,13 +2657,13 @@
         <v>45536.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1">
         <v>-1.0</v>
@@ -922,7 +2672,10 @@
         <v>4.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -930,13 +2683,13 @@
         <v>45566.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E13" s="1">
         <v>-1.0</v>
@@ -945,7 +2698,10 @@
         <v>2.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -953,13 +2709,13 @@
         <v>45597.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E14" s="1">
         <v>1.0</v>
@@ -968,7 +2724,10 @@
         <v>3.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -976,13 +2735,13 @@
         <v>45627.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1">
         <v>1.0</v>
@@ -991,7 +2750,10 @@
         <v>4.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>56</v>
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -999,13 +2761,13 @@
         <v>45658.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1">
         <v>1.0</v>
@@ -1014,7 +2776,10 @@
         <v>4.0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="17">
@@ -1022,13 +2787,13 @@
         <v>45689.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1">
         <v>1.0</v>
@@ -1037,7 +2802,10 @@
         <v>3.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -1045,13 +2813,13 @@
         <v>45717.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1">
         <v>-1.0</v>
@@ -1060,7 +2828,10 @@
         <v>4.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -1068,13 +2839,13 @@
         <v>45748.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E19" s="1">
         <v>1.0</v>
@@ -1083,7 +2854,10 @@
         <v>1.0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20">
@@ -1091,13 +2865,13 @@
         <v>45778.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E20" s="1">
         <v>1.0</v>
@@ -1106,7 +2880,10 @@
         <v>4.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>74</v>
+        <v>93</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21">
@@ -1114,13 +2891,13 @@
         <v>45809.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E21" s="1">
         <v>0.0</v>
@@ -1129,7 +2906,10 @@
         <v>2.0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>98</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="22">
@@ -1137,13 +2917,13 @@
         <v>45839.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E22" s="1">
         <v>1.0</v>
@@ -1152,7 +2932,10 @@
         <v>3.0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="23">
@@ -1160,13 +2943,13 @@
         <v>45870.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E23" s="1">
         <v>1.0</v>
@@ -1175,7 +2958,10 @@
         <v>4.0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -1183,13 +2969,13 @@
         <v>45901.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="E24" s="1">
         <v>-1.0</v>
@@ -1198,7 +2984,10 @@
         <v>4.0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="25">
@@ -1206,13 +2995,13 @@
         <v>45931.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="E25" s="1">
         <v>1.0</v>
@@ -1221,7 +3010,10 @@
         <v>2.0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>114</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="26">
@@ -1229,13 +3021,13 @@
         <v>45962.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E26" s="1">
         <v>1.0</v>
@@ -1244,7 +3036,10 @@
         <v>3.0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>118</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1252,13 +3047,13 @@
         <v>45992.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="E27" s="1">
         <v>-1.0</v>
@@ -1267,7 +3062,10 @@
         <v>3.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>96</v>
+        <v>122</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="28">
@@ -1275,13 +3073,13 @@
         <v>46023.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E28" s="1">
         <v>0.0</v>
@@ -1290,7 +3088,10 @@
         <v>2.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>99</v>
+        <v>126</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="29">
@@ -1298,13 +3099,13 @@
         <v>46054.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="E29" s="1">
         <v>-1.0</v>
@@ -1313,7 +3114,10 @@
         <v>4.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="30">
@@ -1321,13 +3125,13 @@
         <v>46082.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="E30" s="1">
         <v>0.0</v>
@@ -1336,7 +3140,10 @@
         <v>2.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>134</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="31">
@@ -1344,13 +3151,13 @@
         <v>46113.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E31" s="1">
         <v>-1.0</v>
@@ -1359,3884 +3166,4856 @@
         <v>3.0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="32">
       <c r="D32" s="6"/>
       <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33">
       <c r="D33" s="6"/>
       <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34">
       <c r="D34" s="6"/>
       <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35">
       <c r="D35" s="6"/>
       <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36">
       <c r="D36" s="6"/>
       <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37">
       <c r="D37" s="6"/>
       <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38">
       <c r="D38" s="6"/>
       <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39">
       <c r="D39" s="6"/>
       <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40">
       <c r="D40" s="6"/>
       <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41">
       <c r="D41" s="6"/>
       <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42">
       <c r="D42" s="6"/>
       <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43">
       <c r="D43" s="6"/>
       <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44">
       <c r="D44" s="6"/>
       <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45">
       <c r="D45" s="6"/>
       <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46">
       <c r="D46" s="6"/>
       <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47">
       <c r="D47" s="6"/>
       <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48">
       <c r="D48" s="6"/>
       <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49">
       <c r="D49" s="6"/>
       <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50">
       <c r="D50" s="6"/>
       <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51">
       <c r="D51" s="6"/>
       <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52">
       <c r="D52" s="6"/>
       <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53">
       <c r="D53" s="6"/>
       <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54">
       <c r="D54" s="6"/>
       <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55">
       <c r="D55" s="6"/>
       <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56">
       <c r="D56" s="6"/>
       <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
     </row>
     <row r="57">
       <c r="D57" s="6"/>
       <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
     </row>
     <row r="58">
       <c r="D58" s="6"/>
       <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59">
       <c r="D59" s="6"/>
       <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
     </row>
     <row r="60">
       <c r="D60" s="6"/>
       <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61">
       <c r="D61" s="6"/>
       <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62">
       <c r="D62" s="6"/>
       <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63">
       <c r="D63" s="6"/>
       <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64">
       <c r="D64" s="6"/>
       <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
     </row>
     <row r="65">
       <c r="D65" s="6"/>
       <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
     </row>
     <row r="66">
       <c r="D66" s="6"/>
       <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67">
       <c r="D67" s="6"/>
       <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68">
       <c r="D68" s="6"/>
       <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69">
       <c r="D69" s="6"/>
       <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
     </row>
     <row r="70">
       <c r="D70" s="6"/>
       <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71">
       <c r="D71" s="6"/>
       <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72">
       <c r="D72" s="6"/>
       <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
     </row>
     <row r="73">
       <c r="D73" s="6"/>
       <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
     </row>
     <row r="74">
       <c r="D74" s="6"/>
       <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
     </row>
     <row r="75">
       <c r="D75" s="6"/>
       <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76">
       <c r="D76" s="6"/>
       <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
     </row>
     <row r="77">
       <c r="D77" s="6"/>
       <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
     </row>
     <row r="78">
       <c r="D78" s="6"/>
       <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
     </row>
     <row r="79">
       <c r="D79" s="6"/>
       <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
     </row>
     <row r="80">
       <c r="D80" s="6"/>
       <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
     </row>
     <row r="81">
       <c r="D81" s="6"/>
       <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
     </row>
     <row r="82">
       <c r="D82" s="6"/>
       <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
     </row>
     <row r="83">
       <c r="D83" s="6"/>
       <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
     </row>
     <row r="84">
       <c r="D84" s="6"/>
       <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
     </row>
     <row r="85">
       <c r="D85" s="6"/>
       <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
     </row>
     <row r="86">
       <c r="D86" s="6"/>
       <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
     </row>
     <row r="87">
       <c r="D87" s="6"/>
       <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
     </row>
     <row r="88">
       <c r="D88" s="6"/>
       <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
     </row>
     <row r="89">
       <c r="D89" s="6"/>
       <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
     </row>
     <row r="90">
       <c r="D90" s="6"/>
       <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
     </row>
     <row r="91">
       <c r="D91" s="6"/>
       <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
     </row>
     <row r="92">
       <c r="D92" s="6"/>
       <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
     </row>
     <row r="93">
       <c r="D93" s="6"/>
       <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
     </row>
     <row r="94">
       <c r="D94" s="6"/>
       <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
     </row>
     <row r="95">
       <c r="D95" s="6"/>
       <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
     </row>
     <row r="96">
       <c r="D96" s="6"/>
       <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
     </row>
     <row r="97">
       <c r="D97" s="6"/>
       <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
     </row>
     <row r="98">
       <c r="D98" s="6"/>
       <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
     </row>
     <row r="99">
       <c r="D99" s="6"/>
       <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
     </row>
     <row r="100">
       <c r="D100" s="6"/>
       <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
     </row>
     <row r="101">
       <c r="D101" s="6"/>
       <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
     </row>
     <row r="102">
       <c r="D102" s="6"/>
       <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
     </row>
     <row r="103">
       <c r="D103" s="6"/>
       <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
     </row>
     <row r="104">
       <c r="D104" s="6"/>
       <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
     </row>
     <row r="105">
       <c r="D105" s="6"/>
       <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
     </row>
     <row r="106">
       <c r="D106" s="6"/>
       <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
     </row>
     <row r="107">
       <c r="D107" s="6"/>
       <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
     </row>
     <row r="108">
       <c r="D108" s="6"/>
       <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
     </row>
     <row r="109">
       <c r="D109" s="6"/>
       <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
     </row>
     <row r="110">
       <c r="D110" s="6"/>
       <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
     </row>
     <row r="111">
       <c r="D111" s="6"/>
       <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
     </row>
     <row r="112">
       <c r="D112" s="6"/>
       <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
     </row>
     <row r="113">
       <c r="D113" s="6"/>
       <c r="G113" s="6"/>
+      <c r="H113" s="6"/>
     </row>
     <row r="114">
       <c r="D114" s="6"/>
       <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
     </row>
     <row r="115">
       <c r="D115" s="6"/>
       <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
     </row>
     <row r="116">
       <c r="D116" s="6"/>
       <c r="G116" s="6"/>
+      <c r="H116" s="6"/>
     </row>
     <row r="117">
       <c r="D117" s="6"/>
       <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
     </row>
     <row r="118">
       <c r="D118" s="6"/>
       <c r="G118" s="6"/>
+      <c r="H118" s="6"/>
     </row>
     <row r="119">
       <c r="D119" s="6"/>
       <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
     </row>
     <row r="120">
       <c r="D120" s="6"/>
       <c r="G120" s="6"/>
+      <c r="H120" s="6"/>
     </row>
     <row r="121">
       <c r="D121" s="6"/>
       <c r="G121" s="6"/>
+      <c r="H121" s="6"/>
     </row>
     <row r="122">
       <c r="D122" s="6"/>
       <c r="G122" s="6"/>
+      <c r="H122" s="6"/>
     </row>
     <row r="123">
       <c r="D123" s="6"/>
       <c r="G123" s="6"/>
+      <c r="H123" s="6"/>
     </row>
     <row r="124">
       <c r="D124" s="6"/>
       <c r="G124" s="6"/>
+      <c r="H124" s="6"/>
     </row>
     <row r="125">
       <c r="D125" s="6"/>
       <c r="G125" s="6"/>
+      <c r="H125" s="6"/>
     </row>
     <row r="126">
       <c r="D126" s="6"/>
       <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
     </row>
     <row r="127">
       <c r="D127" s="6"/>
       <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
     </row>
     <row r="128">
       <c r="D128" s="6"/>
       <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
     </row>
     <row r="129">
       <c r="D129" s="6"/>
       <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
     </row>
     <row r="130">
       <c r="D130" s="6"/>
       <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
     </row>
     <row r="131">
       <c r="D131" s="6"/>
       <c r="G131" s="6"/>
+      <c r="H131" s="6"/>
     </row>
     <row r="132">
       <c r="D132" s="6"/>
       <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
     </row>
     <row r="133">
       <c r="D133" s="6"/>
       <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
     </row>
     <row r="134">
       <c r="D134" s="6"/>
       <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
     </row>
     <row r="135">
       <c r="D135" s="6"/>
       <c r="G135" s="6"/>
+      <c r="H135" s="6"/>
     </row>
     <row r="136">
       <c r="D136" s="6"/>
       <c r="G136" s="6"/>
+      <c r="H136" s="6"/>
     </row>
     <row r="137">
       <c r="D137" s="6"/>
       <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
     </row>
     <row r="138">
       <c r="D138" s="6"/>
       <c r="G138" s="6"/>
+      <c r="H138" s="6"/>
     </row>
     <row r="139">
       <c r="D139" s="6"/>
       <c r="G139" s="6"/>
+      <c r="H139" s="6"/>
     </row>
     <row r="140">
       <c r="D140" s="6"/>
       <c r="G140" s="6"/>
+      <c r="H140" s="6"/>
     </row>
     <row r="141">
       <c r="D141" s="6"/>
       <c r="G141" s="6"/>
+      <c r="H141" s="6"/>
     </row>
     <row r="142">
       <c r="D142" s="6"/>
       <c r="G142" s="6"/>
+      <c r="H142" s="6"/>
     </row>
     <row r="143">
       <c r="D143" s="6"/>
       <c r="G143" s="6"/>
+      <c r="H143" s="6"/>
     </row>
     <row r="144">
       <c r="D144" s="6"/>
       <c r="G144" s="6"/>
+      <c r="H144" s="6"/>
     </row>
     <row r="145">
       <c r="D145" s="6"/>
       <c r="G145" s="6"/>
+      <c r="H145" s="6"/>
     </row>
     <row r="146">
       <c r="D146" s="6"/>
       <c r="G146" s="6"/>
+      <c r="H146" s="6"/>
     </row>
     <row r="147">
       <c r="D147" s="6"/>
       <c r="G147" s="6"/>
+      <c r="H147" s="6"/>
     </row>
     <row r="148">
       <c r="D148" s="6"/>
       <c r="G148" s="6"/>
+      <c r="H148" s="6"/>
     </row>
     <row r="149">
       <c r="D149" s="6"/>
       <c r="G149" s="6"/>
+      <c r="H149" s="6"/>
     </row>
     <row r="150">
       <c r="D150" s="6"/>
       <c r="G150" s="6"/>
+      <c r="H150" s="6"/>
     </row>
     <row r="151">
       <c r="D151" s="6"/>
       <c r="G151" s="6"/>
+      <c r="H151" s="6"/>
     </row>
     <row r="152">
       <c r="D152" s="6"/>
       <c r="G152" s="6"/>
+      <c r="H152" s="6"/>
     </row>
     <row r="153">
       <c r="D153" s="6"/>
       <c r="G153" s="6"/>
+      <c r="H153" s="6"/>
     </row>
     <row r="154">
       <c r="D154" s="6"/>
       <c r="G154" s="6"/>
+      <c r="H154" s="6"/>
     </row>
     <row r="155">
       <c r="D155" s="6"/>
       <c r="G155" s="6"/>
+      <c r="H155" s="6"/>
     </row>
     <row r="156">
       <c r="D156" s="6"/>
       <c r="G156" s="6"/>
+      <c r="H156" s="6"/>
     </row>
     <row r="157">
       <c r="D157" s="6"/>
       <c r="G157" s="6"/>
+      <c r="H157" s="6"/>
     </row>
     <row r="158">
       <c r="D158" s="6"/>
       <c r="G158" s="6"/>
+      <c r="H158" s="6"/>
     </row>
     <row r="159">
       <c r="D159" s="6"/>
       <c r="G159" s="6"/>
+      <c r="H159" s="6"/>
     </row>
     <row r="160">
       <c r="D160" s="6"/>
       <c r="G160" s="6"/>
+      <c r="H160" s="6"/>
     </row>
     <row r="161">
       <c r="D161" s="6"/>
       <c r="G161" s="6"/>
+      <c r="H161" s="6"/>
     </row>
     <row r="162">
       <c r="D162" s="6"/>
       <c r="G162" s="6"/>
+      <c r="H162" s="6"/>
     </row>
     <row r="163">
       <c r="D163" s="6"/>
       <c r="G163" s="6"/>
+      <c r="H163" s="6"/>
     </row>
     <row r="164">
       <c r="D164" s="6"/>
       <c r="G164" s="6"/>
+      <c r="H164" s="6"/>
     </row>
     <row r="165">
       <c r="D165" s="6"/>
       <c r="G165" s="6"/>
+      <c r="H165" s="6"/>
     </row>
     <row r="166">
       <c r="D166" s="6"/>
       <c r="G166" s="6"/>
+      <c r="H166" s="6"/>
     </row>
     <row r="167">
       <c r="D167" s="6"/>
       <c r="G167" s="6"/>
+      <c r="H167" s="6"/>
     </row>
     <row r="168">
       <c r="D168" s="6"/>
       <c r="G168" s="6"/>
+      <c r="H168" s="6"/>
     </row>
     <row r="169">
       <c r="D169" s="6"/>
       <c r="G169" s="6"/>
+      <c r="H169" s="6"/>
     </row>
     <row r="170">
       <c r="D170" s="6"/>
       <c r="G170" s="6"/>
+      <c r="H170" s="6"/>
     </row>
     <row r="171">
       <c r="D171" s="6"/>
       <c r="G171" s="6"/>
+      <c r="H171" s="6"/>
     </row>
     <row r="172">
       <c r="D172" s="6"/>
       <c r="G172" s="6"/>
+      <c r="H172" s="6"/>
     </row>
     <row r="173">
       <c r="D173" s="6"/>
       <c r="G173" s="6"/>
+      <c r="H173" s="6"/>
     </row>
     <row r="174">
       <c r="D174" s="6"/>
       <c r="G174" s="6"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175">
       <c r="D175" s="6"/>
       <c r="G175" s="6"/>
+      <c r="H175" s="6"/>
     </row>
     <row r="176">
       <c r="D176" s="6"/>
       <c r="G176" s="6"/>
+      <c r="H176" s="6"/>
     </row>
     <row r="177">
       <c r="D177" s="6"/>
       <c r="G177" s="6"/>
+      <c r="H177" s="6"/>
     </row>
     <row r="178">
       <c r="D178" s="6"/>
       <c r="G178" s="6"/>
+      <c r="H178" s="6"/>
     </row>
     <row r="179">
       <c r="D179" s="6"/>
       <c r="G179" s="6"/>
+      <c r="H179" s="6"/>
     </row>
     <row r="180">
       <c r="D180" s="6"/>
       <c r="G180" s="6"/>
+      <c r="H180" s="6"/>
     </row>
     <row r="181">
       <c r="D181" s="6"/>
       <c r="G181" s="6"/>
+      <c r="H181" s="6"/>
     </row>
     <row r="182">
       <c r="D182" s="6"/>
       <c r="G182" s="6"/>
+      <c r="H182" s="6"/>
     </row>
     <row r="183">
       <c r="D183" s="6"/>
       <c r="G183" s="6"/>
+      <c r="H183" s="6"/>
     </row>
     <row r="184">
       <c r="D184" s="6"/>
       <c r="G184" s="6"/>
+      <c r="H184" s="6"/>
     </row>
     <row r="185">
       <c r="D185" s="6"/>
       <c r="G185" s="6"/>
+      <c r="H185" s="6"/>
     </row>
     <row r="186">
       <c r="D186" s="6"/>
       <c r="G186" s="6"/>
+      <c r="H186" s="6"/>
     </row>
     <row r="187">
       <c r="D187" s="6"/>
       <c r="G187" s="6"/>
+      <c r="H187" s="6"/>
     </row>
     <row r="188">
       <c r="D188" s="6"/>
       <c r="G188" s="6"/>
+      <c r="H188" s="6"/>
     </row>
     <row r="189">
       <c r="D189" s="6"/>
       <c r="G189" s="6"/>
+      <c r="H189" s="6"/>
     </row>
     <row r="190">
       <c r="D190" s="6"/>
       <c r="G190" s="6"/>
+      <c r="H190" s="6"/>
     </row>
     <row r="191">
       <c r="D191" s="6"/>
       <c r="G191" s="6"/>
+      <c r="H191" s="6"/>
     </row>
     <row r="192">
       <c r="D192" s="6"/>
       <c r="G192" s="6"/>
+      <c r="H192" s="6"/>
     </row>
     <row r="193">
       <c r="D193" s="6"/>
       <c r="G193" s="6"/>
+      <c r="H193" s="6"/>
     </row>
     <row r="194">
       <c r="D194" s="6"/>
       <c r="G194" s="6"/>
+      <c r="H194" s="6"/>
     </row>
     <row r="195">
       <c r="D195" s="6"/>
       <c r="G195" s="6"/>
+      <c r="H195" s="6"/>
     </row>
     <row r="196">
       <c r="D196" s="6"/>
       <c r="G196" s="6"/>
+      <c r="H196" s="6"/>
     </row>
     <row r="197">
       <c r="D197" s="6"/>
       <c r="G197" s="6"/>
+      <c r="H197" s="6"/>
     </row>
     <row r="198">
       <c r="D198" s="6"/>
       <c r="G198" s="6"/>
+      <c r="H198" s="6"/>
     </row>
     <row r="199">
       <c r="D199" s="6"/>
       <c r="G199" s="6"/>
+      <c r="H199" s="6"/>
     </row>
     <row r="200">
       <c r="D200" s="6"/>
       <c r="G200" s="6"/>
+      <c r="H200" s="6"/>
     </row>
     <row r="201">
       <c r="D201" s="6"/>
       <c r="G201" s="6"/>
+      <c r="H201" s="6"/>
     </row>
     <row r="202">
       <c r="D202" s="6"/>
       <c r="G202" s="6"/>
+      <c r="H202" s="6"/>
     </row>
     <row r="203">
       <c r="D203" s="6"/>
       <c r="G203" s="6"/>
+      <c r="H203" s="6"/>
     </row>
     <row r="204">
       <c r="D204" s="6"/>
       <c r="G204" s="6"/>
+      <c r="H204" s="6"/>
     </row>
     <row r="205">
       <c r="D205" s="6"/>
       <c r="G205" s="6"/>
+      <c r="H205" s="6"/>
     </row>
     <row r="206">
       <c r="D206" s="6"/>
       <c r="G206" s="6"/>
+      <c r="H206" s="6"/>
     </row>
     <row r="207">
       <c r="D207" s="6"/>
       <c r="G207" s="6"/>
+      <c r="H207" s="6"/>
     </row>
     <row r="208">
       <c r="D208" s="6"/>
       <c r="G208" s="6"/>
+      <c r="H208" s="6"/>
     </row>
     <row r="209">
       <c r="D209" s="6"/>
       <c r="G209" s="6"/>
+      <c r="H209" s="6"/>
     </row>
     <row r="210">
       <c r="D210" s="6"/>
       <c r="G210" s="6"/>
+      <c r="H210" s="6"/>
     </row>
     <row r="211">
       <c r="D211" s="6"/>
       <c r="G211" s="6"/>
+      <c r="H211" s="6"/>
     </row>
     <row r="212">
       <c r="D212" s="6"/>
       <c r="G212" s="6"/>
+      <c r="H212" s="6"/>
     </row>
     <row r="213">
       <c r="D213" s="6"/>
       <c r="G213" s="6"/>
+      <c r="H213" s="6"/>
     </row>
     <row r="214">
       <c r="D214" s="6"/>
       <c r="G214" s="6"/>
+      <c r="H214" s="6"/>
     </row>
     <row r="215">
       <c r="D215" s="6"/>
       <c r="G215" s="6"/>
+      <c r="H215" s="6"/>
     </row>
     <row r="216">
       <c r="D216" s="6"/>
       <c r="G216" s="6"/>
+      <c r="H216" s="6"/>
     </row>
     <row r="217">
       <c r="D217" s="6"/>
       <c r="G217" s="6"/>
+      <c r="H217" s="6"/>
     </row>
     <row r="218">
       <c r="D218" s="6"/>
       <c r="G218" s="6"/>
+      <c r="H218" s="6"/>
     </row>
     <row r="219">
       <c r="D219" s="6"/>
       <c r="G219" s="6"/>
+      <c r="H219" s="6"/>
     </row>
     <row r="220">
       <c r="D220" s="6"/>
       <c r="G220" s="6"/>
+      <c r="H220" s="6"/>
     </row>
     <row r="221">
       <c r="D221" s="6"/>
       <c r="G221" s="6"/>
+      <c r="H221" s="6"/>
     </row>
     <row r="222">
       <c r="D222" s="6"/>
       <c r="G222" s="6"/>
+      <c r="H222" s="6"/>
     </row>
     <row r="223">
       <c r="D223" s="6"/>
       <c r="G223" s="6"/>
+      <c r="H223" s="6"/>
     </row>
     <row r="224">
       <c r="D224" s="6"/>
       <c r="G224" s="6"/>
+      <c r="H224" s="6"/>
     </row>
     <row r="225">
       <c r="D225" s="6"/>
       <c r="G225" s="6"/>
+      <c r="H225" s="6"/>
     </row>
     <row r="226">
       <c r="D226" s="6"/>
       <c r="G226" s="6"/>
+      <c r="H226" s="6"/>
     </row>
     <row r="227">
       <c r="D227" s="6"/>
       <c r="G227" s="6"/>
+      <c r="H227" s="6"/>
     </row>
     <row r="228">
       <c r="D228" s="6"/>
       <c r="G228" s="6"/>
+      <c r="H228" s="6"/>
     </row>
     <row r="229">
       <c r="D229" s="6"/>
       <c r="G229" s="6"/>
+      <c r="H229" s="6"/>
     </row>
     <row r="230">
       <c r="D230" s="6"/>
       <c r="G230" s="6"/>
+      <c r="H230" s="6"/>
     </row>
     <row r="231">
       <c r="D231" s="6"/>
       <c r="G231" s="6"/>
+      <c r="H231" s="6"/>
     </row>
     <row r="232">
       <c r="D232" s="6"/>
       <c r="G232" s="6"/>
+      <c r="H232" s="6"/>
     </row>
     <row r="233">
       <c r="D233" s="6"/>
       <c r="G233" s="6"/>
+      <c r="H233" s="6"/>
     </row>
     <row r="234">
       <c r="D234" s="6"/>
       <c r="G234" s="6"/>
+      <c r="H234" s="6"/>
     </row>
     <row r="235">
       <c r="D235" s="6"/>
       <c r="G235" s="6"/>
+      <c r="H235" s="6"/>
     </row>
     <row r="236">
       <c r="D236" s="6"/>
       <c r="G236" s="6"/>
+      <c r="H236" s="6"/>
     </row>
     <row r="237">
       <c r="D237" s="6"/>
       <c r="G237" s="6"/>
+      <c r="H237" s="6"/>
     </row>
     <row r="238">
       <c r="D238" s="6"/>
       <c r="G238" s="6"/>
+      <c r="H238" s="6"/>
     </row>
     <row r="239">
       <c r="D239" s="6"/>
       <c r="G239" s="6"/>
+      <c r="H239" s="6"/>
     </row>
     <row r="240">
       <c r="D240" s="6"/>
       <c r="G240" s="6"/>
+      <c r="H240" s="6"/>
     </row>
     <row r="241">
       <c r="D241" s="6"/>
       <c r="G241" s="6"/>
+      <c r="H241" s="6"/>
     </row>
     <row r="242">
       <c r="D242" s="6"/>
       <c r="G242" s="6"/>
+      <c r="H242" s="6"/>
     </row>
     <row r="243">
       <c r="D243" s="6"/>
       <c r="G243" s="6"/>
+      <c r="H243" s="6"/>
     </row>
     <row r="244">
       <c r="D244" s="6"/>
       <c r="G244" s="6"/>
+      <c r="H244" s="6"/>
     </row>
     <row r="245">
       <c r="D245" s="6"/>
       <c r="G245" s="6"/>
+      <c r="H245" s="6"/>
     </row>
     <row r="246">
       <c r="D246" s="6"/>
       <c r="G246" s="6"/>
+      <c r="H246" s="6"/>
     </row>
     <row r="247">
       <c r="D247" s="6"/>
       <c r="G247" s="6"/>
+      <c r="H247" s="6"/>
     </row>
     <row r="248">
       <c r="D248" s="6"/>
       <c r="G248" s="6"/>
+      <c r="H248" s="6"/>
     </row>
     <row r="249">
       <c r="D249" s="6"/>
       <c r="G249" s="6"/>
+      <c r="H249" s="6"/>
     </row>
     <row r="250">
       <c r="D250" s="6"/>
       <c r="G250" s="6"/>
+      <c r="H250" s="6"/>
     </row>
     <row r="251">
       <c r="D251" s="6"/>
       <c r="G251" s="6"/>
+      <c r="H251" s="6"/>
     </row>
     <row r="252">
       <c r="D252" s="6"/>
       <c r="G252" s="6"/>
+      <c r="H252" s="6"/>
     </row>
     <row r="253">
       <c r="D253" s="6"/>
       <c r="G253" s="6"/>
+      <c r="H253" s="6"/>
     </row>
     <row r="254">
       <c r="D254" s="6"/>
       <c r="G254" s="6"/>
+      <c r="H254" s="6"/>
     </row>
     <row r="255">
       <c r="D255" s="6"/>
       <c r="G255" s="6"/>
+      <c r="H255" s="6"/>
     </row>
     <row r="256">
       <c r="D256" s="6"/>
       <c r="G256" s="6"/>
+      <c r="H256" s="6"/>
     </row>
     <row r="257">
       <c r="D257" s="6"/>
       <c r="G257" s="6"/>
+      <c r="H257" s="6"/>
     </row>
     <row r="258">
       <c r="D258" s="6"/>
       <c r="G258" s="6"/>
+      <c r="H258" s="6"/>
     </row>
     <row r="259">
       <c r="D259" s="6"/>
       <c r="G259" s="6"/>
+      <c r="H259" s="6"/>
     </row>
     <row r="260">
       <c r="D260" s="6"/>
       <c r="G260" s="6"/>
+      <c r="H260" s="6"/>
     </row>
     <row r="261">
       <c r="D261" s="6"/>
       <c r="G261" s="6"/>
+      <c r="H261" s="6"/>
     </row>
     <row r="262">
       <c r="D262" s="6"/>
       <c r="G262" s="6"/>
+      <c r="H262" s="6"/>
     </row>
     <row r="263">
       <c r="D263" s="6"/>
       <c r="G263" s="6"/>
+      <c r="H263" s="6"/>
     </row>
     <row r="264">
       <c r="D264" s="6"/>
       <c r="G264" s="6"/>
+      <c r="H264" s="6"/>
     </row>
     <row r="265">
       <c r="D265" s="6"/>
       <c r="G265" s="6"/>
+      <c r="H265" s="6"/>
     </row>
     <row r="266">
       <c r="D266" s="6"/>
       <c r="G266" s="6"/>
+      <c r="H266" s="6"/>
     </row>
     <row r="267">
       <c r="D267" s="6"/>
       <c r="G267" s="6"/>
+      <c r="H267" s="6"/>
     </row>
     <row r="268">
       <c r="D268" s="6"/>
       <c r="G268" s="6"/>
+      <c r="H268" s="6"/>
     </row>
     <row r="269">
       <c r="D269" s="6"/>
       <c r="G269" s="6"/>
+      <c r="H269" s="6"/>
     </row>
     <row r="270">
       <c r="D270" s="6"/>
       <c r="G270" s="6"/>
+      <c r="H270" s="6"/>
     </row>
     <row r="271">
       <c r="D271" s="6"/>
       <c r="G271" s="6"/>
+      <c r="H271" s="6"/>
     </row>
     <row r="272">
       <c r="D272" s="6"/>
       <c r="G272" s="6"/>
+      <c r="H272" s="6"/>
     </row>
     <row r="273">
       <c r="D273" s="6"/>
       <c r="G273" s="6"/>
+      <c r="H273" s="6"/>
     </row>
     <row r="274">
       <c r="D274" s="6"/>
       <c r="G274" s="6"/>
+      <c r="H274" s="6"/>
     </row>
     <row r="275">
       <c r="D275" s="6"/>
       <c r="G275" s="6"/>
+      <c r="H275" s="6"/>
     </row>
     <row r="276">
       <c r="D276" s="6"/>
       <c r="G276" s="6"/>
+      <c r="H276" s="6"/>
     </row>
     <row r="277">
       <c r="D277" s="6"/>
       <c r="G277" s="6"/>
+      <c r="H277" s="6"/>
     </row>
     <row r="278">
       <c r="D278" s="6"/>
       <c r="G278" s="6"/>
+      <c r="H278" s="6"/>
     </row>
     <row r="279">
       <c r="D279" s="6"/>
       <c r="G279" s="6"/>
+      <c r="H279" s="6"/>
     </row>
     <row r="280">
       <c r="D280" s="6"/>
       <c r="G280" s="6"/>
+      <c r="H280" s="6"/>
     </row>
     <row r="281">
       <c r="D281" s="6"/>
       <c r="G281" s="6"/>
+      <c r="H281" s="6"/>
     </row>
     <row r="282">
       <c r="D282" s="6"/>
       <c r="G282" s="6"/>
+      <c r="H282" s="6"/>
     </row>
     <row r="283">
       <c r="D283" s="6"/>
       <c r="G283" s="6"/>
+      <c r="H283" s="6"/>
     </row>
     <row r="284">
       <c r="D284" s="6"/>
       <c r="G284" s="6"/>
+      <c r="H284" s="6"/>
     </row>
     <row r="285">
       <c r="D285" s="6"/>
       <c r="G285" s="6"/>
+      <c r="H285" s="6"/>
     </row>
     <row r="286">
       <c r="D286" s="6"/>
       <c r="G286" s="6"/>
+      <c r="H286" s="6"/>
     </row>
     <row r="287">
       <c r="D287" s="6"/>
       <c r="G287" s="6"/>
+      <c r="H287" s="6"/>
     </row>
     <row r="288">
       <c r="D288" s="6"/>
       <c r="G288" s="6"/>
+      <c r="H288" s="6"/>
     </row>
     <row r="289">
       <c r="D289" s="6"/>
       <c r="G289" s="6"/>
+      <c r="H289" s="6"/>
     </row>
     <row r="290">
       <c r="D290" s="6"/>
       <c r="G290" s="6"/>
+      <c r="H290" s="6"/>
     </row>
     <row r="291">
       <c r="D291" s="6"/>
       <c r="G291" s="6"/>
+      <c r="H291" s="6"/>
     </row>
     <row r="292">
       <c r="D292" s="6"/>
       <c r="G292" s="6"/>
+      <c r="H292" s="6"/>
     </row>
     <row r="293">
       <c r="D293" s="6"/>
       <c r="G293" s="6"/>
+      <c r="H293" s="6"/>
     </row>
     <row r="294">
       <c r="D294" s="6"/>
       <c r="G294" s="6"/>
+      <c r="H294" s="6"/>
     </row>
     <row r="295">
       <c r="D295" s="6"/>
       <c r="G295" s="6"/>
+      <c r="H295" s="6"/>
     </row>
     <row r="296">
       <c r="D296" s="6"/>
       <c r="G296" s="6"/>
+      <c r="H296" s="6"/>
     </row>
     <row r="297">
       <c r="D297" s="6"/>
       <c r="G297" s="6"/>
+      <c r="H297" s="6"/>
     </row>
     <row r="298">
       <c r="D298" s="6"/>
       <c r="G298" s="6"/>
+      <c r="H298" s="6"/>
     </row>
     <row r="299">
       <c r="D299" s="6"/>
       <c r="G299" s="6"/>
+      <c r="H299" s="6"/>
     </row>
     <row r="300">
       <c r="D300" s="6"/>
       <c r="G300" s="6"/>
+      <c r="H300" s="6"/>
     </row>
     <row r="301">
       <c r="D301" s="6"/>
       <c r="G301" s="6"/>
+      <c r="H301" s="6"/>
     </row>
     <row r="302">
       <c r="D302" s="6"/>
       <c r="G302" s="6"/>
+      <c r="H302" s="6"/>
     </row>
     <row r="303">
       <c r="D303" s="6"/>
       <c r="G303" s="6"/>
+      <c r="H303" s="6"/>
     </row>
     <row r="304">
       <c r="D304" s="6"/>
       <c r="G304" s="6"/>
+      <c r="H304" s="6"/>
     </row>
     <row r="305">
       <c r="D305" s="6"/>
       <c r="G305" s="6"/>
+      <c r="H305" s="6"/>
     </row>
     <row r="306">
       <c r="D306" s="6"/>
       <c r="G306" s="6"/>
+      <c r="H306" s="6"/>
     </row>
     <row r="307">
       <c r="D307" s="6"/>
       <c r="G307" s="6"/>
+      <c r="H307" s="6"/>
     </row>
     <row r="308">
       <c r="D308" s="6"/>
       <c r="G308" s="6"/>
+      <c r="H308" s="6"/>
     </row>
     <row r="309">
       <c r="D309" s="6"/>
       <c r="G309" s="6"/>
+      <c r="H309" s="6"/>
     </row>
     <row r="310">
       <c r="D310" s="6"/>
       <c r="G310" s="6"/>
+      <c r="H310" s="6"/>
     </row>
     <row r="311">
       <c r="D311" s="6"/>
       <c r="G311" s="6"/>
+      <c r="H311" s="6"/>
     </row>
     <row r="312">
       <c r="D312" s="6"/>
       <c r="G312" s="6"/>
+      <c r="H312" s="6"/>
     </row>
     <row r="313">
       <c r="D313" s="6"/>
       <c r="G313" s="6"/>
+      <c r="H313" s="6"/>
     </row>
     <row r="314">
       <c r="D314" s="6"/>
       <c r="G314" s="6"/>
+      <c r="H314" s="6"/>
     </row>
     <row r="315">
       <c r="D315" s="6"/>
       <c r="G315" s="6"/>
+      <c r="H315" s="6"/>
     </row>
     <row r="316">
       <c r="D316" s="6"/>
       <c r="G316" s="6"/>
+      <c r="H316" s="6"/>
     </row>
     <row r="317">
       <c r="D317" s="6"/>
       <c r="G317" s="6"/>
+      <c r="H317" s="6"/>
     </row>
     <row r="318">
       <c r="D318" s="6"/>
       <c r="G318" s="6"/>
+      <c r="H318" s="6"/>
     </row>
     <row r="319">
       <c r="D319" s="6"/>
       <c r="G319" s="6"/>
+      <c r="H319" s="6"/>
     </row>
     <row r="320">
       <c r="D320" s="6"/>
       <c r="G320" s="6"/>
+      <c r="H320" s="6"/>
     </row>
     <row r="321">
       <c r="D321" s="6"/>
       <c r="G321" s="6"/>
+      <c r="H321" s="6"/>
     </row>
     <row r="322">
       <c r="D322" s="6"/>
       <c r="G322" s="6"/>
+      <c r="H322" s="6"/>
     </row>
     <row r="323">
       <c r="D323" s="6"/>
       <c r="G323" s="6"/>
+      <c r="H323" s="6"/>
     </row>
     <row r="324">
       <c r="D324" s="6"/>
       <c r="G324" s="6"/>
+      <c r="H324" s="6"/>
     </row>
     <row r="325">
       <c r="D325" s="6"/>
       <c r="G325" s="6"/>
+      <c r="H325" s="6"/>
     </row>
     <row r="326">
       <c r="D326" s="6"/>
       <c r="G326" s="6"/>
+      <c r="H326" s="6"/>
     </row>
     <row r="327">
       <c r="D327" s="6"/>
       <c r="G327" s="6"/>
+      <c r="H327" s="6"/>
     </row>
     <row r="328">
       <c r="D328" s="6"/>
       <c r="G328" s="6"/>
+      <c r="H328" s="6"/>
     </row>
     <row r="329">
       <c r="D329" s="6"/>
       <c r="G329" s="6"/>
+      <c r="H329" s="6"/>
     </row>
     <row r="330">
       <c r="D330" s="6"/>
       <c r="G330" s="6"/>
+      <c r="H330" s="6"/>
     </row>
     <row r="331">
       <c r="D331" s="6"/>
       <c r="G331" s="6"/>
+      <c r="H331" s="6"/>
     </row>
     <row r="332">
       <c r="D332" s="6"/>
       <c r="G332" s="6"/>
+      <c r="H332" s="6"/>
     </row>
     <row r="333">
       <c r="D333" s="6"/>
       <c r="G333" s="6"/>
+      <c r="H333" s="6"/>
     </row>
     <row r="334">
       <c r="D334" s="6"/>
       <c r="G334" s="6"/>
+      <c r="H334" s="6"/>
     </row>
     <row r="335">
       <c r="D335" s="6"/>
       <c r="G335" s="6"/>
+      <c r="H335" s="6"/>
     </row>
     <row r="336">
       <c r="D336" s="6"/>
       <c r="G336" s="6"/>
+      <c r="H336" s="6"/>
     </row>
     <row r="337">
       <c r="D337" s="6"/>
       <c r="G337" s="6"/>
+      <c r="H337" s="6"/>
     </row>
     <row r="338">
       <c r="D338" s="6"/>
       <c r="G338" s="6"/>
+      <c r="H338" s="6"/>
     </row>
     <row r="339">
       <c r="D339" s="6"/>
       <c r="G339" s="6"/>
+      <c r="H339" s="6"/>
     </row>
     <row r="340">
       <c r="D340" s="6"/>
       <c r="G340" s="6"/>
+      <c r="H340" s="6"/>
     </row>
     <row r="341">
       <c r="D341" s="6"/>
       <c r="G341" s="6"/>
+      <c r="H341" s="6"/>
     </row>
     <row r="342">
       <c r="D342" s="6"/>
       <c r="G342" s="6"/>
+      <c r="H342" s="6"/>
     </row>
     <row r="343">
       <c r="D343" s="6"/>
       <c r="G343" s="6"/>
+      <c r="H343" s="6"/>
     </row>
     <row r="344">
       <c r="D344" s="6"/>
       <c r="G344" s="6"/>
+      <c r="H344" s="6"/>
     </row>
     <row r="345">
       <c r="D345" s="6"/>
       <c r="G345" s="6"/>
+      <c r="H345" s="6"/>
     </row>
     <row r="346">
       <c r="D346" s="6"/>
       <c r="G346" s="6"/>
+      <c r="H346" s="6"/>
     </row>
     <row r="347">
       <c r="D347" s="6"/>
       <c r="G347" s="6"/>
+      <c r="H347" s="6"/>
     </row>
     <row r="348">
       <c r="D348" s="6"/>
       <c r="G348" s="6"/>
+      <c r="H348" s="6"/>
     </row>
     <row r="349">
       <c r="D349" s="6"/>
       <c r="G349" s="6"/>
+      <c r="H349" s="6"/>
     </row>
     <row r="350">
       <c r="D350" s="6"/>
       <c r="G350" s="6"/>
+      <c r="H350" s="6"/>
     </row>
     <row r="351">
       <c r="D351" s="6"/>
       <c r="G351" s="6"/>
+      <c r="H351" s="6"/>
     </row>
     <row r="352">
       <c r="D352" s="6"/>
       <c r="G352" s="6"/>
+      <c r="H352" s="6"/>
     </row>
     <row r="353">
       <c r="D353" s="6"/>
       <c r="G353" s="6"/>
+      <c r="H353" s="6"/>
     </row>
     <row r="354">
       <c r="D354" s="6"/>
       <c r="G354" s="6"/>
+      <c r="H354" s="6"/>
     </row>
     <row r="355">
       <c r="D355" s="6"/>
       <c r="G355" s="6"/>
+      <c r="H355" s="6"/>
     </row>
     <row r="356">
       <c r="D356" s="6"/>
       <c r="G356" s="6"/>
+      <c r="H356" s="6"/>
     </row>
     <row r="357">
       <c r="D357" s="6"/>
       <c r="G357" s="6"/>
+      <c r="H357" s="6"/>
     </row>
     <row r="358">
       <c r="D358" s="6"/>
       <c r="G358" s="6"/>
+      <c r="H358" s="6"/>
     </row>
     <row r="359">
       <c r="D359" s="6"/>
       <c r="G359" s="6"/>
+      <c r="H359" s="6"/>
     </row>
     <row r="360">
       <c r="D360" s="6"/>
       <c r="G360" s="6"/>
+      <c r="H360" s="6"/>
     </row>
     <row r="361">
       <c r="D361" s="6"/>
       <c r="G361" s="6"/>
+      <c r="H361" s="6"/>
     </row>
     <row r="362">
       <c r="D362" s="6"/>
       <c r="G362" s="6"/>
+      <c r="H362" s="6"/>
     </row>
     <row r="363">
       <c r="D363" s="6"/>
       <c r="G363" s="6"/>
+      <c r="H363" s="6"/>
     </row>
     <row r="364">
       <c r="D364" s="6"/>
       <c r="G364" s="6"/>
+      <c r="H364" s="6"/>
     </row>
     <row r="365">
       <c r="D365" s="6"/>
       <c r="G365" s="6"/>
+      <c r="H365" s="6"/>
     </row>
     <row r="366">
       <c r="D366" s="6"/>
       <c r="G366" s="6"/>
+      <c r="H366" s="6"/>
     </row>
     <row r="367">
       <c r="D367" s="6"/>
       <c r="G367" s="6"/>
+      <c r="H367" s="6"/>
     </row>
     <row r="368">
       <c r="D368" s="6"/>
       <c r="G368" s="6"/>
+      <c r="H368" s="6"/>
     </row>
     <row r="369">
       <c r="D369" s="6"/>
       <c r="G369" s="6"/>
+      <c r="H369" s="6"/>
     </row>
     <row r="370">
       <c r="D370" s="6"/>
       <c r="G370" s="6"/>
+      <c r="H370" s="6"/>
     </row>
     <row r="371">
       <c r="D371" s="6"/>
       <c r="G371" s="6"/>
+      <c r="H371" s="6"/>
     </row>
     <row r="372">
       <c r="D372" s="6"/>
       <c r="G372" s="6"/>
+      <c r="H372" s="6"/>
     </row>
     <row r="373">
       <c r="D373" s="6"/>
       <c r="G373" s="6"/>
+      <c r="H373" s="6"/>
     </row>
     <row r="374">
       <c r="D374" s="6"/>
       <c r="G374" s="6"/>
+      <c r="H374" s="6"/>
     </row>
     <row r="375">
       <c r="D375" s="6"/>
       <c r="G375" s="6"/>
+      <c r="H375" s="6"/>
     </row>
     <row r="376">
       <c r="D376" s="6"/>
       <c r="G376" s="6"/>
+      <c r="H376" s="6"/>
     </row>
     <row r="377">
       <c r="D377" s="6"/>
       <c r="G377" s="6"/>
+      <c r="H377" s="6"/>
     </row>
     <row r="378">
       <c r="D378" s="6"/>
       <c r="G378" s="6"/>
+      <c r="H378" s="6"/>
     </row>
     <row r="379">
       <c r="D379" s="6"/>
       <c r="G379" s="6"/>
+      <c r="H379" s="6"/>
     </row>
     <row r="380">
       <c r="D380" s="6"/>
       <c r="G380" s="6"/>
+      <c r="H380" s="6"/>
     </row>
     <row r="381">
       <c r="D381" s="6"/>
       <c r="G381" s="6"/>
+      <c r="H381" s="6"/>
     </row>
     <row r="382">
       <c r="D382" s="6"/>
       <c r="G382" s="6"/>
+      <c r="H382" s="6"/>
     </row>
     <row r="383">
       <c r="D383" s="6"/>
       <c r="G383" s="6"/>
+      <c r="H383" s="6"/>
     </row>
     <row r="384">
       <c r="D384" s="6"/>
       <c r="G384" s="6"/>
+      <c r="H384" s="6"/>
     </row>
     <row r="385">
       <c r="D385" s="6"/>
       <c r="G385" s="6"/>
+      <c r="H385" s="6"/>
     </row>
     <row r="386">
       <c r="D386" s="6"/>
       <c r="G386" s="6"/>
+      <c r="H386" s="6"/>
     </row>
     <row r="387">
       <c r="D387" s="6"/>
       <c r="G387" s="6"/>
+      <c r="H387" s="6"/>
     </row>
     <row r="388">
       <c r="D388" s="6"/>
       <c r="G388" s="6"/>
+      <c r="H388" s="6"/>
     </row>
     <row r="389">
       <c r="D389" s="6"/>
       <c r="G389" s="6"/>
+      <c r="H389" s="6"/>
     </row>
     <row r="390">
       <c r="D390" s="6"/>
       <c r="G390" s="6"/>
+      <c r="H390" s="6"/>
     </row>
     <row r="391">
       <c r="D391" s="6"/>
       <c r="G391" s="6"/>
+      <c r="H391" s="6"/>
     </row>
     <row r="392">
       <c r="D392" s="6"/>
       <c r="G392" s="6"/>
+      <c r="H392" s="6"/>
     </row>
     <row r="393">
       <c r="D393" s="6"/>
       <c r="G393" s="6"/>
+      <c r="H393" s="6"/>
     </row>
     <row r="394">
       <c r="D394" s="6"/>
       <c r="G394" s="6"/>
+      <c r="H394" s="6"/>
     </row>
     <row r="395">
       <c r="D395" s="6"/>
       <c r="G395" s="6"/>
+      <c r="H395" s="6"/>
     </row>
     <row r="396">
       <c r="D396" s="6"/>
       <c r="G396" s="6"/>
+      <c r="H396" s="6"/>
     </row>
     <row r="397">
       <c r="D397" s="6"/>
       <c r="G397" s="6"/>
+      <c r="H397" s="6"/>
     </row>
     <row r="398">
       <c r="D398" s="6"/>
       <c r="G398" s="6"/>
+      <c r="H398" s="6"/>
     </row>
     <row r="399">
       <c r="D399" s="6"/>
       <c r="G399" s="6"/>
+      <c r="H399" s="6"/>
     </row>
     <row r="400">
       <c r="D400" s="6"/>
       <c r="G400" s="6"/>
+      <c r="H400" s="6"/>
     </row>
     <row r="401">
       <c r="D401" s="6"/>
       <c r="G401" s="6"/>
+      <c r="H401" s="6"/>
     </row>
     <row r="402">
       <c r="D402" s="6"/>
       <c r="G402" s="6"/>
+      <c r="H402" s="6"/>
     </row>
     <row r="403">
       <c r="D403" s="6"/>
       <c r="G403" s="6"/>
+      <c r="H403" s="6"/>
     </row>
     <row r="404">
       <c r="D404" s="6"/>
       <c r="G404" s="6"/>
+      <c r="H404" s="6"/>
     </row>
     <row r="405">
       <c r="D405" s="6"/>
       <c r="G405" s="6"/>
+      <c r="H405" s="6"/>
     </row>
     <row r="406">
       <c r="D406" s="6"/>
       <c r="G406" s="6"/>
+      <c r="H406" s="6"/>
     </row>
     <row r="407">
       <c r="D407" s="6"/>
       <c r="G407" s="6"/>
+      <c r="H407" s="6"/>
     </row>
     <row r="408">
       <c r="D408" s="6"/>
       <c r="G408" s="6"/>
+      <c r="H408" s="6"/>
     </row>
     <row r="409">
       <c r="D409" s="6"/>
       <c r="G409" s="6"/>
+      <c r="H409" s="6"/>
     </row>
     <row r="410">
       <c r="D410" s="6"/>
       <c r="G410" s="6"/>
+      <c r="H410" s="6"/>
     </row>
     <row r="411">
       <c r="D411" s="6"/>
       <c r="G411" s="6"/>
+      <c r="H411" s="6"/>
     </row>
     <row r="412">
       <c r="D412" s="6"/>
       <c r="G412" s="6"/>
+      <c r="H412" s="6"/>
     </row>
     <row r="413">
       <c r="D413" s="6"/>
       <c r="G413" s="6"/>
+      <c r="H413" s="6"/>
     </row>
     <row r="414">
       <c r="D414" s="6"/>
       <c r="G414" s="6"/>
+      <c r="H414" s="6"/>
     </row>
     <row r="415">
       <c r="D415" s="6"/>
       <c r="G415" s="6"/>
+      <c r="H415" s="6"/>
     </row>
     <row r="416">
       <c r="D416" s="6"/>
       <c r="G416" s="6"/>
+      <c r="H416" s="6"/>
     </row>
     <row r="417">
       <c r="D417" s="6"/>
       <c r="G417" s="6"/>
+      <c r="H417" s="6"/>
     </row>
     <row r="418">
       <c r="D418" s="6"/>
       <c r="G418" s="6"/>
+      <c r="H418" s="6"/>
     </row>
     <row r="419">
       <c r="D419" s="6"/>
       <c r="G419" s="6"/>
+      <c r="H419" s="6"/>
     </row>
     <row r="420">
       <c r="D420" s="6"/>
       <c r="G420" s="6"/>
+      <c r="H420" s="6"/>
     </row>
     <row r="421">
       <c r="D421" s="6"/>
       <c r="G421" s="6"/>
+      <c r="H421" s="6"/>
     </row>
     <row r="422">
       <c r="D422" s="6"/>
       <c r="G422" s="6"/>
+      <c r="H422" s="6"/>
     </row>
     <row r="423">
       <c r="D423" s="6"/>
       <c r="G423" s="6"/>
+      <c r="H423" s="6"/>
     </row>
     <row r="424">
       <c r="D424" s="6"/>
       <c r="G424" s="6"/>
+      <c r="H424" s="6"/>
     </row>
     <row r="425">
       <c r="D425" s="6"/>
       <c r="G425" s="6"/>
+      <c r="H425" s="6"/>
     </row>
     <row r="426">
       <c r="D426" s="6"/>
       <c r="G426" s="6"/>
+      <c r="H426" s="6"/>
     </row>
     <row r="427">
       <c r="D427" s="6"/>
       <c r="G427" s="6"/>
+      <c r="H427" s="6"/>
     </row>
     <row r="428">
       <c r="D428" s="6"/>
       <c r="G428" s="6"/>
+      <c r="H428" s="6"/>
     </row>
     <row r="429">
       <c r="D429" s="6"/>
       <c r="G429" s="6"/>
+      <c r="H429" s="6"/>
     </row>
     <row r="430">
       <c r="D430" s="6"/>
       <c r="G430" s="6"/>
+      <c r="H430" s="6"/>
     </row>
     <row r="431">
       <c r="D431" s="6"/>
       <c r="G431" s="6"/>
+      <c r="H431" s="6"/>
     </row>
     <row r="432">
       <c r="D432" s="6"/>
       <c r="G432" s="6"/>
+      <c r="H432" s="6"/>
     </row>
     <row r="433">
       <c r="D433" s="6"/>
       <c r="G433" s="6"/>
+      <c r="H433" s="6"/>
     </row>
     <row r="434">
       <c r="D434" s="6"/>
       <c r="G434" s="6"/>
+      <c r="H434" s="6"/>
     </row>
     <row r="435">
       <c r="D435" s="6"/>
       <c r="G435" s="6"/>
+      <c r="H435" s="6"/>
     </row>
     <row r="436">
       <c r="D436" s="6"/>
       <c r="G436" s="6"/>
+      <c r="H436" s="6"/>
     </row>
     <row r="437">
       <c r="D437" s="6"/>
       <c r="G437" s="6"/>
+      <c r="H437" s="6"/>
     </row>
     <row r="438">
       <c r="D438" s="6"/>
       <c r="G438" s="6"/>
+      <c r="H438" s="6"/>
     </row>
     <row r="439">
       <c r="D439" s="6"/>
       <c r="G439" s="6"/>
+      <c r="H439" s="6"/>
     </row>
     <row r="440">
       <c r="D440" s="6"/>
       <c r="G440" s="6"/>
+      <c r="H440" s="6"/>
     </row>
     <row r="441">
       <c r="D441" s="6"/>
       <c r="G441" s="6"/>
+      <c r="H441" s="6"/>
     </row>
     <row r="442">
       <c r="D442" s="6"/>
       <c r="G442" s="6"/>
+      <c r="H442" s="6"/>
     </row>
     <row r="443">
       <c r="D443" s="6"/>
       <c r="G443" s="6"/>
+      <c r="H443" s="6"/>
     </row>
     <row r="444">
       <c r="D444" s="6"/>
       <c r="G444" s="6"/>
+      <c r="H444" s="6"/>
     </row>
     <row r="445">
       <c r="D445" s="6"/>
       <c r="G445" s="6"/>
+      <c r="H445" s="6"/>
     </row>
     <row r="446">
       <c r="D446" s="6"/>
       <c r="G446" s="6"/>
+      <c r="H446" s="6"/>
     </row>
     <row r="447">
       <c r="D447" s="6"/>
       <c r="G447" s="6"/>
+      <c r="H447" s="6"/>
     </row>
     <row r="448">
       <c r="D448" s="6"/>
       <c r="G448" s="6"/>
+      <c r="H448" s="6"/>
     </row>
     <row r="449">
       <c r="D449" s="6"/>
       <c r="G449" s="6"/>
+      <c r="H449" s="6"/>
     </row>
     <row r="450">
       <c r="D450" s="6"/>
       <c r="G450" s="6"/>
+      <c r="H450" s="6"/>
     </row>
     <row r="451">
       <c r="D451" s="6"/>
       <c r="G451" s="6"/>
+      <c r="H451" s="6"/>
     </row>
     <row r="452">
       <c r="D452" s="6"/>
       <c r="G452" s="6"/>
+      <c r="H452" s="6"/>
     </row>
     <row r="453">
       <c r="D453" s="6"/>
       <c r="G453" s="6"/>
+      <c r="H453" s="6"/>
     </row>
     <row r="454">
       <c r="D454" s="6"/>
       <c r="G454" s="6"/>
+      <c r="H454" s="6"/>
     </row>
     <row r="455">
       <c r="D455" s="6"/>
       <c r="G455" s="6"/>
+      <c r="H455" s="6"/>
     </row>
     <row r="456">
       <c r="D456" s="6"/>
       <c r="G456" s="6"/>
+      <c r="H456" s="6"/>
     </row>
     <row r="457">
       <c r="D457" s="6"/>
       <c r="G457" s="6"/>
+      <c r="H457" s="6"/>
     </row>
     <row r="458">
       <c r="D458" s="6"/>
       <c r="G458" s="6"/>
+      <c r="H458" s="6"/>
     </row>
     <row r="459">
       <c r="D459" s="6"/>
       <c r="G459" s="6"/>
+      <c r="H459" s="6"/>
     </row>
     <row r="460">
       <c r="D460" s="6"/>
       <c r="G460" s="6"/>
+      <c r="H460" s="6"/>
     </row>
     <row r="461">
       <c r="D461" s="6"/>
       <c r="G461" s="6"/>
+      <c r="H461" s="6"/>
     </row>
     <row r="462">
       <c r="D462" s="6"/>
       <c r="G462" s="6"/>
+      <c r="H462" s="6"/>
     </row>
     <row r="463">
       <c r="D463" s="6"/>
       <c r="G463" s="6"/>
+      <c r="H463" s="6"/>
     </row>
     <row r="464">
       <c r="D464" s="6"/>
       <c r="G464" s="6"/>
+      <c r="H464" s="6"/>
     </row>
     <row r="465">
       <c r="D465" s="6"/>
       <c r="G465" s="6"/>
+      <c r="H465" s="6"/>
     </row>
     <row r="466">
       <c r="D466" s="6"/>
       <c r="G466" s="6"/>
+      <c r="H466" s="6"/>
     </row>
     <row r="467">
       <c r="D467" s="6"/>
       <c r="G467" s="6"/>
+      <c r="H467" s="6"/>
     </row>
     <row r="468">
       <c r="D468" s="6"/>
       <c r="G468" s="6"/>
+      <c r="H468" s="6"/>
     </row>
     <row r="469">
       <c r="D469" s="6"/>
       <c r="G469" s="6"/>
+      <c r="H469" s="6"/>
     </row>
     <row r="470">
       <c r="D470" s="6"/>
       <c r="G470" s="6"/>
+      <c r="H470" s="6"/>
     </row>
     <row r="471">
       <c r="D471" s="6"/>
       <c r="G471" s="6"/>
+      <c r="H471" s="6"/>
     </row>
     <row r="472">
       <c r="D472" s="6"/>
       <c r="G472" s="6"/>
+      <c r="H472" s="6"/>
     </row>
     <row r="473">
       <c r="D473" s="6"/>
       <c r="G473" s="6"/>
+      <c r="H473" s="6"/>
     </row>
     <row r="474">
       <c r="D474" s="6"/>
       <c r="G474" s="6"/>
+      <c r="H474" s="6"/>
     </row>
     <row r="475">
       <c r="D475" s="6"/>
       <c r="G475" s="6"/>
+      <c r="H475" s="6"/>
     </row>
     <row r="476">
       <c r="D476" s="6"/>
       <c r="G476" s="6"/>
+      <c r="H476" s="6"/>
     </row>
     <row r="477">
       <c r="D477" s="6"/>
       <c r="G477" s="6"/>
+      <c r="H477" s="6"/>
     </row>
     <row r="478">
       <c r="D478" s="6"/>
       <c r="G478" s="6"/>
+      <c r="H478" s="6"/>
     </row>
     <row r="479">
       <c r="D479" s="6"/>
       <c r="G479" s="6"/>
+      <c r="H479" s="6"/>
     </row>
     <row r="480">
       <c r="D480" s="6"/>
       <c r="G480" s="6"/>
+      <c r="H480" s="6"/>
     </row>
     <row r="481">
       <c r="D481" s="6"/>
       <c r="G481" s="6"/>
+      <c r="H481" s="6"/>
     </row>
     <row r="482">
       <c r="D482" s="6"/>
       <c r="G482" s="6"/>
+      <c r="H482" s="6"/>
     </row>
     <row r="483">
       <c r="D483" s="6"/>
       <c r="G483" s="6"/>
+      <c r="H483" s="6"/>
     </row>
     <row r="484">
       <c r="D484" s="6"/>
       <c r="G484" s="6"/>
+      <c r="H484" s="6"/>
     </row>
     <row r="485">
       <c r="D485" s="6"/>
       <c r="G485" s="6"/>
+      <c r="H485" s="6"/>
     </row>
     <row r="486">
       <c r="D486" s="6"/>
       <c r="G486" s="6"/>
+      <c r="H486" s="6"/>
     </row>
     <row r="487">
       <c r="D487" s="6"/>
       <c r="G487" s="6"/>
+      <c r="H487" s="6"/>
     </row>
     <row r="488">
       <c r="D488" s="6"/>
       <c r="G488" s="6"/>
+      <c r="H488" s="6"/>
     </row>
     <row r="489">
       <c r="D489" s="6"/>
       <c r="G489" s="6"/>
+      <c r="H489" s="6"/>
     </row>
     <row r="490">
       <c r="D490" s="6"/>
       <c r="G490" s="6"/>
+      <c r="H490" s="6"/>
     </row>
     <row r="491">
       <c r="D491" s="6"/>
       <c r="G491" s="6"/>
+      <c r="H491" s="6"/>
     </row>
     <row r="492">
       <c r="D492" s="6"/>
       <c r="G492" s="6"/>
+      <c r="H492" s="6"/>
     </row>
     <row r="493">
       <c r="D493" s="6"/>
       <c r="G493" s="6"/>
+      <c r="H493" s="6"/>
     </row>
     <row r="494">
       <c r="D494" s="6"/>
       <c r="G494" s="6"/>
+      <c r="H494" s="6"/>
     </row>
     <row r="495">
       <c r="D495" s="6"/>
       <c r="G495" s="6"/>
+      <c r="H495" s="6"/>
     </row>
     <row r="496">
       <c r="D496" s="6"/>
       <c r="G496" s="6"/>
+      <c r="H496" s="6"/>
     </row>
     <row r="497">
       <c r="D497" s="6"/>
       <c r="G497" s="6"/>
+      <c r="H497" s="6"/>
     </row>
     <row r="498">
       <c r="D498" s="6"/>
       <c r="G498" s="6"/>
+      <c r="H498" s="6"/>
     </row>
     <row r="499">
       <c r="D499" s="6"/>
       <c r="G499" s="6"/>
+      <c r="H499" s="6"/>
     </row>
     <row r="500">
       <c r="D500" s="6"/>
       <c r="G500" s="6"/>
+      <c r="H500" s="6"/>
     </row>
     <row r="501">
       <c r="D501" s="6"/>
       <c r="G501" s="6"/>
+      <c r="H501" s="6"/>
     </row>
     <row r="502">
       <c r="D502" s="6"/>
       <c r="G502" s="6"/>
+      <c r="H502" s="6"/>
     </row>
     <row r="503">
       <c r="D503" s="6"/>
       <c r="G503" s="6"/>
+      <c r="H503" s="6"/>
     </row>
     <row r="504">
       <c r="D504" s="6"/>
       <c r="G504" s="6"/>
+      <c r="H504" s="6"/>
     </row>
     <row r="505">
       <c r="D505" s="6"/>
       <c r="G505" s="6"/>
+      <c r="H505" s="6"/>
     </row>
     <row r="506">
       <c r="D506" s="6"/>
       <c r="G506" s="6"/>
+      <c r="H506" s="6"/>
     </row>
     <row r="507">
       <c r="D507" s="6"/>
       <c r="G507" s="6"/>
+      <c r="H507" s="6"/>
     </row>
     <row r="508">
       <c r="D508" s="6"/>
       <c r="G508" s="6"/>
+      <c r="H508" s="6"/>
     </row>
     <row r="509">
       <c r="D509" s="6"/>
       <c r="G509" s="6"/>
+      <c r="H509" s="6"/>
     </row>
     <row r="510">
       <c r="D510" s="6"/>
       <c r="G510" s="6"/>
+      <c r="H510" s="6"/>
     </row>
     <row r="511">
       <c r="D511" s="6"/>
       <c r="G511" s="6"/>
+      <c r="H511" s="6"/>
     </row>
     <row r="512">
       <c r="D512" s="6"/>
       <c r="G512" s="6"/>
+      <c r="H512" s="6"/>
     </row>
     <row r="513">
       <c r="D513" s="6"/>
       <c r="G513" s="6"/>
+      <c r="H513" s="6"/>
     </row>
     <row r="514">
       <c r="D514" s="6"/>
       <c r="G514" s="6"/>
+      <c r="H514" s="6"/>
     </row>
     <row r="515">
       <c r="D515" s="6"/>
       <c r="G515" s="6"/>
+      <c r="H515" s="6"/>
     </row>
     <row r="516">
       <c r="D516" s="6"/>
       <c r="G516" s="6"/>
+      <c r="H516" s="6"/>
     </row>
     <row r="517">
       <c r="D517" s="6"/>
       <c r="G517" s="6"/>
+      <c r="H517" s="6"/>
     </row>
     <row r="518">
       <c r="D518" s="6"/>
       <c r="G518" s="6"/>
+      <c r="H518" s="6"/>
     </row>
     <row r="519">
       <c r="D519" s="6"/>
       <c r="G519" s="6"/>
+      <c r="H519" s="6"/>
     </row>
     <row r="520">
       <c r="D520" s="6"/>
       <c r="G520" s="6"/>
+      <c r="H520" s="6"/>
     </row>
     <row r="521">
       <c r="D521" s="6"/>
       <c r="G521" s="6"/>
+      <c r="H521" s="6"/>
     </row>
     <row r="522">
       <c r="D522" s="6"/>
       <c r="G522" s="6"/>
+      <c r="H522" s="6"/>
     </row>
     <row r="523">
       <c r="D523" s="6"/>
       <c r="G523" s="6"/>
+      <c r="H523" s="6"/>
     </row>
     <row r="524">
       <c r="D524" s="6"/>
       <c r="G524" s="6"/>
+      <c r="H524" s="6"/>
     </row>
     <row r="525">
       <c r="D525" s="6"/>
       <c r="G525" s="6"/>
+      <c r="H525" s="6"/>
     </row>
     <row r="526">
       <c r="D526" s="6"/>
       <c r="G526" s="6"/>
+      <c r="H526" s="6"/>
     </row>
     <row r="527">
       <c r="D527" s="6"/>
       <c r="G527" s="6"/>
+      <c r="H527" s="6"/>
     </row>
     <row r="528">
       <c r="D528" s="6"/>
       <c r="G528" s="6"/>
+      <c r="H528" s="6"/>
     </row>
     <row r="529">
       <c r="D529" s="6"/>
       <c r="G529" s="6"/>
+      <c r="H529" s="6"/>
     </row>
     <row r="530">
       <c r="D530" s="6"/>
       <c r="G530" s="6"/>
+      <c r="H530" s="6"/>
     </row>
     <row r="531">
       <c r="D531" s="6"/>
       <c r="G531" s="6"/>
+      <c r="H531" s="6"/>
     </row>
     <row r="532">
       <c r="D532" s="6"/>
       <c r="G532" s="6"/>
+      <c r="H532" s="6"/>
     </row>
     <row r="533">
       <c r="D533" s="6"/>
       <c r="G533" s="6"/>
+      <c r="H533" s="6"/>
     </row>
     <row r="534">
       <c r="D534" s="6"/>
       <c r="G534" s="6"/>
+      <c r="H534" s="6"/>
     </row>
     <row r="535">
       <c r="D535" s="6"/>
       <c r="G535" s="6"/>
+      <c r="H535" s="6"/>
     </row>
     <row r="536">
       <c r="D536" s="6"/>
       <c r="G536" s="6"/>
+      <c r="H536" s="6"/>
     </row>
     <row r="537">
       <c r="D537" s="6"/>
       <c r="G537" s="6"/>
+      <c r="H537" s="6"/>
     </row>
     <row r="538">
       <c r="D538" s="6"/>
       <c r="G538" s="6"/>
+      <c r="H538" s="6"/>
     </row>
     <row r="539">
       <c r="D539" s="6"/>
       <c r="G539" s="6"/>
+      <c r="H539" s="6"/>
     </row>
     <row r="540">
       <c r="D540" s="6"/>
       <c r="G540" s="6"/>
+      <c r="H540" s="6"/>
     </row>
     <row r="541">
       <c r="D541" s="6"/>
       <c r="G541" s="6"/>
+      <c r="H541" s="6"/>
     </row>
     <row r="542">
       <c r="D542" s="6"/>
       <c r="G542" s="6"/>
+      <c r="H542" s="6"/>
     </row>
     <row r="543">
       <c r="D543" s="6"/>
       <c r="G543" s="6"/>
+      <c r="H543" s="6"/>
     </row>
     <row r="544">
       <c r="D544" s="6"/>
       <c r="G544" s="6"/>
+      <c r="H544" s="6"/>
     </row>
     <row r="545">
       <c r="D545" s="6"/>
       <c r="G545" s="6"/>
+      <c r="H545" s="6"/>
     </row>
     <row r="546">
       <c r="D546" s="6"/>
       <c r="G546" s="6"/>
+      <c r="H546" s="6"/>
     </row>
     <row r="547">
       <c r="D547" s="6"/>
       <c r="G547" s="6"/>
+      <c r="H547" s="6"/>
     </row>
     <row r="548">
       <c r="D548" s="6"/>
       <c r="G548" s="6"/>
+      <c r="H548" s="6"/>
     </row>
     <row r="549">
       <c r="D549" s="6"/>
       <c r="G549" s="6"/>
+      <c r="H549" s="6"/>
     </row>
     <row r="550">
       <c r="D550" s="6"/>
       <c r="G550" s="6"/>
+      <c r="H550" s="6"/>
     </row>
     <row r="551">
       <c r="D551" s="6"/>
       <c r="G551" s="6"/>
+      <c r="H551" s="6"/>
     </row>
     <row r="552">
       <c r="D552" s="6"/>
       <c r="G552" s="6"/>
+      <c r="H552" s="6"/>
     </row>
     <row r="553">
       <c r="D553" s="6"/>
       <c r="G553" s="6"/>
+      <c r="H553" s="6"/>
     </row>
     <row r="554">
       <c r="D554" s="6"/>
       <c r="G554" s="6"/>
+      <c r="H554" s="6"/>
     </row>
     <row r="555">
       <c r="D555" s="6"/>
       <c r="G555" s="6"/>
+      <c r="H555" s="6"/>
     </row>
     <row r="556">
       <c r="D556" s="6"/>
       <c r="G556" s="6"/>
+      <c r="H556" s="6"/>
     </row>
     <row r="557">
       <c r="D557" s="6"/>
       <c r="G557" s="6"/>
+      <c r="H557" s="6"/>
     </row>
     <row r="558">
       <c r="D558" s="6"/>
       <c r="G558" s="6"/>
+      <c r="H558" s="6"/>
     </row>
     <row r="559">
       <c r="D559" s="6"/>
       <c r="G559" s="6"/>
+      <c r="H559" s="6"/>
     </row>
     <row r="560">
       <c r="D560" s="6"/>
       <c r="G560" s="6"/>
+      <c r="H560" s="6"/>
     </row>
     <row r="561">
       <c r="D561" s="6"/>
       <c r="G561" s="6"/>
+      <c r="H561" s="6"/>
     </row>
     <row r="562">
       <c r="D562" s="6"/>
       <c r="G562" s="6"/>
+      <c r="H562" s="6"/>
     </row>
     <row r="563">
       <c r="D563" s="6"/>
       <c r="G563" s="6"/>
+      <c r="H563" s="6"/>
     </row>
     <row r="564">
       <c r="D564" s="6"/>
       <c r="G564" s="6"/>
+      <c r="H564" s="6"/>
     </row>
     <row r="565">
       <c r="D565" s="6"/>
       <c r="G565" s="6"/>
+      <c r="H565" s="6"/>
     </row>
     <row r="566">
       <c r="D566" s="6"/>
       <c r="G566" s="6"/>
+      <c r="H566" s="6"/>
     </row>
     <row r="567">
       <c r="D567" s="6"/>
       <c r="G567" s="6"/>
+      <c r="H567" s="6"/>
     </row>
     <row r="568">
       <c r="D568" s="6"/>
       <c r="G568" s="6"/>
+      <c r="H568" s="6"/>
     </row>
     <row r="569">
       <c r="D569" s="6"/>
       <c r="G569" s="6"/>
+      <c r="H569" s="6"/>
     </row>
     <row r="570">
       <c r="D570" s="6"/>
       <c r="G570" s="6"/>
+      <c r="H570" s="6"/>
     </row>
     <row r="571">
       <c r="D571" s="6"/>
       <c r="G571" s="6"/>
+      <c r="H571" s="6"/>
     </row>
     <row r="572">
       <c r="D572" s="6"/>
       <c r="G572" s="6"/>
+      <c r="H572" s="6"/>
     </row>
     <row r="573">
       <c r="D573" s="6"/>
       <c r="G573" s="6"/>
+      <c r="H573" s="6"/>
     </row>
     <row r="574">
       <c r="D574" s="6"/>
       <c r="G574" s="6"/>
+      <c r="H574" s="6"/>
     </row>
     <row r="575">
       <c r="D575" s="6"/>
       <c r="G575" s="6"/>
+      <c r="H575" s="6"/>
     </row>
     <row r="576">
       <c r="D576" s="6"/>
       <c r="G576" s="6"/>
+      <c r="H576" s="6"/>
     </row>
     <row r="577">
       <c r="D577" s="6"/>
       <c r="G577" s="6"/>
+      <c r="H577" s="6"/>
     </row>
     <row r="578">
       <c r="D578" s="6"/>
       <c r="G578" s="6"/>
+      <c r="H578" s="6"/>
     </row>
     <row r="579">
       <c r="D579" s="6"/>
       <c r="G579" s="6"/>
+      <c r="H579" s="6"/>
     </row>
     <row r="580">
       <c r="D580" s="6"/>
       <c r="G580" s="6"/>
+      <c r="H580" s="6"/>
     </row>
     <row r="581">
       <c r="D581" s="6"/>
       <c r="G581" s="6"/>
+      <c r="H581" s="6"/>
     </row>
     <row r="582">
       <c r="D582" s="6"/>
       <c r="G582" s="6"/>
+      <c r="H582" s="6"/>
     </row>
     <row r="583">
       <c r="D583" s="6"/>
       <c r="G583" s="6"/>
+      <c r="H583" s="6"/>
     </row>
     <row r="584">
       <c r="D584" s="6"/>
       <c r="G584" s="6"/>
+      <c r="H584" s="6"/>
     </row>
     <row r="585">
       <c r="D585" s="6"/>
       <c r="G585" s="6"/>
+      <c r="H585" s="6"/>
     </row>
     <row r="586">
       <c r="D586" s="6"/>
       <c r="G586" s="6"/>
+      <c r="H586" s="6"/>
     </row>
     <row r="587">
       <c r="D587" s="6"/>
       <c r="G587" s="6"/>
+      <c r="H587" s="6"/>
     </row>
     <row r="588">
       <c r="D588" s="6"/>
       <c r="G588" s="6"/>
+      <c r="H588" s="6"/>
     </row>
     <row r="589">
       <c r="D589" s="6"/>
       <c r="G589" s="6"/>
+      <c r="H589" s="6"/>
     </row>
     <row r="590">
       <c r="D590" s="6"/>
       <c r="G590" s="6"/>
+      <c r="H590" s="6"/>
     </row>
     <row r="591">
       <c r="D591" s="6"/>
       <c r="G591" s="6"/>
+      <c r="H591" s="6"/>
     </row>
     <row r="592">
       <c r="D592" s="6"/>
       <c r="G592" s="6"/>
+      <c r="H592" s="6"/>
     </row>
     <row r="593">
       <c r="D593" s="6"/>
       <c r="G593" s="6"/>
+      <c r="H593" s="6"/>
     </row>
     <row r="594">
       <c r="D594" s="6"/>
       <c r="G594" s="6"/>
+      <c r="H594" s="6"/>
     </row>
     <row r="595">
       <c r="D595" s="6"/>
       <c r="G595" s="6"/>
+      <c r="H595" s="6"/>
     </row>
     <row r="596">
       <c r="D596" s="6"/>
       <c r="G596" s="6"/>
+      <c r="H596" s="6"/>
     </row>
     <row r="597">
       <c r="D597" s="6"/>
       <c r="G597" s="6"/>
+      <c r="H597" s="6"/>
     </row>
     <row r="598">
       <c r="D598" s="6"/>
       <c r="G598" s="6"/>
+      <c r="H598" s="6"/>
     </row>
     <row r="599">
       <c r="D599" s="6"/>
       <c r="G599" s="6"/>
+      <c r="H599" s="6"/>
     </row>
     <row r="600">
       <c r="D600" s="6"/>
       <c r="G600" s="6"/>
+      <c r="H600" s="6"/>
     </row>
     <row r="601">
       <c r="D601" s="6"/>
       <c r="G601" s="6"/>
+      <c r="H601" s="6"/>
     </row>
     <row r="602">
       <c r="D602" s="6"/>
       <c r="G602" s="6"/>
+      <c r="H602" s="6"/>
     </row>
     <row r="603">
       <c r="D603" s="6"/>
       <c r="G603" s="6"/>
+      <c r="H603" s="6"/>
     </row>
     <row r="604">
       <c r="D604" s="6"/>
       <c r="G604" s="6"/>
+      <c r="H604" s="6"/>
     </row>
     <row r="605">
       <c r="D605" s="6"/>
       <c r="G605" s="6"/>
+      <c r="H605" s="6"/>
     </row>
     <row r="606">
       <c r="D606" s="6"/>
       <c r="G606" s="6"/>
+      <c r="H606" s="6"/>
     </row>
     <row r="607">
       <c r="D607" s="6"/>
       <c r="G607" s="6"/>
+      <c r="H607" s="6"/>
     </row>
     <row r="608">
       <c r="D608" s="6"/>
       <c r="G608" s="6"/>
+      <c r="H608" s="6"/>
     </row>
     <row r="609">
       <c r="D609" s="6"/>
       <c r="G609" s="6"/>
+      <c r="H609" s="6"/>
     </row>
     <row r="610">
       <c r="D610" s="6"/>
       <c r="G610" s="6"/>
+      <c r="H610" s="6"/>
     </row>
     <row r="611">
       <c r="D611" s="6"/>
       <c r="G611" s="6"/>
+      <c r="H611" s="6"/>
     </row>
     <row r="612">
       <c r="D612" s="6"/>
       <c r="G612" s="6"/>
+      <c r="H612" s="6"/>
     </row>
     <row r="613">
       <c r="D613" s="6"/>
       <c r="G613" s="6"/>
+      <c r="H613" s="6"/>
     </row>
     <row r="614">
       <c r="D614" s="6"/>
       <c r="G614" s="6"/>
+      <c r="H614" s="6"/>
     </row>
     <row r="615">
       <c r="D615" s="6"/>
       <c r="G615" s="6"/>
+      <c r="H615" s="6"/>
     </row>
     <row r="616">
       <c r="D616" s="6"/>
       <c r="G616" s="6"/>
+      <c r="H616" s="6"/>
     </row>
     <row r="617">
       <c r="D617" s="6"/>
       <c r="G617" s="6"/>
+      <c r="H617" s="6"/>
     </row>
     <row r="618">
       <c r="D618" s="6"/>
       <c r="G618" s="6"/>
+      <c r="H618" s="6"/>
     </row>
     <row r="619">
       <c r="D619" s="6"/>
       <c r="G619" s="6"/>
+      <c r="H619" s="6"/>
     </row>
     <row r="620">
       <c r="D620" s="6"/>
       <c r="G620" s="6"/>
+      <c r="H620" s="6"/>
     </row>
     <row r="621">
       <c r="D621" s="6"/>
       <c r="G621" s="6"/>
+      <c r="H621" s="6"/>
     </row>
     <row r="622">
       <c r="D622" s="6"/>
       <c r="G622" s="6"/>
+      <c r="H622" s="6"/>
     </row>
     <row r="623">
       <c r="D623" s="6"/>
       <c r="G623" s="6"/>
+      <c r="H623" s="6"/>
     </row>
     <row r="624">
       <c r="D624" s="6"/>
       <c r="G624" s="6"/>
+      <c r="H624" s="6"/>
     </row>
     <row r="625">
       <c r="D625" s="6"/>
       <c r="G625" s="6"/>
+      <c r="H625" s="6"/>
     </row>
     <row r="626">
       <c r="D626" s="6"/>
       <c r="G626" s="6"/>
+      <c r="H626" s="6"/>
     </row>
     <row r="627">
       <c r="D627" s="6"/>
       <c r="G627" s="6"/>
+      <c r="H627" s="6"/>
     </row>
     <row r="628">
       <c r="D628" s="6"/>
       <c r="G628" s="6"/>
+      <c r="H628" s="6"/>
     </row>
     <row r="629">
       <c r="D629" s="6"/>
       <c r="G629" s="6"/>
+      <c r="H629" s="6"/>
     </row>
     <row r="630">
       <c r="D630" s="6"/>
       <c r="G630" s="6"/>
+      <c r="H630" s="6"/>
     </row>
     <row r="631">
       <c r="D631" s="6"/>
       <c r="G631" s="6"/>
+      <c r="H631" s="6"/>
     </row>
     <row r="632">
       <c r="D632" s="6"/>
       <c r="G632" s="6"/>
+      <c r="H632" s="6"/>
     </row>
     <row r="633">
       <c r="D633" s="6"/>
       <c r="G633" s="6"/>
+      <c r="H633" s="6"/>
     </row>
     <row r="634">
       <c r="D634" s="6"/>
       <c r="G634" s="6"/>
+      <c r="H634" s="6"/>
     </row>
     <row r="635">
       <c r="D635" s="6"/>
       <c r="G635" s="6"/>
+      <c r="H635" s="6"/>
     </row>
     <row r="636">
       <c r="D636" s="6"/>
       <c r="G636" s="6"/>
+      <c r="H636" s="6"/>
     </row>
     <row r="637">
       <c r="D637" s="6"/>
       <c r="G637" s="6"/>
+      <c r="H637" s="6"/>
     </row>
     <row r="638">
       <c r="D638" s="6"/>
       <c r="G638" s="6"/>
+      <c r="H638" s="6"/>
     </row>
     <row r="639">
       <c r="D639" s="6"/>
       <c r="G639" s="6"/>
+      <c r="H639" s="6"/>
     </row>
     <row r="640">
       <c r="D640" s="6"/>
       <c r="G640" s="6"/>
+      <c r="H640" s="6"/>
     </row>
     <row r="641">
       <c r="D641" s="6"/>
       <c r="G641" s="6"/>
+      <c r="H641" s="6"/>
     </row>
     <row r="642">
       <c r="D642" s="6"/>
       <c r="G642" s="6"/>
+      <c r="H642" s="6"/>
     </row>
     <row r="643">
       <c r="D643" s="6"/>
       <c r="G643" s="6"/>
+      <c r="H643" s="6"/>
     </row>
     <row r="644">
       <c r="D644" s="6"/>
       <c r="G644" s="6"/>
+      <c r="H644" s="6"/>
     </row>
     <row r="645">
       <c r="D645" s="6"/>
       <c r="G645" s="6"/>
+      <c r="H645" s="6"/>
     </row>
     <row r="646">
       <c r="D646" s="6"/>
       <c r="G646" s="6"/>
+      <c r="H646" s="6"/>
     </row>
     <row r="647">
       <c r="D647" s="6"/>
       <c r="G647" s="6"/>
+      <c r="H647" s="6"/>
     </row>
     <row r="648">
       <c r="D648" s="6"/>
       <c r="G648" s="6"/>
+      <c r="H648" s="6"/>
     </row>
     <row r="649">
       <c r="D649" s="6"/>
       <c r="G649" s="6"/>
+      <c r="H649" s="6"/>
     </row>
     <row r="650">
       <c r="D650" s="6"/>
       <c r="G650" s="6"/>
+      <c r="H650" s="6"/>
     </row>
     <row r="651">
       <c r="D651" s="6"/>
       <c r="G651" s="6"/>
+      <c r="H651" s="6"/>
     </row>
     <row r="652">
       <c r="D652" s="6"/>
       <c r="G652" s="6"/>
+      <c r="H652" s="6"/>
     </row>
     <row r="653">
       <c r="D653" s="6"/>
       <c r="G653" s="6"/>
+      <c r="H653" s="6"/>
     </row>
     <row r="654">
       <c r="D654" s="6"/>
       <c r="G654" s="6"/>
+      <c r="H654" s="6"/>
     </row>
     <row r="655">
       <c r="D655" s="6"/>
       <c r="G655" s="6"/>
+      <c r="H655" s="6"/>
     </row>
     <row r="656">
       <c r="D656" s="6"/>
       <c r="G656" s="6"/>
+      <c r="H656" s="6"/>
     </row>
     <row r="657">
       <c r="D657" s="6"/>
       <c r="G657" s="6"/>
+      <c r="H657" s="6"/>
     </row>
     <row r="658">
       <c r="D658" s="6"/>
       <c r="G658" s="6"/>
+      <c r="H658" s="6"/>
     </row>
     <row r="659">
       <c r="D659" s="6"/>
       <c r="G659" s="6"/>
+      <c r="H659" s="6"/>
     </row>
     <row r="660">
       <c r="D660" s="6"/>
       <c r="G660" s="6"/>
+      <c r="H660" s="6"/>
     </row>
     <row r="661">
       <c r="D661" s="6"/>
       <c r="G661" s="6"/>
+      <c r="H661" s="6"/>
     </row>
     <row r="662">
       <c r="D662" s="6"/>
       <c r="G662" s="6"/>
+      <c r="H662" s="6"/>
     </row>
     <row r="663">
       <c r="D663" s="6"/>
       <c r="G663" s="6"/>
+      <c r="H663" s="6"/>
     </row>
     <row r="664">
       <c r="D664" s="6"/>
       <c r="G664" s="6"/>
+      <c r="H664" s="6"/>
     </row>
     <row r="665">
       <c r="D665" s="6"/>
       <c r="G665" s="6"/>
+      <c r="H665" s="6"/>
     </row>
     <row r="666">
       <c r="D666" s="6"/>
       <c r="G666" s="6"/>
+      <c r="H666" s="6"/>
     </row>
     <row r="667">
       <c r="D667" s="6"/>
       <c r="G667" s="6"/>
+      <c r="H667" s="6"/>
     </row>
     <row r="668">
       <c r="D668" s="6"/>
       <c r="G668" s="6"/>
+      <c r="H668" s="6"/>
     </row>
     <row r="669">
       <c r="D669" s="6"/>
       <c r="G669" s="6"/>
+      <c r="H669" s="6"/>
     </row>
     <row r="670">
       <c r="D670" s="6"/>
       <c r="G670" s="6"/>
+      <c r="H670" s="6"/>
     </row>
     <row r="671">
       <c r="D671" s="6"/>
       <c r="G671" s="6"/>
+      <c r="H671" s="6"/>
     </row>
     <row r="672">
       <c r="D672" s="6"/>
       <c r="G672" s="6"/>
+      <c r="H672" s="6"/>
     </row>
     <row r="673">
       <c r="D673" s="6"/>
       <c r="G673" s="6"/>
+      <c r="H673" s="6"/>
     </row>
     <row r="674">
       <c r="D674" s="6"/>
       <c r="G674" s="6"/>
+      <c r="H674" s="6"/>
     </row>
     <row r="675">
       <c r="D675" s="6"/>
       <c r="G675" s="6"/>
+      <c r="H675" s="6"/>
     </row>
     <row r="676">
       <c r="D676" s="6"/>
       <c r="G676" s="6"/>
+      <c r="H676" s="6"/>
     </row>
     <row r="677">
       <c r="D677" s="6"/>
       <c r="G677" s="6"/>
+      <c r="H677" s="6"/>
     </row>
     <row r="678">
       <c r="D678" s="6"/>
       <c r="G678" s="6"/>
+      <c r="H678" s="6"/>
     </row>
     <row r="679">
       <c r="D679" s="6"/>
       <c r="G679" s="6"/>
+      <c r="H679" s="6"/>
     </row>
     <row r="680">
       <c r="D680" s="6"/>
       <c r="G680" s="6"/>
+      <c r="H680" s="6"/>
     </row>
     <row r="681">
       <c r="D681" s="6"/>
       <c r="G681" s="6"/>
+      <c r="H681" s="6"/>
     </row>
     <row r="682">
       <c r="D682" s="6"/>
       <c r="G682" s="6"/>
+      <c r="H682" s="6"/>
     </row>
     <row r="683">
       <c r="D683" s="6"/>
       <c r="G683" s="6"/>
+      <c r="H683" s="6"/>
     </row>
     <row r="684">
       <c r="D684" s="6"/>
       <c r="G684" s="6"/>
+      <c r="H684" s="6"/>
     </row>
     <row r="685">
       <c r="D685" s="6"/>
       <c r="G685" s="6"/>
+      <c r="H685" s="6"/>
     </row>
     <row r="686">
       <c r="D686" s="6"/>
       <c r="G686" s="6"/>
+      <c r="H686" s="6"/>
     </row>
     <row r="687">
       <c r="D687" s="6"/>
       <c r="G687" s="6"/>
+      <c r="H687" s="6"/>
     </row>
     <row r="688">
       <c r="D688" s="6"/>
       <c r="G688" s="6"/>
+      <c r="H688" s="6"/>
     </row>
     <row r="689">
       <c r="D689" s="6"/>
       <c r="G689" s="6"/>
+      <c r="H689" s="6"/>
     </row>
     <row r="690">
       <c r="D690" s="6"/>
       <c r="G690" s="6"/>
+      <c r="H690" s="6"/>
     </row>
     <row r="691">
       <c r="D691" s="6"/>
       <c r="G691" s="6"/>
+      <c r="H691" s="6"/>
     </row>
     <row r="692">
       <c r="D692" s="6"/>
       <c r="G692" s="6"/>
+      <c r="H692" s="6"/>
     </row>
     <row r="693">
       <c r="D693" s="6"/>
       <c r="G693" s="6"/>
+      <c r="H693" s="6"/>
     </row>
     <row r="694">
       <c r="D694" s="6"/>
       <c r="G694" s="6"/>
+      <c r="H694" s="6"/>
     </row>
     <row r="695">
       <c r="D695" s="6"/>
       <c r="G695" s="6"/>
+      <c r="H695" s="6"/>
     </row>
     <row r="696">
       <c r="D696" s="6"/>
       <c r="G696" s="6"/>
+      <c r="H696" s="6"/>
     </row>
     <row r="697">
       <c r="D697" s="6"/>
       <c r="G697" s="6"/>
+      <c r="H697" s="6"/>
     </row>
     <row r="698">
       <c r="D698" s="6"/>
       <c r="G698" s="6"/>
+      <c r="H698" s="6"/>
     </row>
     <row r="699">
       <c r="D699" s="6"/>
       <c r="G699" s="6"/>
+      <c r="H699" s="6"/>
     </row>
     <row r="700">
       <c r="D700" s="6"/>
       <c r="G700" s="6"/>
+      <c r="H700" s="6"/>
     </row>
     <row r="701">
       <c r="D701" s="6"/>
       <c r="G701" s="6"/>
+      <c r="H701" s="6"/>
     </row>
     <row r="702">
       <c r="D702" s="6"/>
       <c r="G702" s="6"/>
+      <c r="H702" s="6"/>
     </row>
     <row r="703">
       <c r="D703" s="6"/>
       <c r="G703" s="6"/>
+      <c r="H703" s="6"/>
     </row>
     <row r="704">
       <c r="D704" s="6"/>
       <c r="G704" s="6"/>
+      <c r="H704" s="6"/>
     </row>
     <row r="705">
       <c r="D705" s="6"/>
       <c r="G705" s="6"/>
+      <c r="H705" s="6"/>
     </row>
     <row r="706">
       <c r="D706" s="6"/>
       <c r="G706" s="6"/>
+      <c r="H706" s="6"/>
     </row>
     <row r="707">
       <c r="D707" s="6"/>
       <c r="G707" s="6"/>
+      <c r="H707" s="6"/>
     </row>
     <row r="708">
       <c r="D708" s="6"/>
       <c r="G708" s="6"/>
+      <c r="H708" s="6"/>
     </row>
     <row r="709">
       <c r="D709" s="6"/>
       <c r="G709" s="6"/>
+      <c r="H709" s="6"/>
     </row>
     <row r="710">
       <c r="D710" s="6"/>
       <c r="G710" s="6"/>
+      <c r="H710" s="6"/>
     </row>
     <row r="711">
       <c r="D711" s="6"/>
       <c r="G711" s="6"/>
+      <c r="H711" s="6"/>
     </row>
     <row r="712">
       <c r="D712" s="6"/>
       <c r="G712" s="6"/>
+      <c r="H712" s="6"/>
     </row>
     <row r="713">
       <c r="D713" s="6"/>
       <c r="G713" s="6"/>
+      <c r="H713" s="6"/>
     </row>
     <row r="714">
       <c r="D714" s="6"/>
       <c r="G714" s="6"/>
+      <c r="H714" s="6"/>
     </row>
     <row r="715">
       <c r="D715" s="6"/>
       <c r="G715" s="6"/>
+      <c r="H715" s="6"/>
     </row>
     <row r="716">
       <c r="D716" s="6"/>
       <c r="G716" s="6"/>
+      <c r="H716" s="6"/>
     </row>
     <row r="717">
       <c r="D717" s="6"/>
       <c r="G717" s="6"/>
+      <c r="H717" s="6"/>
     </row>
     <row r="718">
       <c r="D718" s="6"/>
       <c r="G718" s="6"/>
+      <c r="H718" s="6"/>
     </row>
     <row r="719">
       <c r="D719" s="6"/>
       <c r="G719" s="6"/>
+      <c r="H719" s="6"/>
     </row>
     <row r="720">
       <c r="D720" s="6"/>
       <c r="G720" s="6"/>
+      <c r="H720" s="6"/>
     </row>
     <row r="721">
       <c r="D721" s="6"/>
       <c r="G721" s="6"/>
+      <c r="H721" s="6"/>
     </row>
     <row r="722">
       <c r="D722" s="6"/>
       <c r="G722" s="6"/>
+      <c r="H722" s="6"/>
     </row>
     <row r="723">
       <c r="D723" s="6"/>
       <c r="G723" s="6"/>
+      <c r="H723" s="6"/>
     </row>
     <row r="724">
       <c r="D724" s="6"/>
       <c r="G724" s="6"/>
+      <c r="H724" s="6"/>
     </row>
     <row r="725">
       <c r="D725" s="6"/>
       <c r="G725" s="6"/>
+      <c r="H725" s="6"/>
     </row>
     <row r="726">
       <c r="D726" s="6"/>
       <c r="G726" s="6"/>
+      <c r="H726" s="6"/>
     </row>
     <row r="727">
       <c r="D727" s="6"/>
       <c r="G727" s="6"/>
+      <c r="H727" s="6"/>
     </row>
     <row r="728">
       <c r="D728" s="6"/>
       <c r="G728" s="6"/>
+      <c r="H728" s="6"/>
     </row>
     <row r="729">
       <c r="D729" s="6"/>
       <c r="G729" s="6"/>
+      <c r="H729" s="6"/>
     </row>
     <row r="730">
       <c r="D730" s="6"/>
       <c r="G730" s="6"/>
+      <c r="H730" s="6"/>
     </row>
     <row r="731">
       <c r="D731" s="6"/>
       <c r="G731" s="6"/>
+      <c r="H731" s="6"/>
     </row>
     <row r="732">
       <c r="D732" s="6"/>
       <c r="G732" s="6"/>
+      <c r="H732" s="6"/>
     </row>
     <row r="733">
       <c r="D733" s="6"/>
       <c r="G733" s="6"/>
+      <c r="H733" s="6"/>
     </row>
     <row r="734">
       <c r="D734" s="6"/>
       <c r="G734" s="6"/>
+      <c r="H734" s="6"/>
     </row>
     <row r="735">
       <c r="D735" s="6"/>
       <c r="G735" s="6"/>
+      <c r="H735" s="6"/>
     </row>
     <row r="736">
       <c r="D736" s="6"/>
       <c r="G736" s="6"/>
+      <c r="H736" s="6"/>
     </row>
     <row r="737">
       <c r="D737" s="6"/>
       <c r="G737" s="6"/>
+      <c r="H737" s="6"/>
     </row>
     <row r="738">
       <c r="D738" s="6"/>
       <c r="G738" s="6"/>
+      <c r="H738" s="6"/>
     </row>
     <row r="739">
       <c r="D739" s="6"/>
       <c r="G739" s="6"/>
+      <c r="H739" s="6"/>
     </row>
     <row r="740">
       <c r="D740" s="6"/>
       <c r="G740" s="6"/>
+      <c r="H740" s="6"/>
     </row>
     <row r="741">
       <c r="D741" s="6"/>
       <c r="G741" s="6"/>
+      <c r="H741" s="6"/>
     </row>
     <row r="742">
       <c r="D742" s="6"/>
       <c r="G742" s="6"/>
+      <c r="H742" s="6"/>
     </row>
     <row r="743">
       <c r="D743" s="6"/>
       <c r="G743" s="6"/>
+      <c r="H743" s="6"/>
     </row>
     <row r="744">
       <c r="D744" s="6"/>
       <c r="G744" s="6"/>
+      <c r="H744" s="6"/>
     </row>
     <row r="745">
       <c r="D745" s="6"/>
       <c r="G745" s="6"/>
+      <c r="H745" s="6"/>
     </row>
     <row r="746">
       <c r="D746" s="6"/>
       <c r="G746" s="6"/>
+      <c r="H746" s="6"/>
     </row>
     <row r="747">
       <c r="D747" s="6"/>
       <c r="G747" s="6"/>
+      <c r="H747" s="6"/>
     </row>
     <row r="748">
       <c r="D748" s="6"/>
       <c r="G748" s="6"/>
+      <c r="H748" s="6"/>
     </row>
     <row r="749">
       <c r="D749" s="6"/>
       <c r="G749" s="6"/>
+      <c r="H749" s="6"/>
     </row>
     <row r="750">
       <c r="D750" s="6"/>
       <c r="G750" s="6"/>
+      <c r="H750" s="6"/>
     </row>
     <row r="751">
       <c r="D751" s="6"/>
       <c r="G751" s="6"/>
+      <c r="H751" s="6"/>
     </row>
     <row r="752">
       <c r="D752" s="6"/>
       <c r="G752" s="6"/>
+      <c r="H752" s="6"/>
     </row>
     <row r="753">
       <c r="D753" s="6"/>
       <c r="G753" s="6"/>
+      <c r="H753" s="6"/>
     </row>
     <row r="754">
       <c r="D754" s="6"/>
       <c r="G754" s="6"/>
+      <c r="H754" s="6"/>
     </row>
     <row r="755">
       <c r="D755" s="6"/>
       <c r="G755" s="6"/>
+      <c r="H755" s="6"/>
     </row>
     <row r="756">
       <c r="D756" s="6"/>
       <c r="G756" s="6"/>
+      <c r="H756" s="6"/>
     </row>
     <row r="757">
       <c r="D757" s="6"/>
       <c r="G757" s="6"/>
+      <c r="H757" s="6"/>
     </row>
     <row r="758">
       <c r="D758" s="6"/>
       <c r="G758" s="6"/>
+      <c r="H758" s="6"/>
     </row>
     <row r="759">
       <c r="D759" s="6"/>
       <c r="G759" s="6"/>
+      <c r="H759" s="6"/>
     </row>
     <row r="760">
       <c r="D760" s="6"/>
       <c r="G760" s="6"/>
+      <c r="H760" s="6"/>
     </row>
     <row r="761">
       <c r="D761" s="6"/>
       <c r="G761" s="6"/>
+      <c r="H761" s="6"/>
     </row>
     <row r="762">
       <c r="D762" s="6"/>
       <c r="G762" s="6"/>
+      <c r="H762" s="6"/>
     </row>
     <row r="763">
       <c r="D763" s="6"/>
       <c r="G763" s="6"/>
+      <c r="H763" s="6"/>
     </row>
     <row r="764">
       <c r="D764" s="6"/>
       <c r="G764" s="6"/>
+      <c r="H764" s="6"/>
     </row>
     <row r="765">
       <c r="D765" s="6"/>
       <c r="G765" s="6"/>
+      <c r="H765" s="6"/>
     </row>
     <row r="766">
       <c r="D766" s="6"/>
       <c r="G766" s="6"/>
+      <c r="H766" s="6"/>
     </row>
     <row r="767">
       <c r="D767" s="6"/>
       <c r="G767" s="6"/>
+      <c r="H767" s="6"/>
     </row>
     <row r="768">
       <c r="D768" s="6"/>
       <c r="G768" s="6"/>
+      <c r="H768" s="6"/>
     </row>
     <row r="769">
       <c r="D769" s="6"/>
       <c r="G769" s="6"/>
+      <c r="H769" s="6"/>
     </row>
     <row r="770">
       <c r="D770" s="6"/>
       <c r="G770" s="6"/>
+      <c r="H770" s="6"/>
     </row>
     <row r="771">
       <c r="D771" s="6"/>
       <c r="G771" s="6"/>
+      <c r="H771" s="6"/>
     </row>
     <row r="772">
       <c r="D772" s="6"/>
       <c r="G772" s="6"/>
+      <c r="H772" s="6"/>
     </row>
     <row r="773">
       <c r="D773" s="6"/>
       <c r="G773" s="6"/>
+      <c r="H773" s="6"/>
     </row>
     <row r="774">
       <c r="D774" s="6"/>
       <c r="G774" s="6"/>
+      <c r="H774" s="6"/>
     </row>
     <row r="775">
       <c r="D775" s="6"/>
       <c r="G775" s="6"/>
+      <c r="H775" s="6"/>
     </row>
     <row r="776">
       <c r="D776" s="6"/>
       <c r="G776" s="6"/>
+      <c r="H776" s="6"/>
     </row>
     <row r="777">
       <c r="D777" s="6"/>
       <c r="G777" s="6"/>
+      <c r="H777" s="6"/>
     </row>
     <row r="778">
       <c r="D778" s="6"/>
       <c r="G778" s="6"/>
+      <c r="H778" s="6"/>
     </row>
     <row r="779">
       <c r="D779" s="6"/>
       <c r="G779" s="6"/>
+      <c r="H779" s="6"/>
     </row>
     <row r="780">
       <c r="D780" s="6"/>
       <c r="G780" s="6"/>
+      <c r="H780" s="6"/>
     </row>
     <row r="781">
       <c r="D781" s="6"/>
       <c r="G781" s="6"/>
+      <c r="H781" s="6"/>
     </row>
     <row r="782">
       <c r="D782" s="6"/>
       <c r="G782" s="6"/>
+      <c r="H782" s="6"/>
     </row>
     <row r="783">
       <c r="D783" s="6"/>
       <c r="G783" s="6"/>
+      <c r="H783" s="6"/>
     </row>
     <row r="784">
       <c r="D784" s="6"/>
       <c r="G784" s="6"/>
+      <c r="H784" s="6"/>
     </row>
     <row r="785">
       <c r="D785" s="6"/>
       <c r="G785" s="6"/>
+      <c r="H785" s="6"/>
     </row>
     <row r="786">
       <c r="D786" s="6"/>
       <c r="G786" s="6"/>
+      <c r="H786" s="6"/>
     </row>
     <row r="787">
       <c r="D787" s="6"/>
       <c r="G787" s="6"/>
+      <c r="H787" s="6"/>
     </row>
     <row r="788">
       <c r="D788" s="6"/>
       <c r="G788" s="6"/>
+      <c r="H788" s="6"/>
     </row>
     <row r="789">
       <c r="D789" s="6"/>
       <c r="G789" s="6"/>
+      <c r="H789" s="6"/>
     </row>
     <row r="790">
       <c r="D790" s="6"/>
       <c r="G790" s="6"/>
+      <c r="H790" s="6"/>
     </row>
     <row r="791">
       <c r="D791" s="6"/>
       <c r="G791" s="6"/>
+      <c r="H791" s="6"/>
     </row>
     <row r="792">
       <c r="D792" s="6"/>
       <c r="G792" s="6"/>
+      <c r="H792" s="6"/>
     </row>
     <row r="793">
       <c r="D793" s="6"/>
       <c r="G793" s="6"/>
+      <c r="H793" s="6"/>
     </row>
     <row r="794">
       <c r="D794" s="6"/>
       <c r="G794" s="6"/>
+      <c r="H794" s="6"/>
     </row>
     <row r="795">
       <c r="D795" s="6"/>
       <c r="G795" s="6"/>
+      <c r="H795" s="6"/>
     </row>
     <row r="796">
       <c r="D796" s="6"/>
       <c r="G796" s="6"/>
+      <c r="H796" s="6"/>
     </row>
     <row r="797">
       <c r="D797" s="6"/>
       <c r="G797" s="6"/>
+      <c r="H797" s="6"/>
     </row>
     <row r="798">
       <c r="D798" s="6"/>
       <c r="G798" s="6"/>
+      <c r="H798" s="6"/>
     </row>
     <row r="799">
       <c r="D799" s="6"/>
       <c r="G799" s="6"/>
+      <c r="H799" s="6"/>
     </row>
     <row r="800">
       <c r="D800" s="6"/>
       <c r="G800" s="6"/>
+      <c r="H800" s="6"/>
     </row>
     <row r="801">
       <c r="D801" s="6"/>
       <c r="G801" s="6"/>
+      <c r="H801" s="6"/>
     </row>
     <row r="802">
       <c r="D802" s="6"/>
       <c r="G802" s="6"/>
+      <c r="H802" s="6"/>
     </row>
     <row r="803">
       <c r="D803" s="6"/>
       <c r="G803" s="6"/>
+      <c r="H803" s="6"/>
     </row>
     <row r="804">
       <c r="D804" s="6"/>
       <c r="G804" s="6"/>
+      <c r="H804" s="6"/>
     </row>
     <row r="805">
       <c r="D805" s="6"/>
       <c r="G805" s="6"/>
+      <c r="H805" s="6"/>
     </row>
     <row r="806">
       <c r="D806" s="6"/>
       <c r="G806" s="6"/>
+      <c r="H806" s="6"/>
     </row>
     <row r="807">
       <c r="D807" s="6"/>
       <c r="G807" s="6"/>
+      <c r="H807" s="6"/>
     </row>
     <row r="808">
       <c r="D808" s="6"/>
       <c r="G808" s="6"/>
+      <c r="H808" s="6"/>
     </row>
     <row r="809">
       <c r="D809" s="6"/>
       <c r="G809" s="6"/>
+      <c r="H809" s="6"/>
     </row>
     <row r="810">
       <c r="D810" s="6"/>
       <c r="G810" s="6"/>
+      <c r="H810" s="6"/>
     </row>
     <row r="811">
       <c r="D811" s="6"/>
       <c r="G811" s="6"/>
+      <c r="H811" s="6"/>
     </row>
     <row r="812">
       <c r="D812" s="6"/>
       <c r="G812" s="6"/>
+      <c r="H812" s="6"/>
     </row>
     <row r="813">
       <c r="D813" s="6"/>
       <c r="G813" s="6"/>
+      <c r="H813" s="6"/>
     </row>
     <row r="814">
       <c r="D814" s="6"/>
       <c r="G814" s="6"/>
+      <c r="H814" s="6"/>
     </row>
     <row r="815">
       <c r="D815" s="6"/>
       <c r="G815" s="6"/>
+      <c r="H815" s="6"/>
     </row>
     <row r="816">
       <c r="D816" s="6"/>
       <c r="G816" s="6"/>
+      <c r="H816" s="6"/>
     </row>
     <row r="817">
       <c r="D817" s="6"/>
       <c r="G817" s="6"/>
+      <c r="H817" s="6"/>
     </row>
     <row r="818">
       <c r="D818" s="6"/>
       <c r="G818" s="6"/>
+      <c r="H818" s="6"/>
     </row>
     <row r="819">
       <c r="D819" s="6"/>
       <c r="G819" s="6"/>
+      <c r="H819" s="6"/>
     </row>
     <row r="820">
       <c r="D820" s="6"/>
       <c r="G820" s="6"/>
+      <c r="H820" s="6"/>
     </row>
     <row r="821">
       <c r="D821" s="6"/>
       <c r="G821" s="6"/>
+      <c r="H821" s="6"/>
     </row>
     <row r="822">
       <c r="D822" s="6"/>
       <c r="G822" s="6"/>
+      <c r="H822" s="6"/>
     </row>
     <row r="823">
       <c r="D823" s="6"/>
       <c r="G823" s="6"/>
+      <c r="H823" s="6"/>
     </row>
     <row r="824">
       <c r="D824" s="6"/>
       <c r="G824" s="6"/>
+      <c r="H824" s="6"/>
     </row>
     <row r="825">
       <c r="D825" s="6"/>
       <c r="G825" s="6"/>
+      <c r="H825" s="6"/>
     </row>
     <row r="826">
       <c r="D826" s="6"/>
       <c r="G826" s="6"/>
+      <c r="H826" s="6"/>
     </row>
     <row r="827">
       <c r="D827" s="6"/>
       <c r="G827" s="6"/>
+      <c r="H827" s="6"/>
     </row>
     <row r="828">
       <c r="D828" s="6"/>
       <c r="G828" s="6"/>
+      <c r="H828" s="6"/>
     </row>
     <row r="829">
       <c r="D829" s="6"/>
       <c r="G829" s="6"/>
+      <c r="H829" s="6"/>
     </row>
     <row r="830">
       <c r="D830" s="6"/>
       <c r="G830" s="6"/>
+      <c r="H830" s="6"/>
     </row>
     <row r="831">
       <c r="D831" s="6"/>
       <c r="G831" s="6"/>
+      <c r="H831" s="6"/>
     </row>
     <row r="832">
       <c r="D832" s="6"/>
       <c r="G832" s="6"/>
+      <c r="H832" s="6"/>
     </row>
     <row r="833">
       <c r="D833" s="6"/>
       <c r="G833" s="6"/>
+      <c r="H833" s="6"/>
     </row>
     <row r="834">
       <c r="D834" s="6"/>
       <c r="G834" s="6"/>
+      <c r="H834" s="6"/>
     </row>
     <row r="835">
       <c r="D835" s="6"/>
       <c r="G835" s="6"/>
+      <c r="H835" s="6"/>
     </row>
     <row r="836">
       <c r="D836" s="6"/>
       <c r="G836" s="6"/>
+      <c r="H836" s="6"/>
     </row>
     <row r="837">
       <c r="D837" s="6"/>
       <c r="G837" s="6"/>
+      <c r="H837" s="6"/>
     </row>
     <row r="838">
       <c r="D838" s="6"/>
       <c r="G838" s="6"/>
+      <c r="H838" s="6"/>
     </row>
     <row r="839">
       <c r="D839" s="6"/>
       <c r="G839" s="6"/>
+      <c r="H839" s="6"/>
     </row>
     <row r="840">
       <c r="D840" s="6"/>
       <c r="G840" s="6"/>
+      <c r="H840" s="6"/>
     </row>
     <row r="841">
       <c r="D841" s="6"/>
       <c r="G841" s="6"/>
+      <c r="H841" s="6"/>
     </row>
     <row r="842">
       <c r="D842" s="6"/>
       <c r="G842" s="6"/>
+      <c r="H842" s="6"/>
     </row>
     <row r="843">
       <c r="D843" s="6"/>
       <c r="G843" s="6"/>
+      <c r="H843" s="6"/>
     </row>
     <row r="844">
       <c r="D844" s="6"/>
       <c r="G844" s="6"/>
+      <c r="H844" s="6"/>
     </row>
     <row r="845">
       <c r="D845" s="6"/>
       <c r="G845" s="6"/>
+      <c r="H845" s="6"/>
     </row>
     <row r="846">
       <c r="D846" s="6"/>
       <c r="G846" s="6"/>
+      <c r="H846" s="6"/>
     </row>
     <row r="847">
       <c r="D847" s="6"/>
       <c r="G847" s="6"/>
+      <c r="H847" s="6"/>
     </row>
     <row r="848">
       <c r="D848" s="6"/>
       <c r="G848" s="6"/>
+      <c r="H848" s="6"/>
     </row>
     <row r="849">
       <c r="D849" s="6"/>
       <c r="G849" s="6"/>
+      <c r="H849" s="6"/>
     </row>
     <row r="850">
       <c r="D850" s="6"/>
       <c r="G850" s="6"/>
+      <c r="H850" s="6"/>
     </row>
     <row r="851">
       <c r="D851" s="6"/>
       <c r="G851" s="6"/>
+      <c r="H851" s="6"/>
     </row>
     <row r="852">
       <c r="D852" s="6"/>
       <c r="G852" s="6"/>
+      <c r="H852" s="6"/>
     </row>
     <row r="853">
       <c r="D853" s="6"/>
       <c r="G853" s="6"/>
+      <c r="H853" s="6"/>
     </row>
     <row r="854">
       <c r="D854" s="6"/>
       <c r="G854" s="6"/>
+      <c r="H854" s="6"/>
     </row>
     <row r="855">
       <c r="D855" s="6"/>
       <c r="G855" s="6"/>
+      <c r="H855" s="6"/>
     </row>
     <row r="856">
       <c r="D856" s="6"/>
       <c r="G856" s="6"/>
+      <c r="H856" s="6"/>
     </row>
     <row r="857">
       <c r="D857" s="6"/>
       <c r="G857" s="6"/>
+      <c r="H857" s="6"/>
     </row>
     <row r="858">
       <c r="D858" s="6"/>
       <c r="G858" s="6"/>
+      <c r="H858" s="6"/>
     </row>
     <row r="859">
       <c r="D859" s="6"/>
       <c r="G859" s="6"/>
+      <c r="H859" s="6"/>
     </row>
     <row r="860">
       <c r="D860" s="6"/>
       <c r="G860" s="6"/>
+      <c r="H860" s="6"/>
     </row>
     <row r="861">
       <c r="D861" s="6"/>
       <c r="G861" s="6"/>
+      <c r="H861" s="6"/>
     </row>
     <row r="862">
       <c r="D862" s="6"/>
       <c r="G862" s="6"/>
+      <c r="H862" s="6"/>
     </row>
     <row r="863">
       <c r="D863" s="6"/>
       <c r="G863" s="6"/>
+      <c r="H863" s="6"/>
     </row>
     <row r="864">
       <c r="D864" s="6"/>
       <c r="G864" s="6"/>
+      <c r="H864" s="6"/>
     </row>
     <row r="865">
       <c r="D865" s="6"/>
       <c r="G865" s="6"/>
+      <c r="H865" s="6"/>
     </row>
     <row r="866">
       <c r="D866" s="6"/>
       <c r="G866" s="6"/>
+      <c r="H866" s="6"/>
     </row>
     <row r="867">
       <c r="D867" s="6"/>
       <c r="G867" s="6"/>
+      <c r="H867" s="6"/>
     </row>
     <row r="868">
       <c r="D868" s="6"/>
       <c r="G868" s="6"/>
+      <c r="H868" s="6"/>
     </row>
     <row r="869">
       <c r="D869" s="6"/>
       <c r="G869" s="6"/>
+      <c r="H869" s="6"/>
     </row>
     <row r="870">
       <c r="D870" s="6"/>
       <c r="G870" s="6"/>
+      <c r="H870" s="6"/>
     </row>
     <row r="871">
       <c r="D871" s="6"/>
       <c r="G871" s="6"/>
+      <c r="H871" s="6"/>
     </row>
     <row r="872">
       <c r="D872" s="6"/>
       <c r="G872" s="6"/>
+      <c r="H872" s="6"/>
     </row>
     <row r="873">
       <c r="D873" s="6"/>
       <c r="G873" s="6"/>
+      <c r="H873" s="6"/>
     </row>
     <row r="874">
       <c r="D874" s="6"/>
       <c r="G874" s="6"/>
+      <c r="H874" s="6"/>
     </row>
     <row r="875">
       <c r="D875" s="6"/>
       <c r="G875" s="6"/>
+      <c r="H875" s="6"/>
     </row>
     <row r="876">
       <c r="D876" s="6"/>
       <c r="G876" s="6"/>
+      <c r="H876" s="6"/>
     </row>
     <row r="877">
       <c r="D877" s="6"/>
       <c r="G877" s="6"/>
+      <c r="H877" s="6"/>
     </row>
     <row r="878">
       <c r="D878" s="6"/>
       <c r="G878" s="6"/>
+      <c r="H878" s="6"/>
     </row>
     <row r="879">
       <c r="D879" s="6"/>
       <c r="G879" s="6"/>
+      <c r="H879" s="6"/>
     </row>
     <row r="880">
       <c r="D880" s="6"/>
       <c r="G880" s="6"/>
+      <c r="H880" s="6"/>
     </row>
     <row r="881">
       <c r="D881" s="6"/>
       <c r="G881" s="6"/>
+      <c r="H881" s="6"/>
     </row>
     <row r="882">
       <c r="D882" s="6"/>
       <c r="G882" s="6"/>
+      <c r="H882" s="6"/>
     </row>
     <row r="883">
       <c r="D883" s="6"/>
       <c r="G883" s="6"/>
+      <c r="H883" s="6"/>
     </row>
     <row r="884">
       <c r="D884" s="6"/>
       <c r="G884" s="6"/>
+      <c r="H884" s="6"/>
     </row>
     <row r="885">
       <c r="D885" s="6"/>
       <c r="G885" s="6"/>
+      <c r="H885" s="6"/>
     </row>
     <row r="886">
       <c r="D886" s="6"/>
       <c r="G886" s="6"/>
+      <c r="H886" s="6"/>
     </row>
     <row r="887">
       <c r="D887" s="6"/>
       <c r="G887" s="6"/>
+      <c r="H887" s="6"/>
     </row>
     <row r="888">
       <c r="D888" s="6"/>
       <c r="G888" s="6"/>
+      <c r="H888" s="6"/>
     </row>
     <row r="889">
       <c r="D889" s="6"/>
       <c r="G889" s="6"/>
+      <c r="H889" s="6"/>
     </row>
     <row r="890">
       <c r="D890" s="6"/>
       <c r="G890" s="6"/>
+      <c r="H890" s="6"/>
     </row>
     <row r="891">
       <c r="D891" s="6"/>
       <c r="G891" s="6"/>
+      <c r="H891" s="6"/>
     </row>
     <row r="892">
       <c r="D892" s="6"/>
       <c r="G892" s="6"/>
+      <c r="H892" s="6"/>
     </row>
     <row r="893">
       <c r="D893" s="6"/>
       <c r="G893" s="6"/>
+      <c r="H893" s="6"/>
     </row>
     <row r="894">
       <c r="D894" s="6"/>
       <c r="G894" s="6"/>
+      <c r="H894" s="6"/>
     </row>
     <row r="895">
       <c r="D895" s="6"/>
       <c r="G895" s="6"/>
+      <c r="H895" s="6"/>
     </row>
     <row r="896">
       <c r="D896" s="6"/>
       <c r="G896" s="6"/>
+      <c r="H896" s="6"/>
     </row>
     <row r="897">
       <c r="D897" s="6"/>
       <c r="G897" s="6"/>
+      <c r="H897" s="6"/>
     </row>
     <row r="898">
       <c r="D898" s="6"/>
       <c r="G898" s="6"/>
+      <c r="H898" s="6"/>
     </row>
     <row r="899">
       <c r="D899" s="6"/>
       <c r="G899" s="6"/>
+      <c r="H899" s="6"/>
     </row>
     <row r="900">
       <c r="D900" s="6"/>
       <c r="G900" s="6"/>
+      <c r="H900" s="6"/>
     </row>
     <row r="901">
       <c r="D901" s="6"/>
       <c r="G901" s="6"/>
+      <c r="H901" s="6"/>
     </row>
     <row r="902">
       <c r="D902" s="6"/>
       <c r="G902" s="6"/>
+      <c r="H902" s="6"/>
     </row>
     <row r="903">
       <c r="D903" s="6"/>
       <c r="G903" s="6"/>
+      <c r="H903" s="6"/>
     </row>
     <row r="904">
       <c r="D904" s="6"/>
       <c r="G904" s="6"/>
+      <c r="H904" s="6"/>
     </row>
     <row r="905">
       <c r="D905" s="6"/>
       <c r="G905" s="6"/>
+      <c r="H905" s="6"/>
     </row>
     <row r="906">
       <c r="D906" s="6"/>
       <c r="G906" s="6"/>
+      <c r="H906" s="6"/>
     </row>
     <row r="907">
       <c r="D907" s="6"/>
       <c r="G907" s="6"/>
+      <c r="H907" s="6"/>
     </row>
     <row r="908">
       <c r="D908" s="6"/>
       <c r="G908" s="6"/>
+      <c r="H908" s="6"/>
     </row>
     <row r="909">
       <c r="D909" s="6"/>
       <c r="G909" s="6"/>
+      <c r="H909" s="6"/>
     </row>
     <row r="910">
       <c r="D910" s="6"/>
       <c r="G910" s="6"/>
+      <c r="H910" s="6"/>
     </row>
     <row r="911">
       <c r="D911" s="6"/>
       <c r="G911" s="6"/>
+      <c r="H911" s="6"/>
     </row>
     <row r="912">
       <c r="D912" s="6"/>
       <c r="G912" s="6"/>
+      <c r="H912" s="6"/>
     </row>
     <row r="913">
       <c r="D913" s="6"/>
       <c r="G913" s="6"/>
+      <c r="H913" s="6"/>
     </row>
     <row r="914">
       <c r="D914" s="6"/>
       <c r="G914" s="6"/>
+      <c r="H914" s="6"/>
     </row>
     <row r="915">
       <c r="D915" s="6"/>
       <c r="G915" s="6"/>
+      <c r="H915" s="6"/>
     </row>
     <row r="916">
       <c r="D916" s="6"/>
       <c r="G916" s="6"/>
+      <c r="H916" s="6"/>
     </row>
     <row r="917">
       <c r="D917" s="6"/>
       <c r="G917" s="6"/>
+      <c r="H917" s="6"/>
     </row>
     <row r="918">
       <c r="D918" s="6"/>
       <c r="G918" s="6"/>
+      <c r="H918" s="6"/>
     </row>
     <row r="919">
       <c r="D919" s="6"/>
       <c r="G919" s="6"/>
+      <c r="H919" s="6"/>
     </row>
     <row r="920">
       <c r="D920" s="6"/>
       <c r="G920" s="6"/>
+      <c r="H920" s="6"/>
     </row>
     <row r="921">
       <c r="D921" s="6"/>
       <c r="G921" s="6"/>
+      <c r="H921" s="6"/>
     </row>
     <row r="922">
       <c r="D922" s="6"/>
       <c r="G922" s="6"/>
+      <c r="H922" s="6"/>
     </row>
     <row r="923">
       <c r="D923" s="6"/>
       <c r="G923" s="6"/>
+      <c r="H923" s="6"/>
     </row>
     <row r="924">
       <c r="D924" s="6"/>
       <c r="G924" s="6"/>
+      <c r="H924" s="6"/>
     </row>
     <row r="925">
       <c r="D925" s="6"/>
       <c r="G925" s="6"/>
+      <c r="H925" s="6"/>
     </row>
     <row r="926">
       <c r="D926" s="6"/>
       <c r="G926" s="6"/>
+      <c r="H926" s="6"/>
     </row>
     <row r="927">
       <c r="D927" s="6"/>
       <c r="G927" s="6"/>
+      <c r="H927" s="6"/>
     </row>
     <row r="928">
       <c r="D928" s="6"/>
       <c r="G928" s="6"/>
+      <c r="H928" s="6"/>
     </row>
     <row r="929">
       <c r="D929" s="6"/>
       <c r="G929" s="6"/>
+      <c r="H929" s="6"/>
     </row>
     <row r="930">
       <c r="D930" s="6"/>
       <c r="G930" s="6"/>
+      <c r="H930" s="6"/>
     </row>
     <row r="931">
       <c r="D931" s="6"/>
       <c r="G931" s="6"/>
+      <c r="H931" s="6"/>
     </row>
     <row r="932">
       <c r="D932" s="6"/>
       <c r="G932" s="6"/>
+      <c r="H932" s="6"/>
     </row>
     <row r="933">
       <c r="D933" s="6"/>
       <c r="G933" s="6"/>
+      <c r="H933" s="6"/>
     </row>
     <row r="934">
       <c r="D934" s="6"/>
       <c r="G934" s="6"/>
+      <c r="H934" s="6"/>
     </row>
     <row r="935">
       <c r="D935" s="6"/>
       <c r="G935" s="6"/>
+      <c r="H935" s="6"/>
     </row>
     <row r="936">
       <c r="D936" s="6"/>
       <c r="G936" s="6"/>
+      <c r="H936" s="6"/>
     </row>
     <row r="937">
       <c r="D937" s="6"/>
       <c r="G937" s="6"/>
+      <c r="H937" s="6"/>
     </row>
     <row r="938">
       <c r="D938" s="6"/>
       <c r="G938" s="6"/>
+      <c r="H938" s="6"/>
     </row>
     <row r="939">
       <c r="D939" s="6"/>
       <c r="G939" s="6"/>
+      <c r="H939" s="6"/>
     </row>
     <row r="940">
       <c r="D940" s="6"/>
       <c r="G940" s="6"/>
+      <c r="H940" s="6"/>
     </row>
     <row r="941">
       <c r="D941" s="6"/>
       <c r="G941" s="6"/>
+      <c r="H941" s="6"/>
     </row>
     <row r="942">
       <c r="D942" s="6"/>
       <c r="G942" s="6"/>
+      <c r="H942" s="6"/>
     </row>
     <row r="943">
       <c r="D943" s="6"/>
       <c r="G943" s="6"/>
+      <c r="H943" s="6"/>
     </row>
     <row r="944">
       <c r="D944" s="6"/>
       <c r="G944" s="6"/>
+      <c r="H944" s="6"/>
     </row>
     <row r="945">
       <c r="D945" s="6"/>
       <c r="G945" s="6"/>
+      <c r="H945" s="6"/>
     </row>
     <row r="946">
       <c r="D946" s="6"/>
       <c r="G946" s="6"/>
+      <c r="H946" s="6"/>
     </row>
     <row r="947">
       <c r="D947" s="6"/>
       <c r="G947" s="6"/>
+      <c r="H947" s="6"/>
     </row>
     <row r="948">
       <c r="D948" s="6"/>
       <c r="G948" s="6"/>
+      <c r="H948" s="6"/>
     </row>
     <row r="949">
       <c r="D949" s="6"/>
       <c r="G949" s="6"/>
+      <c r="H949" s="6"/>
     </row>
     <row r="950">
       <c r="D950" s="6"/>
       <c r="G950" s="6"/>
+      <c r="H950" s="6"/>
     </row>
     <row r="951">
       <c r="D951" s="6"/>
       <c r="G951" s="6"/>
+      <c r="H951" s="6"/>
     </row>
     <row r="952">
       <c r="D952" s="6"/>
       <c r="G952" s="6"/>
+      <c r="H952" s="6"/>
     </row>
     <row r="953">
       <c r="D953" s="6"/>
       <c r="G953" s="6"/>
+      <c r="H953" s="6"/>
     </row>
     <row r="954">
       <c r="D954" s="6"/>
       <c r="G954" s="6"/>
+      <c r="H954" s="6"/>
     </row>
     <row r="955">
       <c r="D955" s="6"/>
       <c r="G955" s="6"/>
+      <c r="H955" s="6"/>
     </row>
     <row r="956">
       <c r="D956" s="6"/>
       <c r="G956" s="6"/>
+      <c r="H956" s="6"/>
     </row>
     <row r="957">
       <c r="D957" s="6"/>
       <c r="G957" s="6"/>
+      <c r="H957" s="6"/>
     </row>
     <row r="958">
       <c r="D958" s="6"/>
       <c r="G958" s="6"/>
+      <c r="H958" s="6"/>
     </row>
     <row r="959">
       <c r="D959" s="6"/>
       <c r="G959" s="6"/>
+      <c r="H959" s="6"/>
     </row>
     <row r="960">
       <c r="D960" s="6"/>
       <c r="G960" s="6"/>
+      <c r="H960" s="6"/>
     </row>
     <row r="961">
       <c r="D961" s="6"/>
       <c r="G961" s="6"/>
+      <c r="H961" s="6"/>
     </row>
     <row r="962">
       <c r="D962" s="6"/>
       <c r="G962" s="6"/>
+      <c r="H962" s="6"/>
     </row>
     <row r="963">
       <c r="D963" s="6"/>
       <c r="G963" s="6"/>
+      <c r="H963" s="6"/>
     </row>
     <row r="964">
       <c r="D964" s="6"/>
       <c r="G964" s="6"/>
+      <c r="H964" s="6"/>
     </row>
     <row r="965">
       <c r="D965" s="6"/>
       <c r="G965" s="6"/>
+      <c r="H965" s="6"/>
     </row>
     <row r="966">
       <c r="D966" s="6"/>
       <c r="G966" s="6"/>
+      <c r="H966" s="6"/>
     </row>
     <row r="967">
       <c r="D967" s="6"/>
       <c r="G967" s="6"/>
+      <c r="H967" s="6"/>
     </row>
     <row r="968">
       <c r="D968" s="6"/>
       <c r="G968" s="6"/>
+      <c r="H968" s="6"/>
     </row>
     <row r="969">
       <c r="D969" s="6"/>
       <c r="G969" s="6"/>
+      <c r="H969" s="6"/>
     </row>
     <row r="970">
       <c r="D970" s="6"/>
       <c r="G970" s="6"/>
+      <c r="H970" s="6"/>
     </row>
     <row r="971">
       <c r="D971" s="6"/>
       <c r="G971" s="6"/>
+      <c r="H971" s="6"/>
     </row>
     <row r="972">
       <c r="D972" s="6"/>
       <c r="G972" s="6"/>
+      <c r="H972" s="6"/>
     </row>
     <row r="973">
       <c r="D973" s="6"/>
       <c r="G973" s="6"/>
+      <c r="H973" s="6"/>
     </row>
     <row r="974">
       <c r="D974" s="6"/>
       <c r="G974" s="6"/>
+      <c r="H974" s="6"/>
     </row>
     <row r="975">
       <c r="D975" s="6"/>
       <c r="G975" s="6"/>
+      <c r="H975" s="6"/>
     </row>
     <row r="976">
       <c r="D976" s="6"/>
       <c r="G976" s="6"/>
+      <c r="H976" s="6"/>
     </row>
     <row r="977">
       <c r="D977" s="6"/>
       <c r="G977" s="6"/>
+      <c r="H977" s="6"/>
     </row>
     <row r="978">
       <c r="D978" s="6"/>
       <c r="G978" s="6"/>
+      <c r="H978" s="6"/>
     </row>
     <row r="979">
       <c r="D979" s="6"/>
       <c r="G979" s="6"/>
+      <c r="H979" s="6"/>
     </row>
     <row r="980">
       <c r="D980" s="6"/>
       <c r="G980" s="6"/>
+      <c r="H980" s="6"/>
     </row>
     <row r="981">
       <c r="D981" s="6"/>
       <c r="G981" s="6"/>
+      <c r="H981" s="6"/>
     </row>
     <row r="982">
       <c r="D982" s="6"/>
       <c r="G982" s="6"/>
+      <c r="H982" s="6"/>
     </row>
     <row r="983">
       <c r="D983" s="6"/>
       <c r="G983" s="6"/>
+      <c r="H983" s="6"/>
     </row>
     <row r="984">
       <c r="D984" s="6"/>
       <c r="G984" s="6"/>
+      <c r="H984" s="6"/>
     </row>
     <row r="985">
       <c r="D985" s="6"/>
       <c r="G985" s="6"/>
+      <c r="H985" s="6"/>
     </row>
     <row r="986">
       <c r="D986" s="6"/>
       <c r="G986" s="6"/>
+      <c r="H986" s="6"/>
     </row>
     <row r="987">
       <c r="D987" s="6"/>
       <c r="G987" s="6"/>
+      <c r="H987" s="6"/>
     </row>
     <row r="988">
       <c r="D988" s="6"/>
       <c r="G988" s="6"/>
+      <c r="H988" s="6"/>
     </row>
     <row r="989">
       <c r="D989" s="6"/>
       <c r="G989" s="6"/>
+      <c r="H989" s="6"/>
     </row>
     <row r="990">
       <c r="D990" s="6"/>
       <c r="G990" s="6"/>
+      <c r="H990" s="6"/>
     </row>
     <row r="991">
       <c r="D991" s="6"/>
       <c r="G991" s="6"/>
+      <c r="H991" s="6"/>
     </row>
     <row r="992">
       <c r="D992" s="6"/>
       <c r="G992" s="6"/>
+      <c r="H992" s="6"/>
     </row>
     <row r="993">
       <c r="D993" s="6"/>
       <c r="G993" s="6"/>
+      <c r="H993" s="6"/>
     </row>
     <row r="994">
       <c r="D994" s="6"/>
       <c r="G994" s="6"/>
+      <c r="H994" s="6"/>
     </row>
     <row r="995">
       <c r="D995" s="6"/>
       <c r="G995" s="6"/>
+      <c r="H995" s="6"/>
     </row>
     <row r="996">
       <c r="D996" s="6"/>
       <c r="G996" s="6"/>
+      <c r="H996" s="6"/>
     </row>
     <row r="997">
       <c r="D997" s="6"/>
       <c r="G997" s="6"/>
+      <c r="H997" s="6"/>
     </row>
     <row r="998">
       <c r="D998" s="6"/>
       <c r="G998" s="6"/>
+      <c r="H998" s="6"/>
     </row>
     <row r="999">
       <c r="D999" s="6"/>
       <c r="G999" s="6"/>
+      <c r="H999" s="6"/>
     </row>
     <row r="1000">
       <c r="D1000" s="6"/>
       <c r="G1000" s="6"/>
+      <c r="H1000" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
